--- a/deliverables/qc_gap_analysis/PP_QC_Document_Registers_2026-08-31.xlsx
+++ b/deliverables/qc_gap_analysis/PP_QC_Document_Registers_2026-08-31.xlsx
@@ -2167,9 +2167,9 @@
           <t>microbiology</t>
         </is>
       </c>
-      <c r="K28" s="14" t="inlineStr">
-        <is>
-          <t>amber</t>
+      <c r="K28" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="L28" s="7" t="inlineStr"/>
@@ -2359,9 +2359,9 @@
           <t>microbiology</t>
         </is>
       </c>
-      <c r="K31" s="14" t="inlineStr">
-        <is>
-          <t>amber</t>
+      <c r="K31" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="L31" s="12" t="inlineStr"/>
@@ -2999,9 +2999,9 @@
           <t>microbiology</t>
         </is>
       </c>
-      <c r="K41" s="14" t="inlineStr">
-        <is>
-          <t>amber</t>
+      <c r="K41" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="L41" s="12" t="inlineStr"/>
@@ -4215,9 +4215,9 @@
           <t>microbiology</t>
         </is>
       </c>
-      <c r="K60" s="14" t="inlineStr">
-        <is>
-          <t>amber</t>
+      <c r="K60" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="L60" s="7" t="inlineStr"/>

--- a/deliverables/qc_gap_analysis/PP_QC_Document_Registers_2026-08-31.xlsx
+++ b/deliverables/qc_gap_analysis/PP_QC_Document_Registers_2026-08-31.xlsx
@@ -2167,9 +2167,9 @@
           <t>microbiology</t>
         </is>
       </c>
-      <c r="K28" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="K28" s="14" t="inlineStr">
+        <is>
+          <t>amber</t>
         </is>
       </c>
       <c r="L28" s="7" t="inlineStr"/>
@@ -2359,9 +2359,9 @@
           <t>microbiology</t>
         </is>
       </c>
-      <c r="K31" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="K31" s="14" t="inlineStr">
+        <is>
+          <t>amber</t>
         </is>
       </c>
       <c r="L31" s="12" t="inlineStr"/>
@@ -2999,9 +2999,9 @@
           <t>microbiology</t>
         </is>
       </c>
-      <c r="K41" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="K41" s="14" t="inlineStr">
+        <is>
+          <t>amber</t>
         </is>
       </c>
       <c r="L41" s="12" t="inlineStr"/>
@@ -4215,9 +4215,9 @@
           <t>microbiology</t>
         </is>
       </c>
-      <c r="K60" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="K60" s="14" t="inlineStr">
+        <is>
+          <t>amber</t>
         </is>
       </c>
       <c r="L60" s="7" t="inlineStr"/>

--- a/deliverables/qc_gap_analysis/PP_QC_Document_Registers_2026-08-31.xlsx
+++ b/deliverables/qc_gap_analysis/PP_QC_Document_Registers_2026-08-31.xlsx
@@ -780,7 +780,7 @@
       <c r="H6" s="6" t="inlineStr"/>
       <c r="I6" s="7" t="inlineStr">
         <is>
-          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB /1 g, Salmonella /25 g, E. coli /1 g</t>
+          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB CFU/g, Salmonella /25 g, E. coli /1 g</t>
         </is>
       </c>
       <c r="J6" s="8" t="inlineStr">
@@ -840,7 +840,7 @@
       <c r="H7" s="11" t="inlineStr"/>
       <c r="I7" s="12" t="inlineStr">
         <is>
-          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB /1 g, Salmonella /25 g, E. coli /1 g</t>
+          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB CFU/g, Salmonella /25 g, E. coli /1 g</t>
         </is>
       </c>
       <c r="J7" s="8" t="inlineStr">
@@ -900,7 +900,7 @@
       <c r="H8" s="6" t="inlineStr"/>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB /1 g, Salmonella /25 g, E. coli /1 g</t>
+          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB CFU/g, Salmonella /25 g, E. coli /1 g</t>
         </is>
       </c>
       <c r="J8" s="8" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="I17" s="12" t="inlineStr">
         <is>
-          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB /1 g, Salmonella /25 g, E. coli /1 g</t>
+          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB CFU/g, Salmonella /25 g, E. coli /1 g</t>
         </is>
       </c>
       <c r="J17" s="8" t="inlineStr">
@@ -1516,7 +1516,7 @@
       </c>
       <c r="I18" s="7" t="inlineStr">
         <is>
-          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB /1 g, Salmonella /25 g, E. coli /1 g</t>
+          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB CFU/g, Salmonella /25 g, E. coli /1 g</t>
         </is>
       </c>
       <c r="J18" s="8" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="I21" s="12" t="inlineStr">
         <is>
-          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB /1 g, Salmonella /25 g, E. coli /1 g</t>
+          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB CFU/g, Salmonella /25 g, E. coli /1 g</t>
         </is>
       </c>
       <c r="J21" s="8" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="I26" s="7" t="inlineStr">
         <is>
-          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB /1 g, Salmonella /25 g, E. coli /1 g</t>
+          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB CFU/g, Salmonella /25 g, E. coli /1 g</t>
         </is>
       </c>
       <c r="J26" s="9" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="I28" s="7" t="inlineStr">
         <is>
-          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB /1 g, Salmonella /25 g, E. coli /1 g</t>
+          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB CFU/g, Salmonella /25 g, E. coli /1 g</t>
         </is>
       </c>
       <c r="J28" s="8" t="inlineStr">
@@ -2348,7 +2348,7 @@
       </c>
       <c r="I31" s="12" t="inlineStr">
         <is>
-          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB /1 g, Salmonella /25 g, E. coli /1 g</t>
+          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB CFU/g, Salmonella /25 g, E. coli /1 g</t>
         </is>
       </c>
       <c r="J31" s="8" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="I32" s="7" t="inlineStr">
         <is>
-          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB /1 g, Salmonella /25 g, E. coli /1 g</t>
+          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB CFU/g, Salmonella /25 g, E. coli /1 g</t>
         </is>
       </c>
       <c r="J32" s="8" t="inlineStr">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="I40" s="7" t="inlineStr">
         <is>
-          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB /1 g, Salmonella /25 g, E. coli /1 g</t>
+          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB CFU/g, Salmonella /25 g, E. coli /1 g</t>
         </is>
       </c>
       <c r="J40" s="8" t="inlineStr">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="I41" s="12" t="inlineStr">
         <is>
-          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB /1 g, Salmonella /25 g, E. coli /1 g</t>
+          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB CFU/g, Salmonella /25 g, E. coli /1 g</t>
         </is>
       </c>
       <c r="J41" s="8" t="inlineStr">
@@ -3052,7 +3052,7 @@
       </c>
       <c r="I42" s="7" t="inlineStr">
         <is>
-          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB /1 g, Salmonella /25 g, E. coli /1 g</t>
+          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB CFU/g, Salmonella /25 g, E. coli /1 g</t>
         </is>
       </c>
       <c r="J42" s="8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="I50" s="7" t="inlineStr">
         <is>
-          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB /1 g, Salmonella /25 g, E. coli /1 g</t>
+          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB CFU/g, Salmonella /25 g, E. coli /1 g</t>
         </is>
       </c>
       <c r="J50" s="8" t="inlineStr">
@@ -3628,7 +3628,7 @@
       </c>
       <c r="I51" s="12" t="inlineStr">
         <is>
-          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB /1 g, Salmonella /25 g, E. coli /1 g</t>
+          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB CFU/g, Salmonella /25 g, E. coli /1 g</t>
         </is>
       </c>
       <c r="J51" s="8" t="inlineStr">
@@ -3756,7 +3756,7 @@
       </c>
       <c r="I53" s="12" t="inlineStr">
         <is>
-          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB /1 g, Salmonella /25 g, E. coli /1 g</t>
+          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB CFU/g, Salmonella /25 g, E. coli /1 g</t>
         </is>
       </c>
       <c r="J53" s="8" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="I60" s="7" t="inlineStr">
         <is>
-          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB /1 g, Salmonella /25 g, E. coli /1 g</t>
+          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB CFU/g, Salmonella /25 g, E. coli /1 g</t>
         </is>
       </c>
       <c r="J60" s="8" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="I62" s="7" t="inlineStr">
         <is>
-          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB /1 g, Salmonella /25 g, E. coli /1 g</t>
+          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB CFU/g, Salmonella /25 g, E. coli /1 g</t>
         </is>
       </c>
       <c r="J62" s="8" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="I63" s="12" t="inlineStr">
         <is>
-          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB /1 g, Salmonella /25 g, E. coli /1 g</t>
+          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB CFU/g, Salmonella /25 g, E. coli /1 g</t>
         </is>
       </c>
       <c r="J63" s="8" t="inlineStr">
@@ -4460,7 +4460,7 @@
       </c>
       <c r="I64" s="7" t="inlineStr">
         <is>
-          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB /1 g, Salmonella /25 g, E. coli /1 g</t>
+          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB CFU/g, Salmonella /25 g, E. coli /1 g</t>
         </is>
       </c>
       <c r="J64" s="8" t="inlineStr">
@@ -4780,7 +4780,7 @@
       </c>
       <c r="I69" s="12" t="inlineStr">
         <is>
-          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB /1 g, Salmonella /25 g, E. coli /1 g</t>
+          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB CFU/g, Salmonella /25 g, E. coli /1 g</t>
         </is>
       </c>
       <c r="J69" s="8" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="I70" s="7" t="inlineStr">
         <is>
-          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB /1 g, Salmonella /25 g, E. coli /1 g</t>
+          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB CFU/g, Salmonella /25 g, E. coli /1 g</t>
         </is>
       </c>
       <c r="J70" s="8" t="inlineStr">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="I76" s="7" t="inlineStr">
         <is>
-          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB /1 g, Salmonella /25 g, E. coli /1 g</t>
+          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB CFU/g, Salmonella /25 g, E. coli /1 g</t>
         </is>
       </c>
       <c r="J76" s="8" t="inlineStr">
@@ -5292,7 +5292,7 @@
       </c>
       <c r="I77" s="12" t="inlineStr">
         <is>
-          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB /1 g, Salmonella /25 g, E. coli /1 g</t>
+          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB CFU/g, Salmonella /25 g, E. coli /1 g</t>
         </is>
       </c>
       <c r="J77" s="8" t="inlineStr">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="I84" s="7" t="inlineStr">
         <is>
-          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB /1 g, Salmonella /25 g, E. coli /1 g</t>
+          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB CFU/g, Salmonella /25 g, E. coli /1 g</t>
         </is>
       </c>
       <c r="J84" s="8" t="inlineStr">
@@ -5868,7 +5868,7 @@
       </c>
       <c r="I86" s="7" t="inlineStr">
         <is>
-          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB /1 g, Salmonella /25 g, E. coli /1 g</t>
+          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB CFU/g, Salmonella /25 g, E. coli /1 g</t>
         </is>
       </c>
       <c r="J86" s="8" t="inlineStr">
@@ -5932,7 +5932,7 @@
       </c>
       <c r="I87" s="12" t="inlineStr">
         <is>
-          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB /1 g, Salmonella /25 g, E. coli /1 g</t>
+          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB CFU/g, Salmonella /25 g, E. coli /1 g</t>
         </is>
       </c>
       <c r="J87" s="8" t="inlineStr">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="I88" s="7" t="inlineStr">
         <is>
-          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB /1 g, Salmonella /25 g, E. coli /1 g</t>
+          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB CFU/g, Salmonella /25 g, E. coli /1 g</t>
         </is>
       </c>
       <c r="J88" s="8" t="inlineStr">
@@ -6060,7 +6060,7 @@
       </c>
       <c r="I89" s="12" t="inlineStr">
         <is>
-          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB /1 g, Salmonella /25 g, E. coli /1 g</t>
+          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB CFU/g, Salmonella /25 g, E. coli /1 g</t>
         </is>
       </c>
       <c r="J89" s="8" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="I96" s="7" t="inlineStr">
         <is>
-          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB /1 g, Salmonella /25 g, E. coli /1 g</t>
+          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB CFU/g, Salmonella /25 g, E. coli /1 g</t>
         </is>
       </c>
       <c r="J96" s="8" t="inlineStr">
@@ -6572,7 +6572,7 @@
       </c>
       <c r="I97" s="12" t="inlineStr">
         <is>
-          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB /1 g, Salmonella /25 g, E. coli /1 g</t>
+          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB CFU/g, Salmonella /25 g, E. coli /1 g</t>
         </is>
       </c>
       <c r="J97" s="8" t="inlineStr">
@@ -6636,7 +6636,7 @@
       </c>
       <c r="I98" s="7" t="inlineStr">
         <is>
-          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB /1 g, Salmonella /25 g, E. coli /1 g</t>
+          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB CFU/g, Salmonella /25 g, E. coli /1 g</t>
         </is>
       </c>
       <c r="J98" s="8" t="inlineStr">
@@ -6700,7 +6700,7 @@
       </c>
       <c r="I99" s="12" t="inlineStr">
         <is>
-          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB /1 g, Salmonella /25 g, E. coli /1 g</t>
+          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB CFU/g, Salmonella /25 g, E. coli /1 g</t>
         </is>
       </c>
       <c r="J99" s="8" t="inlineStr">
@@ -7276,7 +7276,7 @@
       </c>
       <c r="I108" s="7" t="inlineStr">
         <is>
-          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB /1 g, Salmonella /25 g, E. coli /1 g</t>
+          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB CFU/g, Salmonella /25 g, E. coli /1 g</t>
         </is>
       </c>
       <c r="J108" s="8" t="inlineStr">
@@ -7340,7 +7340,7 @@
       </c>
       <c r="I109" s="12" t="inlineStr">
         <is>
-          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB /1 g, Salmonella /25 g, E. coli /1 g</t>
+          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB CFU/g, Salmonella /25 g, E. coli /1 g</t>
         </is>
       </c>
       <c r="J109" s="8" t="inlineStr">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="I110" s="7" t="inlineStr">
         <is>
-          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB /1 g, Salmonella /25 g, E. coli /1 g</t>
+          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB CFU/g, Salmonella /25 g, E. coli /1 g</t>
         </is>
       </c>
       <c r="J110" s="8" t="inlineStr">
@@ -7468,7 +7468,7 @@
       </c>
       <c r="I111" s="12" t="inlineStr">
         <is>
-          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB /1 g, Salmonella /25 g, E. coli /1 g</t>
+          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB CFU/g, Salmonella /25 g, E. coli /1 g</t>
         </is>
       </c>
       <c r="J111" s="8" t="inlineStr">
@@ -7532,7 +7532,7 @@
       </c>
       <c r="I112" s="7" t="inlineStr">
         <is>
-          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB /1 g, Salmonella /25 g, E. coli /1 g</t>
+          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB CFU/g, Salmonella /25 g, E. coli /1 g</t>
         </is>
       </c>
       <c r="J112" s="8" t="inlineStr">
@@ -7596,7 +7596,7 @@
       </c>
       <c r="I113" s="12" t="inlineStr">
         <is>
-          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB /1 g, Salmonella /25 g, E. coli /1 g</t>
+          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB CFU/g, Salmonella /25 g, E. coli /1 g</t>
         </is>
       </c>
       <c r="J113" s="8" t="inlineStr">
@@ -7660,7 +7660,7 @@
       </c>
       <c r="I114" s="7" t="inlineStr">
         <is>
-          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB /1 g, Salmonella /25 g, E. coli /1 g</t>
+          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB CFU/g, Salmonella /25 g, E. coli /1 g</t>
         </is>
       </c>
       <c r="J114" s="8" t="inlineStr">
@@ -7724,7 +7724,7 @@
       </c>
       <c r="I115" s="12" t="inlineStr">
         <is>
-          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB /1 g, Salmonella /25 g, E. coli /1 g</t>
+          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB CFU/g, Salmonella /25 g, E. coli /1 g</t>
         </is>
       </c>
       <c r="J115" s="8" t="inlineStr">
@@ -7788,7 +7788,7 @@
       </c>
       <c r="I116" s="7" t="inlineStr">
         <is>
-          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB /1 g, Salmonella /25 g, E. coli /1 g</t>
+          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB CFU/g, Salmonella /25 g, E. coli /1 g</t>
         </is>
       </c>
       <c r="J116" s="8" t="inlineStr">
@@ -11312,7 +11312,7 @@
       <c r="H172" s="6" t="inlineStr"/>
       <c r="I172" s="7" t="inlineStr">
         <is>
-          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB /1 g, Salmonella /25 g, E. coli /1 g</t>
+          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB CFU/g, Salmonella /25 g, E. coli /1 g</t>
         </is>
       </c>
       <c r="J172" s="9" t="inlineStr">
@@ -11372,7 +11372,7 @@
       <c r="H173" s="11" t="inlineStr"/>
       <c r="I173" s="12" t="inlineStr">
         <is>
-          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB /1 g, Salmonella /25 g, E. coli /1 g</t>
+          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB CFU/g, Salmonella /25 g, E. coli /1 g</t>
         </is>
       </c>
       <c r="J173" s="9" t="inlineStr">
@@ -11432,7 +11432,7 @@
       <c r="H174" s="6" t="inlineStr"/>
       <c r="I174" s="7" t="inlineStr">
         <is>
-          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB /1 g, Salmonella /25 g, E. coli /1 g</t>
+          <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB CFU/g, Salmonella /25 g, E. coli /1 g</t>
         </is>
       </c>
       <c r="J174" s="8" t="inlineStr">
@@ -14720,9 +14720,9 @@
           <t>not verified</t>
         </is>
       </c>
-      <c r="K227" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="K227" s="14" t="inlineStr">
+        <is>
+          <t>amber</t>
         </is>
       </c>
       <c r="L227" s="12" t="inlineStr">
@@ -22337,7 +22337,7 @@
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>of 21 required</t>
+          <t>of 21 on an initial CoQ, 10 in the retest scope</t>
         </is>
       </c>
       <c r="M5" s="4" t="inlineStr"/>
@@ -32560,7 +32560,7 @@
       <c r="Q132" s="7" t="inlineStr"/>
       <c r="R132" s="7" t="inlineStr">
         <is>
-          <t>Farmahem — Ident A + B + C with the Assay, at retest</t>
+          <t>Farmahem — Ident A + B + C with the Assay, at retest; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
       <c r="S132" s="17" t="inlineStr">
@@ -32647,7 +32647,7 @@
       </c>
       <c r="R133" s="12" t="inlineStr">
         <is>
-          <t>Farmahem — Ident A + B + C with the Assay, at retest</t>
+          <t>Farmahem — Ident A + B + C with the Assay, at retest; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
       <c r="S133" s="17" t="inlineStr">
@@ -32813,7 +32813,7 @@
       <c r="Q135" s="12" t="inlineStr"/>
       <c r="R135" s="12" t="inlineStr">
         <is>
-          <t>Farmahem — Ident A + B + C with the Assay, at retest</t>
+          <t>Farmahem — Ident A + B + C with the Assay, at retest; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
       <c r="S135" s="17" t="inlineStr">
@@ -34646,7 +34646,7 @@
       <c r="Q162" s="7" t="inlineStr"/>
       <c r="R162" s="7" t="inlineStr">
         <is>
-          <t>Farmahem — Ident A + B + C with the Assay, at retest</t>
+          <t>Farmahem — Ident A + B + C with the Assay, at retest; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
       <c r="S162" s="7" t="inlineStr"/>
@@ -34713,7 +34713,7 @@
       <c r="Q163" s="12" t="inlineStr"/>
       <c r="R163" s="12" t="inlineStr">
         <is>
-          <t>Farmahem — Ident A + B + C with the Assay, at retest</t>
+          <t>Farmahem — Ident A + B + C with the Assay, at retest; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
       <c r="S163" s="12" t="inlineStr"/>
@@ -34780,7 +34780,7 @@
       <c r="Q164" s="7" t="inlineStr"/>
       <c r="R164" s="7" t="inlineStr">
         <is>
-          <t>Farmahem — Ident A + B + C with the Assay, at retest</t>
+          <t>Farmahem — Ident A + B + C with the Assay, at retest; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
       <c r="S164" s="7" t="inlineStr"/>
@@ -34847,7 +34847,7 @@
       <c r="Q165" s="12" t="inlineStr"/>
       <c r="R165" s="12" t="inlineStr">
         <is>
-          <t>Farmahem — Ident A + B + C with the Assay, at retest</t>
+          <t>Farmahem — Ident A + B + C with the Assay, at retest; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
       <c r="S165" s="12" t="inlineStr"/>
@@ -34914,7 +34914,7 @@
       <c r="Q166" s="7" t="inlineStr"/>
       <c r="R166" s="7" t="inlineStr">
         <is>
-          <t>Farmahem — Ident A + B + C with the Assay, at retest</t>
+          <t>Farmahem — Ident A + B + C with the Assay, at retest; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
       <c r="S166" s="7" t="inlineStr"/>
@@ -34981,7 +34981,7 @@
       <c r="Q167" s="12" t="inlineStr"/>
       <c r="R167" s="12" t="inlineStr">
         <is>
-          <t>Farmahem — Ident A + B + C with the Assay, at retest</t>
+          <t>Farmahem — Ident A + B + C with the Assay, at retest; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
       <c r="S167" s="12" t="inlineStr"/>
@@ -35048,7 +35048,7 @@
       <c r="Q168" s="7" t="inlineStr"/>
       <c r="R168" s="7" t="inlineStr">
         <is>
-          <t>Farmahem — Ident A + B + C with the Assay, at retest</t>
+          <t>Farmahem — Ident A + B + C with the Assay, at retest; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
       <c r="S168" s="7" t="inlineStr"/>
@@ -35182,7 +35182,7 @@
       <c r="Q170" s="7" t="inlineStr"/>
       <c r="R170" s="7" t="inlineStr">
         <is>
-          <t>Farmahem — Ident A + B + C with the Assay, at retest</t>
+          <t>Farmahem — Ident A + B + C with the Assay, at retest; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
       <c r="S170" s="7" t="inlineStr"/>
@@ -35270,7 +35270,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C55"/>
+  <dimension ref="A1:C58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -35349,7 +35349,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>one per batch</t>
+          <t>one row per register entry — NOT one per material: six rows (P060152, P060212, P060242, P060352, P060382, P060402) are the Farmahem 12-month re-analyses of plan lots that also appear under their cultivation batch</t>
         </is>
       </c>
     </row>
@@ -35484,7 +35484,7 @@
     <row r="19">
       <c r="A19" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">  re-analysed early — reissue issuable now</t>
+          <t xml:space="preserve">  re-analysed ahead of the 12-month date</t>
         </is>
       </c>
       <c r="B19" s="20" t="n">
@@ -35492,14 +35492,24 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>the Farmahem 197-series pair is already on file</t>
+          <t>the 197-series pair is on file — cannabinoids and mycotoxins certified; identity and foreign matter still to perform before any of them can issue</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="21" t="inlineStr"/>
-      <c r="B20" s="20" t="inlineStr"/>
-      <c r="C20" s="2" t="inlineStr"/>
+      <c r="A20" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  initial CoQs whose banner potency is the re-analysis, not the release assay</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="n">
+        <v>19</v>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>the master spec carries the newest assay; defensible only because no CoQ issues before 11.05.2026 — a QC decision to take knowingly</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="21" t="inlineStr"/>
@@ -35509,348 +35519,373 @@
     <row r="22">
       <c r="A22" s="19" t="inlineStr">
         <is>
+          <t>In-house certificates the routing requires</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="n">
+        <v>224</v>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>one Ident A + B and one foreign-matter iCoA per initial CoQ where no outsourced certificate covers them; one foreign-matter iCoA per reissue</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="21" t="inlineStr"/>
+      <c r="B23" s="20" t="inlineStr"/>
+      <c r="C23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="21" t="inlineStr"/>
+      <c r="B24" s="20" t="inlineStr"/>
+      <c r="C24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
           <t>CoQ parameter schedule</t>
         </is>
       </c>
-      <c r="B22" s="20" t="n">
+      <c r="B25" s="20" t="n">
         <v>3818</v>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>166 CoQs x 23 determinations</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  covered by a certificate on file</t>
-        </is>
-      </c>
-      <c r="B23" s="20" t="n">
-        <v>895</v>
-      </c>
-      <c r="C23" s="2" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  still to be performed</t>
-        </is>
-      </c>
-      <c r="B24" s="20" t="n">
-        <v>625</v>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>identity A, B, C and foreign matter — routed per the Sourcing routes sheet</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  awaiting the 12-month re-analysis — Farmahem</t>
-        </is>
-      </c>
-      <c r="B25" s="20" t="n">
-        <v>372</v>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>cannabinoids + mycotoxins on every not-yet-re-analysed batch</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">  outside the retest scope</t>
+          <t xml:space="preserve">  covered by a certificate on file</t>
         </is>
       </c>
       <c r="B26" s="20" t="n">
-        <v>913</v>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>on a reissue, the release determination stands on the initial CoQ</t>
-        </is>
-      </c>
+        <v>895</v>
+      </c>
+      <c r="C26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">  not tested by anyone</t>
+          <t xml:space="preserve">  still to be performed</t>
         </is>
       </c>
       <c r="B27" s="20" t="n">
-        <v>662</v>
-      </c>
-      <c r="C27" s="2" t="inlineStr"/>
+        <v>625</v>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>identity A, B, C and foreign matter — routed per the Sourcing routes sheet</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">  criterion unstatable — no product specification</t>
+          <t xml:space="preserve">  awaiting the 12-month re-analysis — Farmahem</t>
         </is>
       </c>
       <c r="B28" s="20" t="n">
-        <v>0</v>
+        <v>372</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>parameter 4's criterion is 'per target grade as per Section 01'</t>
+          <t>cannabinoids + mycotoxins on every not-yet-re-analysed batch</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">  upon request — not required for release</t>
+          <t xml:space="preserve">  outside the retest scope</t>
         </is>
       </c>
       <c r="B29" s="20" t="n">
-        <v>332</v>
+        <v>913</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>P. aeruginosa and S. aureus</t>
+          <t>on a reissue, the release determination stands on the initial CoQ</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">  out of specification</t>
+          <t xml:space="preserve">  not tested by anyone</t>
         </is>
       </c>
       <c r="B30" s="20" t="n">
-        <v>6</v>
+        <v>662</v>
       </c>
       <c r="C30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">  undetermined pending the QCSP 001 reading</t>
+          <t xml:space="preserve">  criterion unstatable — no product specification</t>
         </is>
       </c>
       <c r="B31" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="C31" s="2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>parameter 4's criterion is 'per target grade as per Section 01'</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="21" t="inlineStr"/>
-      <c r="B32" s="20" t="inlineStr"/>
-      <c r="C32" s="2" t="inlineStr"/>
+      <c r="A32" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  upon request — not required for release</t>
+        </is>
+      </c>
+      <c r="B32" s="20" t="n">
+        <v>332</v>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>P. aeruginosa and S. aureus</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="19" t="inlineStr">
-        <is>
-          <t>Determinations no laboratory has ever performed</t>
-        </is>
-      </c>
-      <c r="B33" s="20" t="inlineStr"/>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>per CoQ, over 166 CoQs</t>
-        </is>
-      </c>
+      <c r="A33" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  out of specification</t>
+        </is>
+      </c>
+      <c r="B33" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="C33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Identification A, Appearance · Macroscopic</t>
+          <t xml:space="preserve">  undetermined pending the QCSP 001 reading</t>
         </is>
       </c>
       <c r="B34" s="20" t="n">
-        <v>153</v>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>QCSP 001 no. 1</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="C34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Identification B · Microscopic</t>
-        </is>
-      </c>
-      <c r="B35" s="20" t="n">
-        <v>154</v>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>QCSP 001 no. 2</t>
-        </is>
-      </c>
+      <c r="A35" s="21" t="inlineStr"/>
+      <c r="B35" s="20" t="inlineStr"/>
+      <c r="C35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Identification C · HPLC/HPTLC</t>
-        </is>
-      </c>
-      <c r="B36" s="20" t="n">
-        <v>165</v>
-      </c>
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>Determinations no laboratory has ever performed</t>
+        </is>
+      </c>
+      <c r="B36" s="20" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>QCSP 001 no. 3</t>
+          <t>per CoQ, over 166 CoQs</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Total CBN</t>
+          <t xml:space="preserve">  Identification A, Appearance · Macroscopic</t>
         </is>
       </c>
       <c r="B37" s="20" t="n">
-        <v>61</v>
+        <v>153</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>QCSP 001 no. 6</t>
+          <t>QCSP 001 no. 1</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Foreign Matter</t>
+          <t xml:space="preserve">  Identification B · Microscopic</t>
         </is>
       </c>
       <c r="B38" s="20" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>QCSP 001 no. 7</t>
+          <t>QCSP 001 no. 2</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Aflatoxin B₁</t>
+          <t xml:space="preserve">  Identification C · HPLC/HPTLC</t>
         </is>
       </c>
       <c r="B39" s="20" t="n">
-        <v>82</v>
+        <v>165</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>QCSP 001 no. 10.1</t>
+          <t>QCSP 001 no. 3</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="21" t="inlineStr">
         <is>
+          <t xml:space="preserve">  Total CBN</t>
+        </is>
+      </c>
+      <c r="B40" s="20" t="n">
+        <v>61</v>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>QCSP 001 no. 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Foreign Matter</t>
+        </is>
+      </c>
+      <c r="B41" s="20" t="n">
+        <v>153</v>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>QCSP 001 no. 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Aflatoxin B₁</t>
+        </is>
+      </c>
+      <c r="B42" s="20" t="n">
+        <v>82</v>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>QCSP 001 no. 10.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="21" t="inlineStr">
+        <is>
           <t xml:space="preserve">  Ochratoxin A</t>
         </is>
       </c>
-      <c r="B40" s="20" t="n">
+      <c r="B43" s="20" t="n">
         <v>82</v>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>QCSP 001 no. 10.3</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="21" t="inlineStr"/>
-      <c r="B41" s="20" t="inlineStr"/>
-      <c r="C41" s="2" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="19" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="21" t="inlineStr"/>
+      <c r="B44" s="20" t="inlineStr"/>
+      <c r="C44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="19" t="inlineStr">
         <is>
           <t>CoQs whose grade range disagrees with the QCSP 001 PDF</t>
         </is>
       </c>
-      <c r="B42" s="20" t="n">
+      <c r="B45" s="20" t="n">
         <v>54</v>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>two owner documents, two grade designs — recorded, not resolved</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="22" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="22" t="inlineStr">
         <is>
           <t>NOTES</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="14" customHeight="1">
-      <c r="A46" s="23" t="inlineStr">
+    <row r="49" ht="14" customHeight="1">
+      <c r="A49" s="23" t="inlineStr">
         <is>
           <t>THE CULTIVATION-BATCH / PACKAGED-LOT LINKAGE, and why the CoQ total depends on it.</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="48" customHeight="1">
-      <c r="A47" s="23" t="inlineStr">
+    <row r="50" ht="48" customHeight="1">
+      <c r="A50" s="23" t="inlineStr">
         <is>
           <t>PP_Potency_MASTER_Spec.xlsx carries a column the release register does not: Cultiv. Batch No. beside PP Batch No. Seven register entries named by a P-number are packaged lots, and for four of them the cultivation batch is a separate register entry of its own: P060152 (ref 72) from J31102501 (ref 43); P060212 (73) from JD112501 (58); P060242 (74) from OPM122501 (51); P060402 (78) from GG012603 (62).</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="48" customHeight="1">
-      <c r="A48" s="23" t="inlineStr">
+    <row r="51" ht="48" customHeight="1">
+      <c r="A51" s="23" t="inlineStr">
         <is>
           <t>That is what those seven were. They carry only the Farmahem 197-series because that is the analysis performed at packaging; their earlier testing sits under the cultivation batch's own entry. Two more — P060352 from FB012602, P060382 from SCR012603 — are packaged lots whose cultivation batch is not in the release register at all. P060332 appears in neither document.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="48" customHeight="1">
-      <c r="A49" s="23" t="inlineStr">
-        <is>
-          <t>So for four batches the register counts the same material twice, and the CoQ total turns on whether a CoQ is issued per cultivation batch or per released lot. 102 is the count on the register's own numbering; issuing one CoQ per released material instead would remove four. That is a QC decision and is not made here — the linkage is carried on every sheet so the question is visible wherever a count is read.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="24" t="inlineStr"/>
-    </row>
-    <row r="51" ht="60" customHeight="1">
-      <c r="A51" s="23" t="inlineStr">
-        <is>
-          <t>WHY THE iCoA SHEET STILL LISTS 81 WHILE THE ISSUE_COQ PLAN CARRIES 61 CoQ DOCUMENTS. The 81 rows predate the plan and are kept as the per-cultivation-batch view; the plan's iCoA-PP-YYYY-NNNN references and the routing decision of 31.08.2026 are on the CoQ sheets and in PP_CoQ_Parameter_Schedule_2026-08-31.xlsx. Identity and foreign matter are properties of the material, determined once. A CoQ reissued because the cannabinoids and mycotoxins were re-analysed covers the same batch, so it references the iCoA already issued.</t>
         </is>
       </c>
     </row>
     <row r="52" ht="48" customHeight="1">
       <c r="A52" s="23" t="inlineStr">
         <is>
+          <t>So for four batches the register counts the same material twice, and the CoQ total turns on whether a CoQ is issued per cultivation batch or per released lot. 102 is the count on the register's own numbering; issuing one CoQ per released material instead would remove four. That is a QC decision and is not made here — the linkage is carried on every sheet so the question is visible wherever a count is read.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="24" t="inlineStr"/>
+    </row>
+    <row r="54" ht="60" customHeight="1">
+      <c r="A54" s="23" t="inlineStr">
+        <is>
+          <t>WHY THE iCoA SHEET STILL LISTS 81 WHILE THE ISSUE_COQ PLAN CARRIES 61 CoQ DOCUMENTS. The 81 rows predate the plan and are kept as the per-cultivation-batch view; the plan's iCoA-PP-YYYY-NNNN references and the routing decision of 31.08.2026 are on the CoQ sheets and in PP_CoQ_Parameter_Schedule_2026-08-31.xlsx. Identity and foreign matter are properties of the material, determined once. A CoQ reissued because the cannabinoids and mycotoxins were re-analysed covers the same batch, so it references the iCoA already issued.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="48" customHeight="1">
+      <c r="A55" s="23" t="inlineStr">
+        <is>
           <t>WHERE THE SCOPE SPLIT COMES FROM. CNP changed its certificate form in mid-2026: the older DAB form reports loss on drying and cannabinoids only; the Ph. Eur. 11.5 form adds identification (macroscopy and microscopy) and foreign matter. Twelve certificates are on the newer form — ППК26110-26119, ППК26127, ППК26128 — and all 73 CNP certificates were read off their own pages on 31.08.2026, so this is not inferred from a filename or a parse.</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="36" customHeight="1">
-      <c r="A53" s="23" t="inlineStr">
+    <row r="56" ht="36" customHeight="1">
+      <c r="A56" s="23" t="inlineStr">
         <is>
           <t>IDENTIFICATION C is on every iCoA because no laboratory has ever performed it. Those twelve Ph. Eur. pages print Идентификација — Макроскопија, Микроскопија and stop. It is discharged in-house by risk analysis with scientific justification, from the HPLC assay.</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="36" customHeight="1">
-      <c r="A54" s="23" t="inlineStr">
+    <row r="57" ht="36" customHeight="1">
+      <c r="A57" s="23" t="inlineStr">
         <is>
           <t>FB032601 needs Ident C only, like its eleven siblings, and its CoQ still cannot be issued: the foreign matter CNP does cover reads 0.08 % against a 2.00 % maximum and is marked Не одговара, cannabis seed present. A blocker, not a gap.</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="24" customHeight="1">
-      <c r="A55" s="23" t="inlineStr">
+    <row r="58" ht="24" customHeight="1">
+      <c r="A58" s="23" t="inlineStr">
         <is>
           <t>THE BLANK COLUMNS on the right of each sheet are where issuance is recorded — number, date, issuer, and the reference the CoQ gives it.</t>
         </is>
@@ -35859,12 +35894,12 @@
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="A49:C49"/>
-    <mergeCell ref="A47:C47"/>
-    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="A56:C56"/>
     <mergeCell ref="A53:C53"/>
     <mergeCell ref="A55:C55"/>
     <mergeCell ref="A50:C50"/>
-    <mergeCell ref="A48:C48"/>
+    <mergeCell ref="A57:C57"/>
     <mergeCell ref="A54:C54"/>
     <mergeCell ref="A51:C51"/>
     <mergeCell ref="A52:C52"/>

--- a/deliverables/qc_gap_analysis/PP_QC_Document_Registers_2026-08-31.xlsx
+++ b/deliverables/qc_gap_analysis/PP_QC_Document_Registers_2026-08-31.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary &amp; Notes" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'eCoA Receipt'!$A$5:$N$253</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'eCoA Receipt'!$A$5:$N$252</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'iCoA Issuance'!$A$5:$R$86</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'CoQ Issuance'!$A$5:$S$171</definedName>
   </definedNames>
@@ -594,7 +594,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N253"/>
+  <dimension ref="A1:N252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -616,14 +616,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Purely Plant GmbH — eCoA receipt register</t>
+          <t>Purely Plant GmbH — certificate receipt register</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Every certificate received from an outside laboratory, in issue-date order. Document control: what was received, from whom, when, and whether it has been checked.</t>
+          <t>Every certificate the release register cites, in issue-date order — outsourced and, where the batch has one, Purely Plant's own in-house CoA. Document control: what was received, from whom, when, and whether it has been read off its page.</t>
         </is>
       </c>
     </row>
@@ -16347,72 +16347,8 @@
         </is>
       </c>
     </row>
-    <row r="253">
-      <c r="A253" s="9" t="n">
-        <v>248</v>
-      </c>
-      <c r="B253" s="11" t="inlineStr">
-        <is>
-          <t>no date</t>
-        </is>
-      </c>
-      <c r="C253" s="11" t="inlineStr">
-        <is>
-          <t>Purely Plant GmbH (in-house)</t>
-        </is>
-      </c>
-      <c r="D253" s="11" t="inlineStr">
-        <is>
-          <t>PP CoA #033</t>
-        </is>
-      </c>
-      <c r="E253" s="11" t="inlineStr">
-        <is>
-          <t>GP092501</t>
-        </is>
-      </c>
-      <c r="F253" s="9" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="G253" s="11" t="inlineStr">
-        <is>
-          <t>Grape Pie</t>
-        </is>
-      </c>
-      <c r="H253" s="11" t="inlineStr">
-        <is>
-          <t>P060092</t>
-        </is>
-      </c>
-      <c r="I253" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J253" s="9" t="inlineStr">
-        <is>
-          <t>not verified</t>
-        </is>
-      </c>
-      <c r="K253" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L253" s="12" t="inlineStr"/>
-      <c r="M253" s="9" t="n">
-        <v>183</v>
-      </c>
-      <c r="N253" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A5:N253"/>
+  <autoFilter ref="A5:N252"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N6" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N7" r:id="rId2"/>
@@ -16661,7 +16597,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N250" r:id="rId245"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N251" r:id="rId246"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N252" r:id="rId247"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N253" r:id="rId248"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -25813,10 +25748,10 @@
         </is>
       </c>
       <c r="L46" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M46" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N46" s="5" t="n">
         <v>16</v>
@@ -28749,7 +28684,7 @@
         </is>
       </c>
       <c r="L86" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M86" s="5" t="n">
         <v>1</v>
@@ -35270,7 +35205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C58"/>
+  <dimension ref="A1:C63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -35295,15 +35230,15 @@
     <row r="4">
       <c r="A4" s="19" t="inlineStr">
         <is>
-          <t>eCoA receipt register</t>
+          <t>Certificate receipt register</t>
         </is>
       </c>
       <c r="B4" s="20" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>certificates received from outside laboratories</t>
+          <t>distinct certificates the release register cites — 15 of them Purely Plant's own in-house CoA · 1 duplicate row removed: PP CoA #033</t>
         </is>
       </c>
     </row>
@@ -35329,7 +35264,7 @@
         </is>
       </c>
       <c r="B6" s="20" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C6" s="2" t="inlineStr"/>
     </row>
@@ -35563,9 +35498,13 @@
         </is>
       </c>
       <c r="B26" s="20" t="n">
-        <v>895</v>
-      </c>
-      <c r="C26" s="2" t="inlineStr"/>
+        <v>897</v>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>conforming, findings, OOS, undetermined and blocked alike</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="21" t="inlineStr">
@@ -35656,107 +35595,95 @@
     <row r="33">
       <c r="A33" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">  out of specification</t>
+          <t xml:space="preserve">  in-house CoA only — no outsourced eCoA on file</t>
         </is>
       </c>
       <c r="B33" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="C33" s="2" t="inlineStr"/>
+        <v>17</v>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>GG1024: locate the physical certificates, scan and upload</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">  undetermined pending the QCSP 001 reading</t>
+          <t xml:space="preserve">     of the covered, out of specification</t>
         </is>
       </c>
       <c r="B34" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="C34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     of the covered, undetermined pending QCSP 001</t>
+        </is>
+      </c>
+      <c r="B35" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="C34" s="2" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="21" t="inlineStr"/>
-      <c r="B35" s="20" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="19" t="inlineStr">
-        <is>
-          <t>Determinations no laboratory has ever performed</t>
-        </is>
-      </c>
-      <c r="B36" s="20" t="inlineStr"/>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>per CoQ, over 166 CoQs</t>
-        </is>
-      </c>
+      <c r="A36" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     of the covered, a conforming laboratory finding</t>
+        </is>
+      </c>
+      <c r="B36" s="20" t="n">
+        <v>9</v>
+      </c>
+      <c r="C36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Identification A, Appearance · Macroscopic</t>
+          <t xml:space="preserve">     of the covered, declared out of specification by the laboratory</t>
         </is>
       </c>
       <c r="B37" s="20" t="n">
-        <v>153</v>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>QCSP 001 no. 1</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Identification B · Microscopic</t>
+          <t xml:space="preserve">     of the covered, batch not in the release register</t>
         </is>
       </c>
       <c r="B38" s="20" t="n">
-        <v>154</v>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>QCSP 001 no. 2</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Identification C · HPLC/HPTLC</t>
-        </is>
-      </c>
-      <c r="B39" s="20" t="n">
-        <v>165</v>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>QCSP 001 no. 3</t>
-        </is>
-      </c>
+      <c r="A39" s="21" t="inlineStr"/>
+      <c r="B39" s="20" t="inlineStr"/>
+      <c r="C39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Total CBN</t>
-        </is>
-      </c>
-      <c r="B40" s="20" t="n">
-        <v>61</v>
-      </c>
+      <c r="A40" s="19" t="inlineStr">
+        <is>
+          <t>Determinations no laboratory has ever performed</t>
+        </is>
+      </c>
+      <c r="B40" s="20" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>QCSP 001 no. 6</t>
+          <t>per CoQ, over 166 CoQs</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Foreign Matter</t>
+          <t xml:space="preserve">  Identification A, Appearance · Macroscopic</t>
         </is>
       </c>
       <c r="B41" s="20" t="n">
@@ -35764,145 +35691,213 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>QCSP 001 no. 7</t>
+          <t>QCSP 001 no. 1</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Aflatoxin B₁</t>
+          <t xml:space="preserve">  Identification B · Microscopic</t>
         </is>
       </c>
       <c r="B42" s="20" t="n">
-        <v>82</v>
+        <v>154</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>QCSP 001 no. 10.1</t>
+          <t>QCSP 001 no. 2</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="21" t="inlineStr">
         <is>
+          <t xml:space="preserve">  Identification C · HPLC/HPTLC</t>
+        </is>
+      </c>
+      <c r="B43" s="20" t="n">
+        <v>165</v>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>QCSP 001 no. 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Total CBN</t>
+        </is>
+      </c>
+      <c r="B44" s="20" t="n">
+        <v>61</v>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>QCSP 001 no. 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Foreign Matter</t>
+        </is>
+      </c>
+      <c r="B45" s="20" t="n">
+        <v>153</v>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>QCSP 001 no. 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Aflatoxin B₁</t>
+        </is>
+      </c>
+      <c r="B46" s="20" t="n">
+        <v>82</v>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>QCSP 001 no. 10.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="21" t="inlineStr">
+        <is>
           <t xml:space="preserve">  Ochratoxin A</t>
         </is>
       </c>
-      <c r="B43" s="20" t="n">
+      <c r="B47" s="20" t="n">
         <v>82</v>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
         <is>
           <t>QCSP 001 no. 10.3</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="21" t="inlineStr"/>
-      <c r="B44" s="20" t="inlineStr"/>
-      <c r="C44" s="2" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="19" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="21" t="inlineStr"/>
+      <c r="B48" s="20" t="inlineStr"/>
+      <c r="C48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="19" t="inlineStr">
         <is>
           <t>CoQs whose grade range disagrees with the QCSP 001 PDF</t>
         </is>
       </c>
-      <c r="B45" s="20" t="n">
+      <c r="B49" s="20" t="n">
         <v>54</v>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>two owner documents, two grade designs — recorded, not resolved</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="22" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="22" t="inlineStr">
         <is>
           <t>NOTES</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="14" customHeight="1">
-      <c r="A49" s="23" t="inlineStr">
+    <row r="53" ht="14" customHeight="1">
+      <c r="A53" s="23" t="inlineStr">
         <is>
           <t>THE CULTIVATION-BATCH / PACKAGED-LOT LINKAGE, and why the CoQ total depends on it.</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="48" customHeight="1">
-      <c r="A50" s="23" t="inlineStr">
+    <row r="54" ht="48" customHeight="1">
+      <c r="A54" s="23" t="inlineStr">
         <is>
           <t>PP_Potency_MASTER_Spec.xlsx carries a column the release register does not: Cultiv. Batch No. beside PP Batch No. Seven register entries named by a P-number are packaged lots, and for four of them the cultivation batch is a separate register entry of its own: P060152 (ref 72) from J31102501 (ref 43); P060212 (73) from JD112501 (58); P060242 (74) from OPM122501 (51); P060402 (78) from GG012603 (62).</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="48" customHeight="1">
-      <c r="A51" s="23" t="inlineStr">
-        <is>
-          <t>That is what those seven were. They carry only the Farmahem 197-series because that is the analysis performed at packaging; their earlier testing sits under the cultivation batch's own entry. Two more — P060352 from FB012602, P060382 from SCR012603 — are packaged lots whose cultivation batch is not in the release register at all. P060332 appears in neither document.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="48" customHeight="1">
-      <c r="A52" s="23" t="inlineStr">
-        <is>
-          <t>So for four batches the register counts the same material twice, and the CoQ total turns on whether a CoQ is issued per cultivation batch or per released lot. 102 is the count on the register's own numbering; issuing one CoQ per released material instead would remove four. That is a QC decision and is not made here — the linkage is carried on every sheet so the question is visible wherever a count is read.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="24" t="inlineStr"/>
-    </row>
-    <row r="54" ht="60" customHeight="1">
-      <c r="A54" s="23" t="inlineStr">
-        <is>
-          <t>WHY THE iCoA SHEET STILL LISTS 81 WHILE THE ISSUE_COQ PLAN CARRIES 61 CoQ DOCUMENTS. The 81 rows predate the plan and are kept as the per-cultivation-batch view; the plan's iCoA-PP-YYYY-NNNN references and the routing decision of 31.08.2026 are on the CoQ sheets and in PP_CoQ_Parameter_Schedule_2026-08-31.xlsx. Identity and foreign matter are properties of the material, determined once. A CoQ reissued because the cannabinoids and mycotoxins were re-analysed covers the same batch, so it references the iCoA already issued.</t>
         </is>
       </c>
     </row>
     <row r="55" ht="48" customHeight="1">
       <c r="A55" s="23" t="inlineStr">
         <is>
+          <t>That is what those seven were. They carry only the Farmahem 197-series because that is the analysis performed at packaging; their earlier testing sits under the cultivation batch's own entry. Two more — P060352 from FB012602, P060382 from SCR012603 — are packaged lots whose cultivation batch is not in the release register at all. P060332 appears in neither document.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="60" customHeight="1">
+      <c r="A56" s="23" t="inlineStr">
+        <is>
+          <t>So for four batches the register counts the same material twice. THAT QUESTION IS NOW SETTLED: the owner's ruling of 31.08.2026 issues one CoQ per released material, and the six P-number blocks fold into their cultivation batch rather than standing as batches of their own. The CoQ sheet counts 166 documents on that basis — one initial per batch on record and one 12-month reissue per batch. The linkage is still carried on every sheet, because the register itself has not been renumbered.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="24" t="inlineStr"/>
+    </row>
+    <row r="58" ht="60" customHeight="1">
+      <c r="A58" s="23" t="inlineStr">
+        <is>
+          <t>WHY THIS SHEET STILL LISTS 81 ROWS WHILE THE ROUTING REQUIRES 224 IN-HOUSE CERTIFICATES. The 81 rows predate the plan and are kept as the per-register-entry view — and six of them (P060152, P060212, P060242, P060352, P060382, P060402) are the Farmahem re-analysis rows of plan lots, so 81 rows are not 81 materials. What the routing actually requires is on the CoQ sheets and in PP_CoQ_Parameter_Schedule_2026-08-31.xlsx: 71 Ident A + B certificates and 153 foreign-matter certificates, 224 in all.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="72" customHeight="1">
+      <c r="A59" s="23" t="inlineStr">
+        <is>
+          <t>AN EARLIER NOTE HERE SAID THE OPPOSITE AND IS WITHDRAWN. It read: "Identity and foreign matter are properties of the material, determined once. A CoQ reissued because the cannabinoids and mycotoxins were re-analysed covers the same batch, so it references the iCoA already issued." The owner's routing of 31.08.2026 rules otherwise: at a 12-month reissue Farmahem performs identity together with the assay, and Purely Plant's laboratory issues a fresh foreign-matter iCoA. A certificate from the release round cannot stand behind a determination on a document dated a year later — the same rule that stops an initial CoQ citing the 197-series re-analysis, running the other way.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="48" customHeight="1">
+      <c r="A60" s="23" t="inlineStr">
+        <is>
           <t>WHERE THE SCOPE SPLIT COMES FROM. CNP changed its certificate form in mid-2026: the older DAB form reports loss on drying and cannabinoids only; the Ph. Eur. 11.5 form adds identification (macroscopy and microscopy) and foreign matter. Twelve certificates are on the newer form — ППК26110-26119, ППК26127, ППК26128 — and all 73 CNP certificates were read off their own pages on 31.08.2026, so this is not inferred from a filename or a parse.</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="36" customHeight="1">
-      <c r="A56" s="23" t="inlineStr">
+    <row r="61" ht="36" customHeight="1">
+      <c r="A61" s="23" t="inlineStr">
         <is>
           <t>IDENTIFICATION C is on every iCoA because no laboratory has ever performed it. Those twelve Ph. Eur. pages print Идентификација — Макроскопија, Микроскопија and stop. It is discharged in-house by risk analysis with scientific justification, from the HPLC assay.</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="36" customHeight="1">
-      <c r="A57" s="23" t="inlineStr">
+    <row r="62" ht="36" customHeight="1">
+      <c r="A62" s="23" t="inlineStr">
         <is>
           <t>FB032601 needs Ident C only, like its eleven siblings, and its CoQ still cannot be issued: the foreign matter CNP does cover reads 0.08 % against a 2.00 % maximum and is marked Не одговара, cannabis seed present. A blocker, not a gap.</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="24" customHeight="1">
-      <c r="A58" s="23" t="inlineStr">
+    <row r="63" ht="24" customHeight="1">
+      <c r="A63" s="23" t="inlineStr">
         <is>
           <t>THE BLANK COLUMNS on the right of each sheet are where issuance is recorded — number, date, issuer, and the reference the CoQ gives it.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A49:C49"/>
+  <mergeCells count="11">
+    <mergeCell ref="A60:C60"/>
+    <mergeCell ref="A63:C63"/>
+    <mergeCell ref="A61:C61"/>
     <mergeCell ref="A58:C58"/>
     <mergeCell ref="A56:C56"/>
+    <mergeCell ref="A62:C62"/>
     <mergeCell ref="A53:C53"/>
     <mergeCell ref="A55:C55"/>
-    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="A59:C59"/>
     <mergeCell ref="A57:C57"/>
     <mergeCell ref="A54:C54"/>
-    <mergeCell ref="A51:C51"/>
-    <mergeCell ref="A52:C52"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/deliverables/qc_gap_analysis/PP_QC_Document_Registers_2026-08-31.xlsx
+++ b/deliverables/qc_gap_analysis/PP_QC_Document_Registers_2026-08-31.xlsx
@@ -22247,7 +22247,7 @@
       <c r="B5" s="4" t="inlineStr"/>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>no earlier than — set at issue</t>
+          <t>set on the day of issue — no earlier than shown, never post-dated</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr"/>

--- a/deliverables/qc_gap_analysis/PP_QC_Document_Registers_2026-08-31.xlsx
+++ b/deliverables/qc_gap_analysis/PP_QC_Document_Registers_2026-08-31.xlsx
@@ -2031,9 +2031,9 @@
           <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB CFU/g, Salmonella /25 g, E. coli /1 g</t>
         </is>
       </c>
-      <c r="J26" s="9" t="inlineStr">
-        <is>
-          <t>not verified</t>
+      <c r="J26" s="8" t="inlineStr">
+        <is>
+          <t>iph_physchem</t>
         </is>
       </c>
       <c r="K26" s="9" t="inlineStr">
@@ -6447,9 +6447,9 @@
           <t>Aflatoxins Σ µg/kg, Aflatoxin B1 µg/kg, Ochratoxin A µg/kg</t>
         </is>
       </c>
-      <c r="J95" s="9" t="inlineStr">
-        <is>
-          <t>not verified</t>
+      <c r="J95" s="8" t="inlineStr">
+        <is>
+          <t>farmahem</t>
         </is>
       </c>
       <c r="K95" s="9" t="inlineStr">
@@ -10091,9 +10091,9 @@
           <t>Loss on drying %</t>
         </is>
       </c>
-      <c r="J152" s="9" t="inlineStr">
-        <is>
-          <t>not verified</t>
+      <c r="J152" s="8" t="inlineStr">
+        <is>
+          <t>farmahem</t>
         </is>
       </c>
       <c r="K152" s="9" t="inlineStr">
@@ -10151,9 +10151,9 @@
           <t>Loss on drying %</t>
         </is>
       </c>
-      <c r="J153" s="9" t="inlineStr">
-        <is>
-          <t>not verified</t>
+      <c r="J153" s="8" t="inlineStr">
+        <is>
+          <t>farmahem</t>
         </is>
       </c>
       <c r="K153" s="9" t="inlineStr">
@@ -10211,9 +10211,9 @@
           <t>Loss on drying %</t>
         </is>
       </c>
-      <c r="J154" s="9" t="inlineStr">
-        <is>
-          <t>not verified</t>
+      <c r="J154" s="8" t="inlineStr">
+        <is>
+          <t>farmahem</t>
         </is>
       </c>
       <c r="K154" s="9" t="inlineStr">
@@ -10271,9 +10271,9 @@
           <t>Loss on drying %</t>
         </is>
       </c>
-      <c r="J155" s="9" t="inlineStr">
-        <is>
-          <t>not verified</t>
+      <c r="J155" s="8" t="inlineStr">
+        <is>
+          <t>farmahem</t>
         </is>
       </c>
       <c r="K155" s="9" t="inlineStr">
@@ -10331,9 +10331,9 @@
           <t>Loss on drying %</t>
         </is>
       </c>
-      <c r="J156" s="9" t="inlineStr">
-        <is>
-          <t>not verified</t>
+      <c r="J156" s="8" t="inlineStr">
+        <is>
+          <t>farmahem</t>
         </is>
       </c>
       <c r="K156" s="9" t="inlineStr">
@@ -10391,9 +10391,9 @@
           <t>Loss on drying %</t>
         </is>
       </c>
-      <c r="J157" s="9" t="inlineStr">
-        <is>
-          <t>not verified</t>
+      <c r="J157" s="8" t="inlineStr">
+        <is>
+          <t>farmahem</t>
         </is>
       </c>
       <c r="K157" s="9" t="inlineStr">
@@ -11315,9 +11315,9 @@
           <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB CFU/g, Salmonella /25 g, E. coli /1 g</t>
         </is>
       </c>
-      <c r="J172" s="9" t="inlineStr">
-        <is>
-          <t>not verified</t>
+      <c r="J172" s="8" t="inlineStr">
+        <is>
+          <t>residual</t>
         </is>
       </c>
       <c r="K172" s="9" t="inlineStr">
@@ -11375,9 +11375,9 @@
           <t>TAMC CFU/g, TYMC CFU/g, Bile-tolerant GNB CFU/g, Salmonella /25 g, E. coli /1 g</t>
         </is>
       </c>
-      <c r="J173" s="9" t="inlineStr">
-        <is>
-          <t>not verified</t>
+      <c r="J173" s="8" t="inlineStr">
+        <is>
+          <t>residual</t>
         </is>
       </c>
       <c r="K173" s="9" t="inlineStr">
@@ -11495,9 +11495,9 @@
           <t>Loss on drying %</t>
         </is>
       </c>
-      <c r="J175" s="9" t="inlineStr">
-        <is>
-          <t>not verified</t>
+      <c r="J175" s="8" t="inlineStr">
+        <is>
+          <t>farmahem</t>
         </is>
       </c>
       <c r="K175" s="9" t="inlineStr">
@@ -11615,9 +11615,9 @@
           <t>THC %, CBD %, CBN %</t>
         </is>
       </c>
-      <c r="J177" s="9" t="inlineStr">
-        <is>
-          <t>not verified</t>
+      <c r="J177" s="8" t="inlineStr">
+        <is>
+          <t>farmahem</t>
         </is>
       </c>
       <c r="K177" s="9" t="inlineStr">
@@ -11675,9 +11675,9 @@
           <t>Loss on drying %</t>
         </is>
       </c>
-      <c r="J178" s="9" t="inlineStr">
-        <is>
-          <t>not verified</t>
+      <c r="J178" s="8" t="inlineStr">
+        <is>
+          <t>farmahem</t>
         </is>
       </c>
       <c r="K178" s="14" t="inlineStr">
@@ -11735,9 +11735,9 @@
           <t>THC %, CBD %, CBN %</t>
         </is>
       </c>
-      <c r="J179" s="9" t="inlineStr">
-        <is>
-          <t>not verified</t>
+      <c r="J179" s="8" t="inlineStr">
+        <is>
+          <t>farmahem</t>
         </is>
       </c>
       <c r="K179" s="9" t="inlineStr">
@@ -11795,9 +11795,9 @@
           <t>Loss on drying %</t>
         </is>
       </c>
-      <c r="J180" s="9" t="inlineStr">
-        <is>
-          <t>not verified</t>
+      <c r="J180" s="8" t="inlineStr">
+        <is>
+          <t>farmahem</t>
         </is>
       </c>
       <c r="K180" s="14" t="inlineStr">
@@ -11855,9 +11855,9 @@
           <t>THC %, CBD %, CBN %</t>
         </is>
       </c>
-      <c r="J181" s="9" t="inlineStr">
-        <is>
-          <t>not verified</t>
+      <c r="J181" s="8" t="inlineStr">
+        <is>
+          <t>farmahem</t>
         </is>
       </c>
       <c r="K181" s="9" t="inlineStr">
@@ -11915,9 +11915,9 @@
           <t>Loss on drying %</t>
         </is>
       </c>
-      <c r="J182" s="9" t="inlineStr">
-        <is>
-          <t>not verified</t>
+      <c r="J182" s="8" t="inlineStr">
+        <is>
+          <t>farmahem</t>
         </is>
       </c>
       <c r="K182" s="9" t="inlineStr">
@@ -13683,9 +13683,9 @@
           <t>THC %, THC spec, CBD %, CBN %</t>
         </is>
       </c>
-      <c r="J211" s="9" t="inlineStr">
-        <is>
-          <t>not verified</t>
+      <c r="J211" s="8" t="inlineStr">
+        <is>
+          <t>farmahem</t>
         </is>
       </c>
       <c r="K211" s="9" t="inlineStr">
@@ -13743,9 +13743,9 @@
           <t>THC %, THC spec, CBD %, CBN %</t>
         </is>
       </c>
-      <c r="J212" s="9" t="inlineStr">
-        <is>
-          <t>not verified</t>
+      <c r="J212" s="8" t="inlineStr">
+        <is>
+          <t>farmahem</t>
         </is>
       </c>
       <c r="K212" s="9" t="inlineStr">
@@ -13807,9 +13807,9 @@
           <t>THC %, THC spec, CBD %, CBN %</t>
         </is>
       </c>
-      <c r="J213" s="9" t="inlineStr">
-        <is>
-          <t>not verified</t>
+      <c r="J213" s="8" t="inlineStr">
+        <is>
+          <t>farmahem</t>
         </is>
       </c>
       <c r="K213" s="9" t="inlineStr">
@@ -13871,9 +13871,9 @@
           <t>THC %, THC spec, CBD %, CBN %</t>
         </is>
       </c>
-      <c r="J214" s="9" t="inlineStr">
-        <is>
-          <t>not verified</t>
+      <c r="J214" s="8" t="inlineStr">
+        <is>
+          <t>farmahem</t>
         </is>
       </c>
       <c r="K214" s="9" t="inlineStr">
@@ -13935,9 +13935,9 @@
           <t>THC %, THC spec, CBD %, CBN %</t>
         </is>
       </c>
-      <c r="J215" s="9" t="inlineStr">
-        <is>
-          <t>not verified</t>
+      <c r="J215" s="8" t="inlineStr">
+        <is>
+          <t>farmahem</t>
         </is>
       </c>
       <c r="K215" s="9" t="inlineStr">
@@ -13999,9 +13999,9 @@
           <t>THC %, THC spec, CBD %, CBN %</t>
         </is>
       </c>
-      <c r="J216" s="9" t="inlineStr">
-        <is>
-          <t>not verified</t>
+      <c r="J216" s="8" t="inlineStr">
+        <is>
+          <t>farmahem</t>
         </is>
       </c>
       <c r="K216" s="9" t="inlineStr">
@@ -14063,9 +14063,9 @@
           <t>THC %, THC spec, CBD %, CBN %</t>
         </is>
       </c>
-      <c r="J217" s="9" t="inlineStr">
-        <is>
-          <t>not verified</t>
+      <c r="J217" s="8" t="inlineStr">
+        <is>
+          <t>farmahem</t>
         </is>
       </c>
       <c r="K217" s="9" t="inlineStr">
@@ -14127,9 +14127,9 @@
           <t>THC %, THC spec, CBD %, CBN %</t>
         </is>
       </c>
-      <c r="J218" s="9" t="inlineStr">
-        <is>
-          <t>not verified</t>
+      <c r="J218" s="8" t="inlineStr">
+        <is>
+          <t>farmahem</t>
         </is>
       </c>
       <c r="K218" s="9" t="inlineStr">
@@ -14191,9 +14191,9 @@
           <t>THC %, THC spec, CBD %, CBN %</t>
         </is>
       </c>
-      <c r="J219" s="9" t="inlineStr">
-        <is>
-          <t>not verified</t>
+      <c r="J219" s="8" t="inlineStr">
+        <is>
+          <t>farmahem</t>
         </is>
       </c>
       <c r="K219" s="9" t="inlineStr">
@@ -14255,9 +14255,9 @@
           <t>THC %, THC spec, CBD %, CBN %</t>
         </is>
       </c>
-      <c r="J220" s="9" t="inlineStr">
-        <is>
-          <t>not verified</t>
+      <c r="J220" s="8" t="inlineStr">
+        <is>
+          <t>farmahem</t>
         </is>
       </c>
       <c r="K220" s="9" t="inlineStr">
@@ -14319,9 +14319,9 @@
           <t>THC %, THC spec, CBD %, CBN %</t>
         </is>
       </c>
-      <c r="J221" s="9" t="inlineStr">
-        <is>
-          <t>not verified</t>
+      <c r="J221" s="8" t="inlineStr">
+        <is>
+          <t>farmahem</t>
         </is>
       </c>
       <c r="K221" s="9" t="inlineStr">
@@ -14383,9 +14383,9 @@
           <t>THC %, THC spec, CBD %, CBN %</t>
         </is>
       </c>
-      <c r="J222" s="9" t="inlineStr">
-        <is>
-          <t>not verified</t>
+      <c r="J222" s="8" t="inlineStr">
+        <is>
+          <t>farmahem</t>
         </is>
       </c>
       <c r="K222" s="9" t="inlineStr">
@@ -14447,9 +14447,9 @@
           <t>THC %, THC spec, CBD %, CBN %</t>
         </is>
       </c>
-      <c r="J223" s="9" t="inlineStr">
-        <is>
-          <t>not verified</t>
+      <c r="J223" s="8" t="inlineStr">
+        <is>
+          <t>farmahem</t>
         </is>
       </c>
       <c r="K223" s="9" t="inlineStr">
@@ -14515,9 +14515,9 @@
           <t>THC %, THC spec, CBD %, CBN %</t>
         </is>
       </c>
-      <c r="J224" s="9" t="inlineStr">
-        <is>
-          <t>not verified</t>
+      <c r="J224" s="8" t="inlineStr">
+        <is>
+          <t>farmahem</t>
         </is>
       </c>
       <c r="K224" s="9" t="inlineStr">
@@ -14583,9 +14583,9 @@
           <t>THC %, THC spec, CBD %, CBN %</t>
         </is>
       </c>
-      <c r="J225" s="9" t="inlineStr">
-        <is>
-          <t>not verified</t>
+      <c r="J225" s="8" t="inlineStr">
+        <is>
+          <t>farmahem</t>
         </is>
       </c>
       <c r="K225" s="9" t="inlineStr">
@@ -14651,14 +14651,14 @@
           <t>THC %, THC spec, CBD %, CBN %</t>
         </is>
       </c>
-      <c r="J226" s="9" t="inlineStr">
-        <is>
-          <t>not verified</t>
-        </is>
-      </c>
-      <c r="K226" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="J226" s="8" t="inlineStr">
+        <is>
+          <t>farmahem</t>
+        </is>
+      </c>
+      <c r="K226" s="14" t="inlineStr">
+        <is>
+          <t>amber</t>
         </is>
       </c>
       <c r="L226" s="7" t="inlineStr"/>
@@ -14715,9 +14715,9 @@
           <t>THC %, THC spec, CBD %, CBN %</t>
         </is>
       </c>
-      <c r="J227" s="9" t="inlineStr">
-        <is>
-          <t>not verified</t>
+      <c r="J227" s="8" t="inlineStr">
+        <is>
+          <t>farmahem</t>
         </is>
       </c>
       <c r="K227" s="14" t="inlineStr">
@@ -14783,9 +14783,9 @@
           <t>THC %, THC spec, CBD %, CBN %</t>
         </is>
       </c>
-      <c r="J228" s="9" t="inlineStr">
-        <is>
-          <t>not verified</t>
+      <c r="J228" s="8" t="inlineStr">
+        <is>
+          <t>farmahem</t>
         </is>
       </c>
       <c r="K228" s="9" t="inlineStr">
@@ -14851,9 +14851,9 @@
           <t>THC %, THC spec, CBD %, CBN %</t>
         </is>
       </c>
-      <c r="J229" s="9" t="inlineStr">
-        <is>
-          <t>not verified</t>
+      <c r="J229" s="8" t="inlineStr">
+        <is>
+          <t>farmahem</t>
         </is>
       </c>
       <c r="K229" s="9" t="inlineStr">
@@ -14915,9 +14915,9 @@
           <t>THC %, THC spec, CBD %, CBN %</t>
         </is>
       </c>
-      <c r="J230" s="9" t="inlineStr">
-        <is>
-          <t>not verified</t>
+      <c r="J230" s="8" t="inlineStr">
+        <is>
+          <t>farmahem</t>
         </is>
       </c>
       <c r="K230" s="9" t="inlineStr">
@@ -14975,9 +14975,9 @@
           <t>THC %, THC spec, CBD %, CBN %</t>
         </is>
       </c>
-      <c r="J231" s="9" t="inlineStr">
-        <is>
-          <t>not verified</t>
+      <c r="J231" s="8" t="inlineStr">
+        <is>
+          <t>farmahem</t>
         </is>
       </c>
       <c r="K231" s="9" t="inlineStr">
@@ -15035,9 +15035,9 @@
           <t>Aflatoxins Σ µg/kg, Aflatoxin B1 µg/kg, Ochratoxin A µg/kg</t>
         </is>
       </c>
-      <c r="J232" s="9" t="inlineStr">
-        <is>
-          <t>not verified</t>
+      <c r="J232" s="8" t="inlineStr">
+        <is>
+          <t>farmahem</t>
         </is>
       </c>
       <c r="K232" s="9" t="inlineStr">
@@ -15095,9 +15095,9 @@
           <t>Aflatoxins Σ µg/kg, Aflatoxin B1 µg/kg, Ochratoxin A µg/kg</t>
         </is>
       </c>
-      <c r="J233" s="9" t="inlineStr">
-        <is>
-          <t>not verified</t>
+      <c r="J233" s="8" t="inlineStr">
+        <is>
+          <t>farmahem</t>
         </is>
       </c>
       <c r="K233" s="9" t="inlineStr">
@@ -15159,9 +15159,9 @@
           <t>Aflatoxins Σ µg/kg, Aflatoxin B1 µg/kg, Ochratoxin A µg/kg</t>
         </is>
       </c>
-      <c r="J234" s="9" t="inlineStr">
-        <is>
-          <t>not verified</t>
+      <c r="J234" s="8" t="inlineStr">
+        <is>
+          <t>farmahem</t>
         </is>
       </c>
       <c r="K234" s="9" t="inlineStr">
@@ -15223,9 +15223,9 @@
           <t>Aflatoxins Σ µg/kg, Aflatoxin B1 µg/kg, Ochratoxin A µg/kg</t>
         </is>
       </c>
-      <c r="J235" s="9" t="inlineStr">
-        <is>
-          <t>not verified</t>
+      <c r="J235" s="8" t="inlineStr">
+        <is>
+          <t>farmahem</t>
         </is>
       </c>
       <c r="K235" s="14" t="inlineStr">
@@ -15287,9 +15287,9 @@
           <t>Aflatoxins Σ µg/kg, Aflatoxin B1 µg/kg, Ochratoxin A µg/kg</t>
         </is>
       </c>
-      <c r="J236" s="9" t="inlineStr">
-        <is>
-          <t>not verified</t>
+      <c r="J236" s="8" t="inlineStr">
+        <is>
+          <t>farmahem</t>
         </is>
       </c>
       <c r="K236" s="9" t="inlineStr">
@@ -15351,9 +15351,9 @@
           <t>Aflatoxins Σ µg/kg, Aflatoxin B1 µg/kg, Ochratoxin A µg/kg</t>
         </is>
       </c>
-      <c r="J237" s="9" t="inlineStr">
-        <is>
-          <t>not verified</t>
+      <c r="J237" s="8" t="inlineStr">
+        <is>
+          <t>farmahem</t>
         </is>
       </c>
       <c r="K237" s="9" t="inlineStr">
@@ -15415,9 +15415,9 @@
           <t>Aflatoxins Σ µg/kg, Aflatoxin B1 µg/kg, Ochratoxin A µg/kg</t>
         </is>
       </c>
-      <c r="J238" s="9" t="inlineStr">
-        <is>
-          <t>not verified</t>
+      <c r="J238" s="8" t="inlineStr">
+        <is>
+          <t>farmahem</t>
         </is>
       </c>
       <c r="K238" s="9" t="inlineStr">
@@ -15479,9 +15479,9 @@
           <t>Aflatoxins Σ µg/kg, Aflatoxin B1 µg/kg, Ochratoxin A µg/kg</t>
         </is>
       </c>
-      <c r="J239" s="9" t="inlineStr">
-        <is>
-          <t>not verified</t>
+      <c r="J239" s="8" t="inlineStr">
+        <is>
+          <t>farmahem</t>
         </is>
       </c>
       <c r="K239" s="9" t="inlineStr">
@@ -15543,9 +15543,9 @@
           <t>Aflatoxins Σ µg/kg, Aflatoxin B1 µg/kg, Ochratoxin A µg/kg</t>
         </is>
       </c>
-      <c r="J240" s="9" t="inlineStr">
-        <is>
-          <t>not verified</t>
+      <c r="J240" s="8" t="inlineStr">
+        <is>
+          <t>farmahem</t>
         </is>
       </c>
       <c r="K240" s="9" t="inlineStr">
@@ -15607,9 +15607,9 @@
           <t>Aflatoxins Σ µg/kg, Aflatoxin B1 µg/kg, Ochratoxin A µg/kg</t>
         </is>
       </c>
-      <c r="J241" s="9" t="inlineStr">
-        <is>
-          <t>not verified</t>
+      <c r="J241" s="8" t="inlineStr">
+        <is>
+          <t>farmahem</t>
         </is>
       </c>
       <c r="K241" s="9" t="inlineStr">
@@ -15671,9 +15671,9 @@
           <t>Aflatoxins Σ µg/kg, Aflatoxin B1 µg/kg, Ochratoxin A µg/kg</t>
         </is>
       </c>
-      <c r="J242" s="9" t="inlineStr">
-        <is>
-          <t>not verified</t>
+      <c r="J242" s="8" t="inlineStr">
+        <is>
+          <t>farmahem</t>
         </is>
       </c>
       <c r="K242" s="9" t="inlineStr">
@@ -15735,9 +15735,9 @@
           <t>Aflatoxins Σ µg/kg, Aflatoxin B1 µg/kg, Ochratoxin A µg/kg</t>
         </is>
       </c>
-      <c r="J243" s="9" t="inlineStr">
-        <is>
-          <t>not verified</t>
+      <c r="J243" s="8" t="inlineStr">
+        <is>
+          <t>farmahem</t>
         </is>
       </c>
       <c r="K243" s="9" t="inlineStr">
@@ -15799,9 +15799,9 @@
           <t>Aflatoxins Σ µg/kg, Aflatoxin B1 µg/kg, Ochratoxin A µg/kg</t>
         </is>
       </c>
-      <c r="J244" s="9" t="inlineStr">
-        <is>
-          <t>not verified</t>
+      <c r="J244" s="8" t="inlineStr">
+        <is>
+          <t>farmahem</t>
         </is>
       </c>
       <c r="K244" s="9" t="inlineStr">
@@ -15867,9 +15867,9 @@
           <t>Aflatoxins Σ µg/kg, Aflatoxin B1 µg/kg, Ochratoxin A µg/kg</t>
         </is>
       </c>
-      <c r="J245" s="9" t="inlineStr">
-        <is>
-          <t>not verified</t>
+      <c r="J245" s="8" t="inlineStr">
+        <is>
+          <t>farmahem</t>
         </is>
       </c>
       <c r="K245" s="9" t="inlineStr">
@@ -15935,9 +15935,9 @@
           <t>Aflatoxins Σ µg/kg, Aflatoxin B1 µg/kg, Ochratoxin A µg/kg</t>
         </is>
       </c>
-      <c r="J246" s="9" t="inlineStr">
-        <is>
-          <t>not verified</t>
+      <c r="J246" s="8" t="inlineStr">
+        <is>
+          <t>farmahem</t>
         </is>
       </c>
       <c r="K246" s="9" t="inlineStr">
@@ -16003,9 +16003,9 @@
           <t>Aflatoxins Σ µg/kg, Aflatoxin B1 µg/kg, Ochratoxin A µg/kg</t>
         </is>
       </c>
-      <c r="J247" s="9" t="inlineStr">
-        <is>
-          <t>not verified</t>
+      <c r="J247" s="8" t="inlineStr">
+        <is>
+          <t>farmahem</t>
         </is>
       </c>
       <c r="K247" s="9" t="inlineStr">
@@ -16067,9 +16067,9 @@
           <t>Aflatoxins Σ µg/kg, Aflatoxin B1 µg/kg, Ochratoxin A µg/kg</t>
         </is>
       </c>
-      <c r="J248" s="9" t="inlineStr">
-        <is>
-          <t>not verified</t>
+      <c r="J248" s="8" t="inlineStr">
+        <is>
+          <t>farmahem</t>
         </is>
       </c>
       <c r="K248" s="9" t="inlineStr">
@@ -16135,9 +16135,9 @@
           <t>Aflatoxins Σ µg/kg, Aflatoxin B1 µg/kg, Ochratoxin A µg/kg</t>
         </is>
       </c>
-      <c r="J249" s="9" t="inlineStr">
-        <is>
-          <t>not verified</t>
+      <c r="J249" s="8" t="inlineStr">
+        <is>
+          <t>farmahem</t>
         </is>
       </c>
       <c r="K249" s="9" t="inlineStr">
@@ -16203,9 +16203,9 @@
           <t>Aflatoxins Σ µg/kg, Aflatoxin B1 µg/kg, Ochratoxin A µg/kg</t>
         </is>
       </c>
-      <c r="J250" s="9" t="inlineStr">
-        <is>
-          <t>not verified</t>
+      <c r="J250" s="8" t="inlineStr">
+        <is>
+          <t>farmahem</t>
         </is>
       </c>
       <c r="K250" s="9" t="inlineStr">
@@ -16267,9 +16267,9 @@
           <t>Aflatoxins Σ µg/kg, Aflatoxin B1 µg/kg, Ochratoxin A µg/kg</t>
         </is>
       </c>
-      <c r="J251" s="9" t="inlineStr">
-        <is>
-          <t>not verified</t>
+      <c r="J251" s="8" t="inlineStr">
+        <is>
+          <t>farmahem</t>
         </is>
       </c>
       <c r="K251" s="9" t="inlineStr">
@@ -16327,9 +16327,9 @@
           <t>Aflatoxins Σ µg/kg, Aflatoxin B1 µg/kg, Ochratoxin A µg/kg</t>
         </is>
       </c>
-      <c r="J252" s="9" t="inlineStr">
-        <is>
-          <t>not verified</t>
+      <c r="J252" s="8" t="inlineStr">
+        <is>
+          <t>farmahem</t>
         </is>
       </c>
       <c r="K252" s="9" t="inlineStr">
@@ -35249,7 +35249,7 @@
         </is>
       </c>
       <c r="B5" s="20" t="n">
-        <v>173</v>
+        <v>94</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>

--- a/deliverables/qc_gap_analysis/PP_QC_Document_Registers_2026-08-31.xlsx
+++ b/deliverables/qc_gap_analysis/PP_QC_Document_Registers_2026-08-31.xlsx
@@ -12948,7 +12948,7 @@
       <c r="H199" s="11" t="inlineStr"/>
       <c r="I199" s="12" t="inlineStr">
         <is>
-          <t>THC %, THC spec, CBD %, CBN %, Loss on drying %</t>
+          <t>THC %, THC spec, CBD %, CBN %, Loss on drying %, Ident A + B, Foreign matter</t>
         </is>
       </c>
       <c r="J199" s="8" t="inlineStr">
@@ -13008,7 +13008,7 @@
       <c r="H200" s="6" t="inlineStr"/>
       <c r="I200" s="7" t="inlineStr">
         <is>
-          <t>THC %, THC spec, CBD %, CBN %, Loss on drying %</t>
+          <t>THC %, THC spec, CBD %, CBN %, Loss on drying %, Ident A + B, Foreign matter</t>
         </is>
       </c>
       <c r="J200" s="8" t="inlineStr">
@@ -13068,7 +13068,7 @@
       <c r="H201" s="11" t="inlineStr"/>
       <c r="I201" s="12" t="inlineStr">
         <is>
-          <t>THC %, THC spec, CBD %, CBN %, Loss on drying %</t>
+          <t>THC %, THC spec, CBD %, CBN %, Loss on drying %, Ident A + B, Foreign matter</t>
         </is>
       </c>
       <c r="J201" s="8" t="inlineStr">
@@ -13128,7 +13128,7 @@
       <c r="H202" s="6" t="inlineStr"/>
       <c r="I202" s="7" t="inlineStr">
         <is>
-          <t>THC %, THC spec, CBD %, CBN %, Loss on drying %</t>
+          <t>THC %, THC spec, CBD %, CBN %, Loss on drying %, Ident A + B, Foreign matter</t>
         </is>
       </c>
       <c r="J202" s="8" t="inlineStr">
@@ -13188,7 +13188,7 @@
       <c r="H203" s="11" t="inlineStr"/>
       <c r="I203" s="12" t="inlineStr">
         <is>
-          <t>THC %, THC spec, CBD %, CBN %, Loss on drying %</t>
+          <t>THC %, THC spec, CBD %, CBN %, Loss on drying %, Ident A + B, Foreign matter</t>
         </is>
       </c>
       <c r="J203" s="8" t="inlineStr">
@@ -13248,7 +13248,7 @@
       <c r="H204" s="6" t="inlineStr"/>
       <c r="I204" s="7" t="inlineStr">
         <is>
-          <t>THC %, THC spec, CBD %, CBN %, Loss on drying %</t>
+          <t>THC %, THC spec, CBD %, CBN %, Loss on drying %, Ident A + B, Foreign matter</t>
         </is>
       </c>
       <c r="J204" s="8" t="inlineStr">
@@ -13312,7 +13312,7 @@
       </c>
       <c r="I205" s="12" t="inlineStr">
         <is>
-          <t>THC %, THC spec, CBD %, CBN %, Loss on drying %</t>
+          <t>THC %, THC spec, CBD %, CBN %, Loss on drying %, Ident A + B, Foreign matter</t>
         </is>
       </c>
       <c r="J205" s="8" t="inlineStr">
@@ -13376,7 +13376,7 @@
       </c>
       <c r="I206" s="7" t="inlineStr">
         <is>
-          <t>THC %, THC spec, CBD %, CBN %, Loss on drying %</t>
+          <t>THC %, THC spec, CBD %, CBN %, Loss on drying %, Ident A + B, Foreign matter</t>
         </is>
       </c>
       <c r="J206" s="8" t="inlineStr">
@@ -13440,7 +13440,7 @@
       </c>
       <c r="I207" s="12" t="inlineStr">
         <is>
-          <t>THC %, THC spec, CBD %, CBN %, Loss on drying %</t>
+          <t>THC %, THC spec, CBD %, CBN %, Loss on drying %, Ident A + B, Foreign matter</t>
         </is>
       </c>
       <c r="J207" s="8" t="inlineStr">
@@ -13500,7 +13500,7 @@
       <c r="H208" s="6" t="inlineStr"/>
       <c r="I208" s="7" t="inlineStr">
         <is>
-          <t>THC %, THC spec, CBD %, CBN %, Loss on drying %</t>
+          <t>THC %, THC spec, CBD %, CBN %, Loss on drying %, Ident A + B, Foreign matter</t>
         </is>
       </c>
       <c r="J208" s="8" t="inlineStr">
@@ -13560,7 +13560,7 @@
       <c r="H209" s="11" t="inlineStr"/>
       <c r="I209" s="12" t="inlineStr">
         <is>
-          <t>THC %, THC spec, CBD %, CBN %, Loss on drying %</t>
+          <t>THC %, THC spec, CBD %, CBN %, Loss on drying %, Ident A + B, Foreign matter</t>
         </is>
       </c>
       <c r="J209" s="8" t="inlineStr">
@@ -13620,7 +13620,7 @@
       <c r="H210" s="6" t="inlineStr"/>
       <c r="I210" s="7" t="inlineStr">
         <is>
-          <t>THC %, THC spec, CBD %, CBN %, Loss on drying %</t>
+          <t>THC %, THC spec, CBD %, CBN %, Loss on drying %, Ident A + B, Foreign matter</t>
         </is>
       </c>
       <c r="J210" s="8" t="inlineStr">

--- a/deliverables/qc_gap_analysis/PP_QC_Document_Registers_2026-08-31.xlsx
+++ b/deliverables/qc_gap_analysis/PP_QC_Document_Registers_2026-08-31.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary &amp; Notes" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'eCoA Receipt'!$A$5:$N$252</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'eCoA Receipt'!$A$5:$N$253</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'iCoA Issuance'!$A$5:$R$86</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'CoQ Issuance'!$A$5:$S$171</definedName>
   </definedNames>
@@ -594,7 +594,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N252"/>
+  <dimension ref="A1:N253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -16347,8 +16347,68 @@
         </is>
       </c>
     </row>
+    <row r="253">
+      <c r="A253" s="9" t="n">
+        <v>248</v>
+      </c>
+      <c r="B253" s="11" t="inlineStr">
+        <is>
+          <t>no date</t>
+        </is>
+      </c>
+      <c r="C253" s="11" t="inlineStr">
+        <is>
+          <t>IPH — Institute of Public Health</t>
+        </is>
+      </c>
+      <c r="D253" s="11" t="inlineStr">
+        <is>
+          <t>305/0549/26</t>
+        </is>
+      </c>
+      <c r="E253" s="11" t="inlineStr">
+        <is>
+          <t>SCR112501</t>
+        </is>
+      </c>
+      <c r="F253" s="9" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="G253" s="11" t="inlineStr">
+        <is>
+          <t>Scrambler</t>
+        </is>
+      </c>
+      <c r="H253" s="11" t="inlineStr"/>
+      <c r="I253" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J253" s="8" t="inlineStr">
+        <is>
+          <t>microbiology</t>
+        </is>
+      </c>
+      <c r="K253" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L253" s="12" t="inlineStr"/>
+      <c r="M253" s="9" t="n">
+        <v>239</v>
+      </c>
+      <c r="N253" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A5:N252"/>
+  <autoFilter ref="A5:N253"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N6" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N7" r:id="rId2"/>
@@ -35234,7 +35294,7 @@
         </is>
       </c>
       <c r="B4" s="20" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
@@ -35249,7 +35309,7 @@
         </is>
       </c>
       <c r="B5" s="20" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>

--- a/deliverables/qc_gap_analysis/PP_QC_Document_Registers_2026-08-31.xlsx
+++ b/deliverables/qc_gap_analysis/PP_QC_Document_Registers_2026-08-31.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'eCoA Receipt'!$A$5:$N$253</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'iCoA Issuance'!$A$5:$R$86</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'CoQ Issuance'!$A$5:$S$171</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'CoQ Issuance'!$A$5:$S$169</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -12452,7 +12452,7 @@
       </c>
       <c r="E191" s="11" t="inlineStr">
         <is>
-          <t>FB012601</t>
+          <t>FB012601/1</t>
         </is>
       </c>
       <c r="F191" s="9" t="inlineStr">
@@ -20333,7 +20333,7 @@
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>FB012601</t>
+          <t>FB012601/1</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
@@ -20770,7 +20770,7 @@
       <c r="L66" s="5" t="inlineStr"/>
       <c r="M66" s="7" t="inlineStr">
         <is>
-          <t>microbiology; physchem</t>
+          <t>physchem</t>
         </is>
       </c>
       <c r="N66" s="7" t="inlineStr"/>
@@ -22163,7 +22163,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S171"/>
+  <dimension ref="A1:S169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -25808,13 +25808,13 @@
         </is>
       </c>
       <c r="L46" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M46" s="5" t="n">
         <v>4</v>
       </c>
       <c r="N46" s="5" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="O46" s="5" t="n">
         <v>0</v>
@@ -25832,9 +25832,9 @@
           <t>Purely Plant laboratory — iCoA covering Ident A + B; outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest); Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
-      <c r="S46" s="18" t="inlineStr">
-        <is>
-          <t>No eCoA on file for this cultivation batch — locate the physical certificates, scan and upload. QCSP 001 prints 14.86 – 17.14 % for this lot; the issue plan's grade range is 16.20 – 19.79 %. Recorded, not resolved.</t>
+      <c r="S46" s="17" t="inlineStr">
+        <is>
+          <t>QCSP 001 prints 14.86 – 17.14 % for this lot; the issue plan's grade range is 16.20 – 19.79 %. Recorded, not resolved.</t>
         </is>
       </c>
     </row>
@@ -27866,7 +27866,7 @@
       <c r="D74" s="6" t="inlineStr"/>
       <c r="E74" s="6" t="inlineStr">
         <is>
-          <t>FB012601</t>
+          <t>FB112501</t>
         </is>
       </c>
       <c r="F74" s="6" t="inlineStr">
@@ -27908,7 +27908,7 @@
       </c>
       <c r="Q74" s="7" t="inlineStr">
         <is>
-          <t>ППК26067</t>
+          <t>ППК26066</t>
         </is>
       </c>
       <c r="R74" s="7" t="inlineStr">
@@ -27937,12 +27937,12 @@
       <c r="D75" s="11" t="inlineStr"/>
       <c r="E75" s="11" t="inlineStr">
         <is>
-          <t>FB112501</t>
+          <t>GG012601</t>
         </is>
       </c>
       <c r="F75" s="11" t="inlineStr">
         <is>
-          <t>Fat Bastard</t>
+          <t>Gorilla Glue</t>
         </is>
       </c>
       <c r="G75" s="9" t="inlineStr"/>
@@ -27979,7 +27979,7 @@
       </c>
       <c r="Q75" s="12" t="inlineStr">
         <is>
-          <t>ППК26066</t>
+          <t>ППК26062</t>
         </is>
       </c>
       <c r="R75" s="12" t="inlineStr">
@@ -28008,7 +28008,7 @@
       <c r="D76" s="6" t="inlineStr"/>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>GG012601</t>
+          <t>GG112501</t>
         </is>
       </c>
       <c r="F76" s="6" t="inlineStr">
@@ -28050,7 +28050,7 @@
       </c>
       <c r="Q76" s="7" t="inlineStr">
         <is>
-          <t>ППК26062</t>
+          <t>ППК26061</t>
         </is>
       </c>
       <c r="R76" s="7" t="inlineStr">
@@ -28079,12 +28079,12 @@
       <c r="D77" s="11" t="inlineStr"/>
       <c r="E77" s="11" t="inlineStr">
         <is>
-          <t>GG112501</t>
+          <t>JD012601</t>
         </is>
       </c>
       <c r="F77" s="11" t="inlineStr">
         <is>
-          <t>Gorilla Glue</t>
+          <t>Jelly Donutz</t>
         </is>
       </c>
       <c r="G77" s="9" t="inlineStr"/>
@@ -28121,7 +28121,7 @@
       </c>
       <c r="Q77" s="12" t="inlineStr">
         <is>
-          <t>ППК26061</t>
+          <t>ППК26064</t>
         </is>
       </c>
       <c r="R77" s="12" t="inlineStr">
@@ -28144,18 +28144,18 @@
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>≥ 11.05.2026</t>
+          <t>≥ 30.06.2026</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr"/>
       <c r="E78" s="6" t="inlineStr">
         <is>
-          <t>JD012601</t>
+          <t>FB012603</t>
         </is>
       </c>
       <c r="F78" s="6" t="inlineStr">
         <is>
-          <t>Jelly Donutz</t>
+          <t>Fat Bastard</t>
         </is>
       </c>
       <c r="G78" s="5" t="inlineStr"/>
@@ -28176,13 +28176,13 @@
         </is>
       </c>
       <c r="L78" s="5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M78" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N78" s="5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O78" s="5" t="n">
         <v>0</v>
@@ -28192,12 +28192,12 @@
       </c>
       <c r="Q78" s="7" t="inlineStr">
         <is>
-          <t>ППК26064</t>
+          <t>ППК26112</t>
         </is>
       </c>
       <c r="R78" s="7" t="inlineStr">
         <is>
-          <t>Purely Plant laboratory — iCoA covering Ident A + B; outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest); Purely Plant laboratory — iCoA covering Foreign matter</t>
+          <t>outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest)</t>
         </is>
       </c>
       <c r="S78" s="7" t="inlineStr"/>
@@ -28221,12 +28221,12 @@
       <c r="D79" s="11" t="inlineStr"/>
       <c r="E79" s="11" t="inlineStr">
         <is>
-          <t>FB012603</t>
+          <t>FB012603V</t>
         </is>
       </c>
       <c r="F79" s="11" t="inlineStr">
         <is>
-          <t>Fat Bastard</t>
+          <t>FatBastard</t>
         </is>
       </c>
       <c r="G79" s="9" t="inlineStr"/>
@@ -28263,7 +28263,7 @@
       </c>
       <c r="Q79" s="12" t="inlineStr">
         <is>
-          <t>ППК26112</t>
+          <t>ППК26110</t>
         </is>
       </c>
       <c r="R79" s="12" t="inlineStr">
@@ -28292,12 +28292,12 @@
       <c r="D80" s="6" t="inlineStr"/>
       <c r="E80" s="6" t="inlineStr">
         <is>
-          <t>FB012603V</t>
+          <t>JD022601</t>
         </is>
       </c>
       <c r="F80" s="6" t="inlineStr">
         <is>
-          <t>FatBastard</t>
+          <t>JellyDonutz</t>
         </is>
       </c>
       <c r="G80" s="5" t="inlineStr"/>
@@ -28334,7 +28334,7 @@
       </c>
       <c r="Q80" s="7" t="inlineStr">
         <is>
-          <t>ППК26110</t>
+          <t>ППК26115</t>
         </is>
       </c>
       <c r="R80" s="7" t="inlineStr">
@@ -28357,18 +28357,18 @@
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>≥ 30.06.2026</t>
+          <t>≥ 06.07.2026</t>
         </is>
       </c>
       <c r="D81" s="11" t="inlineStr"/>
       <c r="E81" s="11" t="inlineStr">
         <is>
-          <t>JD022601</t>
+          <t>P160012</t>
         </is>
       </c>
       <c r="F81" s="11" t="inlineStr">
         <is>
-          <t>JellyDonutz</t>
+          <t>GrapePie</t>
         </is>
       </c>
       <c r="G81" s="9" t="inlineStr"/>
@@ -28405,7 +28405,7 @@
       </c>
       <c r="Q81" s="12" t="inlineStr">
         <is>
-          <t>ППК26115</t>
+          <t>ППК26117</t>
         </is>
       </c>
       <c r="R81" s="12" t="inlineStr">
@@ -28434,7 +28434,7 @@
       <c r="D82" s="6" t="inlineStr"/>
       <c r="E82" s="6" t="inlineStr">
         <is>
-          <t>P160012</t>
+          <t>P160022</t>
         </is>
       </c>
       <c r="F82" s="6" t="inlineStr">
@@ -28476,7 +28476,7 @@
       </c>
       <c r="Q82" s="7" t="inlineStr">
         <is>
-          <t>ППК26117</t>
+          <t>ППК26118</t>
         </is>
       </c>
       <c r="R82" s="7" t="inlineStr">
@@ -28505,7 +28505,7 @@
       <c r="D83" s="11" t="inlineStr"/>
       <c r="E83" s="11" t="inlineStr">
         <is>
-          <t>P160022</t>
+          <t>P160032</t>
         </is>
       </c>
       <c r="F83" s="11" t="inlineStr">
@@ -28547,7 +28547,7 @@
       </c>
       <c r="Q83" s="12" t="inlineStr">
         <is>
-          <t>ППК26118</t>
+          <t>ППК26119</t>
         </is>
       </c>
       <c r="R83" s="12" t="inlineStr">
@@ -28576,12 +28576,12 @@
       <c r="D84" s="6" t="inlineStr"/>
       <c r="E84" s="6" t="inlineStr">
         <is>
-          <t>P160032</t>
+          <t>SCR022601</t>
         </is>
       </c>
       <c r="F84" s="6" t="inlineStr">
         <is>
-          <t>GrapePie</t>
+          <t>Scrambler</t>
         </is>
       </c>
       <c r="G84" s="5" t="inlineStr"/>
@@ -28618,7 +28618,7 @@
       </c>
       <c r="Q84" s="7" t="inlineStr">
         <is>
-          <t>ППК26119</t>
+          <t>ППК26116</t>
         </is>
       </c>
       <c r="R84" s="7" t="inlineStr">
@@ -28641,18 +28641,18 @@
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>≥ 06.07.2026</t>
+          <t>≥ 21.07.2026</t>
         </is>
       </c>
       <c r="D85" s="11" t="inlineStr"/>
       <c r="E85" s="11" t="inlineStr">
         <is>
-          <t>SCR022601</t>
+          <t>FB032601</t>
         </is>
       </c>
       <c r="F85" s="11" t="inlineStr">
         <is>
-          <t>Scrambler</t>
+          <t>FatBastard</t>
         </is>
       </c>
       <c r="G85" s="9" t="inlineStr"/>
@@ -28681,15 +28681,15 @@
       <c r="N85" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="O85" s="9" t="n">
-        <v>0</v>
+      <c r="O85" s="15" t="n">
+        <v>1</v>
       </c>
       <c r="P85" s="9" t="n">
         <v>1</v>
       </c>
       <c r="Q85" s="12" t="inlineStr">
         <is>
-          <t>ППК26116</t>
+          <t>ППК26127</t>
         </is>
       </c>
       <c r="R85" s="12" t="inlineStr">
@@ -28718,12 +28718,12 @@
       <c r="D86" s="6" t="inlineStr"/>
       <c r="E86" s="6" t="inlineStr">
         <is>
-          <t>FB032601</t>
+          <t>GG032601</t>
         </is>
       </c>
       <c r="F86" s="6" t="inlineStr">
         <is>
-          <t>FatBastard</t>
+          <t>GorillaGlue</t>
         </is>
       </c>
       <c r="G86" s="5" t="inlineStr"/>
@@ -28752,15 +28752,15 @@
       <c r="N86" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="O86" s="15" t="n">
-        <v>1</v>
+      <c r="O86" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="P86" s="5" t="n">
         <v>1</v>
       </c>
       <c r="Q86" s="7" t="inlineStr">
         <is>
-          <t>ППК26127</t>
+          <t>ППК26128</t>
         </is>
       </c>
       <c r="R86" s="7" t="inlineStr">
@@ -28783,18 +28783,18 @@
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>≥ 21.07.2026</t>
+          <t>≥ 11.05.2026</t>
         </is>
       </c>
       <c r="D87" s="11" t="inlineStr"/>
       <c r="E87" s="11" t="inlineStr">
         <is>
-          <t>GG032601</t>
+          <t>P060332</t>
         </is>
       </c>
       <c r="F87" s="11" t="inlineStr">
         <is>
-          <t>GorillaGlue</t>
+          <t>CashCow</t>
         </is>
       </c>
       <c r="G87" s="9" t="inlineStr"/>
@@ -28815,28 +28815,24 @@
         </is>
       </c>
       <c r="L87" s="9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M87" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N87" s="9" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="O87" s="9" t="n">
         <v>0</v>
       </c>
       <c r="P87" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q87" s="12" t="inlineStr">
-        <is>
-          <t>ППК26128</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q87" s="12" t="inlineStr"/>
       <c r="R87" s="12" t="inlineStr">
         <is>
-          <t>outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest)</t>
+          <t>Purely Plant laboratory — iCoA covering Ident A + B; outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest); Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
       <c r="S87" s="12" t="inlineStr"/>
@@ -28844,74 +28840,94 @@
     <row r="88">
       <c r="A88" s="6" t="inlineStr">
         <is>
-          <t>(assigned on issue)</t>
+          <t>CoQ-PP-2026-0027</t>
         </is>
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>initial release — predicted</t>
+          <t>additional testing (12-month)</t>
         </is>
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>≥ 11.05.2026</t>
-        </is>
-      </c>
-      <c r="D88" s="6" t="inlineStr"/>
+          <t>≥ 10.08.2026</t>
+        </is>
+      </c>
+      <c r="D88" s="6" t="inlineStr">
+        <is>
+          <t>BSS1024</t>
+        </is>
+      </c>
       <c r="E88" s="6" t="inlineStr">
         <is>
-          <t>P060332</t>
+          <t>BSS1024</t>
         </is>
       </c>
       <c r="F88" s="6" t="inlineStr">
         <is>
-          <t>CashCow</t>
-        </is>
-      </c>
-      <c r="G88" s="5" t="inlineStr"/>
+          <t>Blue Sunset Sherbet</t>
+        </is>
+      </c>
+      <c r="G88" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="H88" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">THC </t>
-        </is>
-      </c>
-      <c r="I88" s="5" t="inlineStr"/>
+          <t>THC 24</t>
+        </is>
+      </c>
+      <c r="I88" s="5" t="inlineStr">
+        <is>
+          <t>25.01</t>
+        </is>
+      </c>
       <c r="J88" s="7" t="inlineStr">
         <is>
-          <t>Per target grade — no packaged lot or grade assigned in the master spec yet</t>
+          <t>21.60 – 26.39 %  (grade I, class THC 24, nominal 24.00 ± 2.40)</t>
         </is>
       </c>
       <c r="K88" s="6" t="inlineStr">
         <is>
-          <t>(assigned on issue)</t>
+          <t>iCoA-PP-2025-0001</t>
         </is>
       </c>
       <c r="L88" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M88" s="5" t="n">
         <v>4</v>
       </c>
       <c r="N88" s="5" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="O88" s="5" t="n">
         <v>0</v>
       </c>
       <c r="P88" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q88" s="7" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="Q88" s="7" t="inlineStr">
+        <is>
+          <t>197-2-К/26; 197-2-М/26</t>
+        </is>
+      </c>
       <c r="R88" s="7" t="inlineStr">
         <is>
-          <t>Purely Plant laboratory — iCoA covering Ident A + B; outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest); Purely Plant laboratory — iCoA covering Foreign matter</t>
-        </is>
-      </c>
-      <c r="S88" s="7" t="inlineStr"/>
+          <t>Farmahem — Ident A + B + C with the Assay, at retest; Purely Plant laboratory — iCoA covering Foreign matter</t>
+        </is>
+      </c>
+      <c r="S88" s="17" t="inlineStr">
+        <is>
+          <t>QCSP 001 prints 22.01 – 25.99 % for this lot; the issue plan's grade range is 21.60 – 26.39 %. Recorded, not resolved.</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="11" t="inlineStr">
         <is>
-          <t>CoQ-PP-2026-0027</t>
+          <t>CoQ-PP-2026-0028</t>
         </is>
       </c>
       <c r="B89" s="11" t="inlineStr">
@@ -28926,17 +28942,17 @@
       </c>
       <c r="D89" s="11" t="inlineStr">
         <is>
-          <t>BSS1024</t>
+          <t>BG1024</t>
         </is>
       </c>
       <c r="E89" s="11" t="inlineStr">
         <is>
-          <t>BSS1024</t>
+          <t>BG1024</t>
         </is>
       </c>
       <c r="F89" s="11" t="inlineStr">
         <is>
-          <t>Blue Sunset Sherbet</t>
+          <t>Blue Gelato</t>
         </is>
       </c>
       <c r="G89" s="9" t="inlineStr">
@@ -28946,22 +28962,22 @@
       </c>
       <c r="H89" s="9" t="inlineStr">
         <is>
-          <t>THC 24</t>
+          <t>THC 26</t>
         </is>
       </c>
       <c r="I89" s="9" t="inlineStr">
         <is>
-          <t>25.01</t>
+          <t>26.14</t>
         </is>
       </c>
       <c r="J89" s="12" t="inlineStr">
         <is>
-          <t>21.60 – 26.39 %  (grade I, class THC 24, nominal 24.00 ± 2.40)</t>
+          <t>23.40 – 28.59 %  (grade I, class THC 26, nominal 26.00 ± 2.60)</t>
         </is>
       </c>
       <c r="K89" s="11" t="inlineStr">
         <is>
-          <t>iCoA-PP-2025-0001</t>
+          <t>iCoA-PP-2025-0002</t>
         </is>
       </c>
       <c r="L89" s="9" t="n">
@@ -28981,7 +28997,7 @@
       </c>
       <c r="Q89" s="12" t="inlineStr">
         <is>
-          <t>197-2-К/26; 197-2-М/26</t>
+          <t>197-1-К/26; 197-1-М/26</t>
         </is>
       </c>
       <c r="R89" s="12" t="inlineStr">
@@ -28989,16 +29005,12 @@
           <t>Farmahem — Ident A + B + C with the Assay, at retest; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
-      <c r="S89" s="17" t="inlineStr">
-        <is>
-          <t>QCSP 001 prints 22.01 – 25.99 % for this lot; the issue plan's grade range is 21.60 – 26.39 %. Recorded, not resolved.</t>
-        </is>
-      </c>
+      <c r="S89" s="12" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="6" t="inlineStr">
         <is>
-          <t>CoQ-PP-2026-0028</t>
+          <t>CoQ-PP-2026-0029</t>
         </is>
       </c>
       <c r="B90" s="6" t="inlineStr">
@@ -29008,54 +29020,54 @@
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>≥ 10.08.2026</t>
+          <t>≥ 11.05.2026</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr">
         <is>
-          <t>BG1024</t>
+          <t>GG1024</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
         <is>
-          <t>BG1024</t>
+          <t>GG1024</t>
         </is>
       </c>
       <c r="F90" s="6" t="inlineStr">
         <is>
-          <t>Blue Gelato</t>
+          <t>Gorilla Glue</t>
         </is>
       </c>
       <c r="G90" s="5" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
       <c r="H90" s="5" t="inlineStr">
         <is>
-          <t>THC 26</t>
+          <t>THC 16</t>
         </is>
       </c>
       <c r="I90" s="5" t="inlineStr">
         <is>
-          <t>26.14</t>
+          <t>15.51</t>
         </is>
       </c>
       <c r="J90" s="7" t="inlineStr">
         <is>
-          <t>23.40 – 28.59 %  (grade I, class THC 26, nominal 26.00 ± 2.60)</t>
+          <t>14.40 – 17.59 %  (grade II, class THC 16, nominal 16.00 ± 1.60)</t>
         </is>
       </c>
       <c r="K90" s="6" t="inlineStr">
         <is>
-          <t>iCoA-PP-2025-0002</t>
+          <t>iCoA-PP-2025-0003</t>
         </is>
       </c>
       <c r="L90" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M90" s="5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="N90" s="5" t="n">
         <v>0</v>
@@ -29064,24 +29076,24 @@
         <v>0</v>
       </c>
       <c r="P90" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q90" s="7" t="inlineStr">
-        <is>
-          <t>197-1-К/26; 197-1-М/26</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q90" s="7" t="inlineStr"/>
       <c r="R90" s="7" t="inlineStr">
         <is>
           <t>Farmahem — Ident A + B + C with the Assay, at retest; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
-      <c r="S90" s="7" t="inlineStr"/>
+      <c r="S90" s="18" t="inlineStr">
+        <is>
+          <t>No eCoA on file for this cultivation batch — locate the physical certificates, scan and upload. QCSP 001 prints 15.00 – 17.00 % for this lot; the issue plan's grade range is 14.40 – 17.59 %. Recorded, not resolved.</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="11" t="inlineStr">
         <is>
-          <t>CoQ-PP-2026-0029</t>
+          <t>CoQ-PP-2026-0030</t>
         </is>
       </c>
       <c r="B91" s="11" t="inlineStr">
@@ -29091,54 +29103,54 @@
       </c>
       <c r="C91" s="11" t="inlineStr">
         <is>
-          <t>≥ 11.05.2026</t>
+          <t>≥ 10.08.2026</t>
         </is>
       </c>
       <c r="D91" s="11" t="inlineStr">
         <is>
-          <t>GG1024</t>
+          <t>HPA1024</t>
         </is>
       </c>
       <c r="E91" s="11" t="inlineStr">
         <is>
-          <t>GG1024</t>
+          <t>HPA1024</t>
         </is>
       </c>
       <c r="F91" s="11" t="inlineStr">
         <is>
-          <t>Gorilla Glue</t>
+          <t>High Pro Amnesia</t>
         </is>
       </c>
       <c r="G91" s="9" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>III</t>
         </is>
       </c>
       <c r="H91" s="9" t="inlineStr">
         <is>
-          <t>THC 16</t>
+          <t>THC 18</t>
         </is>
       </c>
       <c r="I91" s="9" t="inlineStr">
         <is>
-          <t>15.51</t>
+          <t>17.31</t>
         </is>
       </c>
       <c r="J91" s="12" t="inlineStr">
         <is>
-          <t>14.40 – 17.59 %  (grade II, class THC 16, nominal 16.00 ± 1.60)</t>
+          <t>16.20 – 19.79 %  (grade III, class THC 18, nominal 18.00 ± 1.80)</t>
         </is>
       </c>
       <c r="K91" s="11" t="inlineStr">
         <is>
-          <t>iCoA-PP-2025-0003</t>
+          <t>iCoA-PP-2025-0004</t>
         </is>
       </c>
       <c r="L91" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M91" s="9" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="N91" s="9" t="n">
         <v>0</v>
@@ -29147,24 +29159,28 @@
         <v>0</v>
       </c>
       <c r="P91" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q91" s="12" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="Q91" s="12" t="inlineStr">
+        <is>
+          <t>197-13-К/26; 197-13-М/26</t>
+        </is>
+      </c>
       <c r="R91" s="12" t="inlineStr">
         <is>
           <t>Farmahem — Ident A + B + C with the Assay, at retest; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
-      <c r="S91" s="18" t="inlineStr">
-        <is>
-          <t>No eCoA on file for this cultivation batch — locate the physical certificates, scan and upload. QCSP 001 prints 15.00 – 17.00 % for this lot; the issue plan's grade range is 14.40 – 17.59 %. Recorded, not resolved.</t>
+      <c r="S91" s="17" t="inlineStr">
+        <is>
+          <t>QCSP 001 prints 17.00 – 19.00 % for this lot; the issue plan's grade range is 16.20 – 19.79 %. Recorded, not resolved.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>CoQ-PP-2026-0030</t>
+          <t>CoQ-PP-2026-0031</t>
         </is>
       </c>
       <c r="B92" s="6" t="inlineStr">
@@ -29179,42 +29195,42 @@
       </c>
       <c r="D92" s="6" t="inlineStr">
         <is>
-          <t>HPA1024</t>
+          <t>OPM1024</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
         <is>
-          <t>HPA1024</t>
+          <t>OPM1024</t>
         </is>
       </c>
       <c r="F92" s="6" t="inlineStr">
         <is>
-          <t>High Pro Amnesia</t>
+          <t>Orange Punch Mimosa</t>
         </is>
       </c>
       <c r="G92" s="5" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>I</t>
         </is>
       </c>
       <c r="H92" s="5" t="inlineStr">
         <is>
-          <t>THC 18</t>
+          <t>THC 22</t>
         </is>
       </c>
       <c r="I92" s="5" t="inlineStr">
         <is>
-          <t>17.31</t>
+          <t>20.03</t>
         </is>
       </c>
       <c r="J92" s="7" t="inlineStr">
         <is>
-          <t>16.20 – 19.79 %  (grade III, class THC 18, nominal 18.00 ± 1.80)</t>
+          <t>19.80 – 24.19 %  (grade I, class THC 22, nominal 22.00 ± 2.20)</t>
         </is>
       </c>
       <c r="K92" s="6" t="inlineStr">
         <is>
-          <t>iCoA-PP-2025-0004</t>
+          <t>iCoA-PP-2025-0005</t>
         </is>
       </c>
       <c r="L92" s="5" t="n">
@@ -29234,7 +29250,7 @@
       </c>
       <c r="Q92" s="7" t="inlineStr">
         <is>
-          <t>197-13-К/26; 197-13-М/26</t>
+          <t>197-17-К/26; 197-17-М/26</t>
         </is>
       </c>
       <c r="R92" s="7" t="inlineStr">
@@ -29242,16 +29258,12 @@
           <t>Farmahem — Ident A + B + C with the Assay, at retest; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
-      <c r="S92" s="17" t="inlineStr">
-        <is>
-          <t>QCSP 001 prints 17.00 – 19.00 % for this lot; the issue plan's grade range is 16.20 – 19.79 %. Recorded, not resolved.</t>
-        </is>
-      </c>
+      <c r="S92" s="7" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="11" t="inlineStr">
         <is>
-          <t>CoQ-PP-2026-0031</t>
+          <t>CoQ-PP-2026-0032</t>
         </is>
       </c>
       <c r="B93" s="11" t="inlineStr">
@@ -29266,42 +29278,42 @@
       </c>
       <c r="D93" s="11" t="inlineStr">
         <is>
-          <t>OPM1024</t>
+          <t>P050022</t>
         </is>
       </c>
       <c r="E93" s="11" t="inlineStr">
         <is>
-          <t>OPM1024</t>
+          <t>GP0824_02</t>
         </is>
       </c>
       <c r="F93" s="11" t="inlineStr">
         <is>
-          <t>Orange Punch Mimosa</t>
+          <t>Grape Pie</t>
         </is>
       </c>
       <c r="G93" s="9" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>III</t>
         </is>
       </c>
       <c r="H93" s="9" t="inlineStr">
         <is>
-          <t>THC 22</t>
+          <t>THC 24</t>
         </is>
       </c>
       <c r="I93" s="9" t="inlineStr">
         <is>
-          <t>20.03</t>
+          <t>22.61</t>
         </is>
       </c>
       <c r="J93" s="12" t="inlineStr">
         <is>
-          <t>19.80 – 24.19 %  (grade I, class THC 22, nominal 22.00 ± 2.20)</t>
+          <t>21.60 – 26.39 %  (grade III, class THC 24, nominal 24.00 ± 2.40)</t>
         </is>
       </c>
       <c r="K93" s="11" t="inlineStr">
         <is>
-          <t>iCoA-PP-2025-0005</t>
+          <t>iCoA-PP-2025-0006</t>
         </is>
       </c>
       <c r="L93" s="9" t="n">
@@ -29321,7 +29333,7 @@
       </c>
       <c r="Q93" s="12" t="inlineStr">
         <is>
-          <t>197-17-К/26; 197-17-М/26</t>
+          <t>197-11-К/26; 197-11-М/26</t>
         </is>
       </c>
       <c r="R93" s="12" t="inlineStr">
@@ -29329,12 +29341,16 @@
           <t>Farmahem — Ident A + B + C with the Assay, at retest; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
-      <c r="S93" s="12" t="inlineStr"/>
+      <c r="S93" s="17" t="inlineStr">
+        <is>
+          <t>QCSP 001 prints 22.61 – 25.39 % for this lot; the issue plan's grade range is 21.60 – 26.39 %. Recorded, not resolved.</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t>CoQ-PP-2026-0032</t>
+          <t>CoQ-PP-2026-0033</t>
         </is>
       </c>
       <c r="B94" s="6" t="inlineStr">
@@ -29344,22 +29360,22 @@
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>≥ 10.08.2026</t>
+          <t>≥ 20.06.2026</t>
         </is>
       </c>
       <c r="D94" s="6" t="inlineStr">
         <is>
-          <t>P050022</t>
+          <t>P050042</t>
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr">
         <is>
-          <t>GP0824_02</t>
+          <t>OMP1024_01</t>
         </is>
       </c>
       <c r="F94" s="6" t="inlineStr">
         <is>
-          <t>Grape Pie</t>
+          <t>Orange Punch Mimosa</t>
         </is>
       </c>
       <c r="G94" s="5" t="inlineStr">
@@ -29369,29 +29385,29 @@
       </c>
       <c r="H94" s="5" t="inlineStr">
         <is>
-          <t>THC 24</t>
+          <t>THC 18</t>
         </is>
       </c>
       <c r="I94" s="5" t="inlineStr">
         <is>
-          <t>22.61</t>
+          <t>18.99</t>
         </is>
       </c>
       <c r="J94" s="7" t="inlineStr">
         <is>
-          <t>21.60 – 26.39 %  (grade III, class THC 24, nominal 24.00 ± 2.40)</t>
+          <t>16.20 – 19.79 %  (grade III, class THC 18, nominal 18.00 ± 1.80)</t>
         </is>
       </c>
       <c r="K94" s="6" t="inlineStr">
         <is>
-          <t>iCoA-PP-2025-0006</t>
+          <t>iCoA-PP-2025-0007</t>
         </is>
       </c>
       <c r="L94" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M94" s="5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="N94" s="5" t="n">
         <v>0</v>
@@ -29400,28 +29416,20 @@
         <v>0</v>
       </c>
       <c r="P94" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q94" s="7" t="inlineStr">
-        <is>
-          <t>197-11-К/26; 197-11-М/26</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q94" s="7" t="inlineStr"/>
       <c r="R94" s="7" t="inlineStr">
         <is>
           <t>Farmahem — Ident A + B + C with the Assay, at retest; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
-      <c r="S94" s="17" t="inlineStr">
-        <is>
-          <t>QCSP 001 prints 22.61 – 25.39 % for this lot; the issue plan's grade range is 21.60 – 26.39 %. Recorded, not resolved.</t>
-        </is>
-      </c>
+      <c r="S94" s="7" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="11" t="inlineStr">
         <is>
-          <t>CoQ-PP-2026-0033</t>
+          <t>CoQ-PP-2026-0034</t>
         </is>
       </c>
       <c r="B95" s="11" t="inlineStr">
@@ -29431,54 +29439,54 @@
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>≥ 20.06.2026</t>
+          <t>≥ 10.08.2026</t>
         </is>
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>P050042</t>
+          <t>P050052</t>
         </is>
       </c>
       <c r="E95" s="11" t="inlineStr">
         <is>
-          <t>OMP1024_01</t>
+          <t>HPA1024_01</t>
         </is>
       </c>
       <c r="F95" s="11" t="inlineStr">
         <is>
-          <t>Orange Punch Mimosa</t>
+          <t>High Pro Amnesia</t>
         </is>
       </c>
       <c r="G95" s="9" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>I</t>
         </is>
       </c>
       <c r="H95" s="9" t="inlineStr">
         <is>
-          <t>THC 18</t>
+          <t>THC 22</t>
         </is>
       </c>
       <c r="I95" s="9" t="inlineStr">
         <is>
-          <t>18.99</t>
+          <t>21.61</t>
         </is>
       </c>
       <c r="J95" s="12" t="inlineStr">
         <is>
-          <t>16.20 – 19.79 %  (grade III, class THC 18, nominal 18.00 ± 1.80)</t>
+          <t>19.80 – 24.19 %  (grade I, class THC 22, nominal 22.00 ± 2.20)</t>
         </is>
       </c>
       <c r="K95" s="11" t="inlineStr">
         <is>
-          <t>iCoA-PP-2025-0007</t>
+          <t>iCoA-PP-2025-0008</t>
         </is>
       </c>
       <c r="L95" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M95" s="9" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="N95" s="9" t="n">
         <v>0</v>
@@ -29487,20 +29495,28 @@
         <v>0</v>
       </c>
       <c r="P95" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q95" s="12" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="Q95" s="12" t="inlineStr">
+        <is>
+          <t>197-14-К/26; 197-14-М/26</t>
+        </is>
+      </c>
       <c r="R95" s="12" t="inlineStr">
         <is>
           <t>Farmahem — Ident A + B + C with the Assay, at retest; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
-      <c r="S95" s="12" t="inlineStr"/>
+      <c r="S95" s="17" t="inlineStr">
+        <is>
+          <t>QCSP 001 prints 21.00 – 23.00 % for this lot; the issue plan's grade range is 19.80 – 24.19 %. Recorded, not resolved.</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="6" t="inlineStr">
         <is>
-          <t>CoQ-PP-2026-0034</t>
+          <t>CoQ-PP-2026-0035</t>
         </is>
       </c>
       <c r="B96" s="6" t="inlineStr">
@@ -29515,42 +29531,42 @@
       </c>
       <c r="D96" s="6" t="inlineStr">
         <is>
-          <t>P050052</t>
+          <t>P050062</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr">
         <is>
-          <t>HPA1024_01</t>
+          <t>OPM1024_02</t>
         </is>
       </c>
       <c r="F96" s="6" t="inlineStr">
         <is>
-          <t>High Pro Amnesia</t>
+          <t>Orange Punch Mimosa</t>
         </is>
       </c>
       <c r="G96" s="5" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>III</t>
         </is>
       </c>
       <c r="H96" s="5" t="inlineStr">
         <is>
-          <t>THC 22</t>
+          <t>THC 18</t>
         </is>
       </c>
       <c r="I96" s="5" t="inlineStr">
         <is>
-          <t>21.61</t>
+          <t>18.04</t>
         </is>
       </c>
       <c r="J96" s="7" t="inlineStr">
         <is>
-          <t>19.80 – 24.19 %  (grade I, class THC 22, nominal 22.00 ± 2.20)</t>
+          <t>16.20 – 19.79 %  (grade III, class THC 18, nominal 18.00 ± 1.80)</t>
         </is>
       </c>
       <c r="K96" s="6" t="inlineStr">
         <is>
-          <t>iCoA-PP-2025-0008</t>
+          <t>iCoA-PP-2025-0009</t>
         </is>
       </c>
       <c r="L96" s="5" t="n">
@@ -29570,7 +29586,7 @@
       </c>
       <c r="Q96" s="7" t="inlineStr">
         <is>
-          <t>197-14-К/26; 197-14-М/26</t>
+          <t>197-18-К/26; 197-18-М/26</t>
         </is>
       </c>
       <c r="R96" s="7" t="inlineStr">
@@ -29578,16 +29594,12 @@
           <t>Farmahem — Ident A + B + C with the Assay, at retest; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
-      <c r="S96" s="17" t="inlineStr">
-        <is>
-          <t>QCSP 001 prints 21.00 – 23.00 % for this lot; the issue plan's grade range is 19.80 – 24.19 %. Recorded, not resolved.</t>
-        </is>
-      </c>
+      <c r="S96" s="7" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="11" t="inlineStr">
         <is>
-          <t>CoQ-PP-2026-0035</t>
+          <t>CoQ-PP-2026-0036</t>
         </is>
       </c>
       <c r="B97" s="11" t="inlineStr">
@@ -29597,54 +29609,54 @@
       </c>
       <c r="C97" s="11" t="inlineStr">
         <is>
-          <t>≥ 10.08.2026</t>
+          <t>≥ 14.07.2026</t>
         </is>
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>P050062</t>
+          <t>P050072</t>
         </is>
       </c>
       <c r="E97" s="11" t="inlineStr">
         <is>
-          <t>OPM1024_02</t>
+          <t>GP0824_03</t>
         </is>
       </c>
       <c r="F97" s="11" t="inlineStr">
         <is>
-          <t>Orange Punch Mimosa</t>
+          <t>Grape Pie</t>
         </is>
       </c>
       <c r="G97" s="9" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>I</t>
         </is>
       </c>
       <c r="H97" s="9" t="inlineStr">
         <is>
-          <t>THC 18</t>
+          <t>THC 28</t>
         </is>
       </c>
       <c r="I97" s="9" t="inlineStr">
         <is>
-          <t>18.04</t>
+          <t>28.30</t>
         </is>
       </c>
       <c r="J97" s="12" t="inlineStr">
         <is>
-          <t>16.20 – 19.79 %  (grade III, class THC 18, nominal 18.00 ± 1.80)</t>
+          <t>25.20 – 30.79 %  (grade I, class THC 28, nominal 28.00 ± 2.80)</t>
         </is>
       </c>
       <c r="K97" s="11" t="inlineStr">
         <is>
-          <t>iCoA-PP-2025-0009</t>
+          <t>iCoA-PP-2025-0010</t>
         </is>
       </c>
       <c r="L97" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M97" s="9" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="N97" s="9" t="n">
         <v>0</v>
@@ -29653,24 +29665,24 @@
         <v>0</v>
       </c>
       <c r="P97" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q97" s="12" t="inlineStr">
-        <is>
-          <t>197-18-К/26; 197-18-М/26</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q97" s="12" t="inlineStr"/>
       <c r="R97" s="12" t="inlineStr">
         <is>
           <t>Farmahem — Ident A + B + C with the Assay, at retest; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
-      <c r="S97" s="12" t="inlineStr"/>
+      <c r="S97" s="17" t="inlineStr">
+        <is>
+          <t>QCSP 001 prints 26.61 – 29.39 % for this lot; the issue plan's grade range is 25.20 – 30.79 %. Recorded, not resolved.</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="6" t="inlineStr">
         <is>
-          <t>CoQ-PP-2026-0036</t>
+          <t>CoQ-PP-2026-0037</t>
         </is>
       </c>
       <c r="B98" s="6" t="inlineStr">
@@ -29680,47 +29692,47 @@
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>≥ 14.07.2026</t>
+          <t>≥ 22.07.2026</t>
         </is>
       </c>
       <c r="D98" s="6" t="inlineStr">
         <is>
-          <t>P050072</t>
+          <t>P050082</t>
         </is>
       </c>
       <c r="E98" s="6" t="inlineStr">
         <is>
-          <t>GP0824_03</t>
+          <t>OPM1024_03</t>
         </is>
       </c>
       <c r="F98" s="6" t="inlineStr">
         <is>
-          <t>Grape Pie</t>
+          <t>Orange Punch Mimosa</t>
         </is>
       </c>
       <c r="G98" s="5" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
       <c r="H98" s="5" t="inlineStr">
         <is>
-          <t>THC 28</t>
+          <t>THC 20</t>
         </is>
       </c>
       <c r="I98" s="5" t="inlineStr">
         <is>
-          <t>28.30</t>
+          <t>19.30</t>
         </is>
       </c>
       <c r="J98" s="7" t="inlineStr">
         <is>
-          <t>25.20 – 30.79 %  (grade I, class THC 28, nominal 28.00 ± 2.80)</t>
+          <t>18.00 – 21.99 %  (grade II, class THC 20, nominal 20.00 ± 2.00)</t>
         </is>
       </c>
       <c r="K98" s="6" t="inlineStr">
         <is>
-          <t>iCoA-PP-2025-0010</t>
+          <t>iCoA-PP-2025-0011</t>
         </is>
       </c>
       <c r="L98" s="5" t="n">
@@ -29746,14 +29758,14 @@
       </c>
       <c r="S98" s="17" t="inlineStr">
         <is>
-          <t>QCSP 001 prints 26.61 – 29.39 % for this lot; the issue plan's grade range is 25.20 – 30.79 %. Recorded, not resolved.</t>
+          <t>QCSP 001 prints 16.20 – 19.80 % for this lot; the issue plan's grade range is 18.00 – 21.99 %. Recorded, not resolved.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="11" t="inlineStr">
         <is>
-          <t>CoQ-PP-2026-0037</t>
+          <t>CoQ-PP-2026-0038</t>
         </is>
       </c>
       <c r="B99" s="11" t="inlineStr">
@@ -29763,54 +29775,54 @@
       </c>
       <c r="C99" s="11" t="inlineStr">
         <is>
-          <t>≥ 22.07.2026</t>
+          <t>≥ 10.08.2026</t>
         </is>
       </c>
       <c r="D99" s="11" t="inlineStr">
         <is>
-          <t>P050082</t>
+          <t>P050092</t>
         </is>
       </c>
       <c r="E99" s="11" t="inlineStr">
         <is>
-          <t>OPM1024_03</t>
+          <t>GG1024_01</t>
         </is>
       </c>
       <c r="F99" s="11" t="inlineStr">
         <is>
-          <t>Orange Punch Mimosa</t>
+          <t>Gorilla Glue</t>
         </is>
       </c>
       <c r="G99" s="9" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
       <c r="H99" s="9" t="inlineStr">
         <is>
-          <t>THC 20</t>
+          <t>THC 18</t>
         </is>
       </c>
       <c r="I99" s="9" t="inlineStr">
         <is>
-          <t>19.30</t>
+          <t>18.67</t>
         </is>
       </c>
       <c r="J99" s="12" t="inlineStr">
         <is>
-          <t>18.00 – 21.99 %  (grade II, class THC 20, nominal 20.00 ± 2.00)</t>
+          <t>16.20 – 19.79 %  (grade I, class THC 18, nominal 18.00 ± 1.80)</t>
         </is>
       </c>
       <c r="K99" s="11" t="inlineStr">
         <is>
-          <t>iCoA-PP-2025-0011</t>
+          <t>iCoA-PP-2025-0012</t>
         </is>
       </c>
       <c r="L99" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M99" s="9" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="N99" s="9" t="n">
         <v>0</v>
@@ -29819,9 +29831,13 @@
         <v>0</v>
       </c>
       <c r="P99" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q99" s="12" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="Q99" s="12" t="inlineStr">
+        <is>
+          <t>197-9-К/26; 197-9-М/26</t>
+        </is>
+      </c>
       <c r="R99" s="12" t="inlineStr">
         <is>
           <t>Farmahem — Ident A + B + C with the Assay, at retest; Purely Plant laboratory — iCoA covering Foreign matter</t>
@@ -29829,14 +29845,14 @@
       </c>
       <c r="S99" s="17" t="inlineStr">
         <is>
-          <t>QCSP 001 prints 16.20 – 19.80 % for this lot; the issue plan's grade range is 18.00 – 21.99 %. Recorded, not resolved.</t>
+          <t>QCSP 001 prints 17.01 – 18.99 % for this lot; the issue plan's grade range is 16.20 – 19.79 %. Recorded, not resolved.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="6" t="inlineStr">
         <is>
-          <t>CoQ-PP-2026-0038</t>
+          <t>CoQ-PP-2026-0039</t>
         </is>
       </c>
       <c r="B100" s="6" t="inlineStr">
@@ -29846,22 +29862,22 @@
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>≥ 10.08.2026</t>
+          <t>≥ 25.08.2026</t>
         </is>
       </c>
       <c r="D100" s="6" t="inlineStr">
         <is>
-          <t>P050092</t>
+          <t>P050112</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr">
         <is>
-          <t>GG1024_01</t>
+          <t>MB0824_05</t>
         </is>
       </c>
       <c r="F100" s="6" t="inlineStr">
         <is>
-          <t>Gorilla Glue</t>
+          <t>Motor Breath</t>
         </is>
       </c>
       <c r="G100" s="5" t="inlineStr">
@@ -29876,7 +29892,7 @@
       </c>
       <c r="I100" s="5" t="inlineStr">
         <is>
-          <t>18.67</t>
+          <t>17.93</t>
         </is>
       </c>
       <c r="J100" s="7" t="inlineStr">
@@ -29886,14 +29902,14 @@
       </c>
       <c r="K100" s="6" t="inlineStr">
         <is>
-          <t>iCoA-PP-2025-0012</t>
+          <t>iCoA-PP-2025-0013</t>
         </is>
       </c>
       <c r="L100" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M100" s="5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="N100" s="5" t="n">
         <v>0</v>
@@ -29902,58 +29918,50 @@
         <v>0</v>
       </c>
       <c r="P100" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q100" s="7" t="inlineStr">
-        <is>
-          <t>197-9-К/26; 197-9-М/26</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q100" s="7" t="inlineStr"/>
       <c r="R100" s="7" t="inlineStr">
         <is>
           <t>Farmahem — Ident A + B + C with the Assay, at retest; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
-      <c r="S100" s="17" t="inlineStr">
-        <is>
-          <t>QCSP 001 prints 17.01 – 18.99 % for this lot; the issue plan's grade range is 16.20 – 19.79 %. Recorded, not resolved.</t>
-        </is>
-      </c>
+      <c r="S100" s="7" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="11" t="inlineStr">
         <is>
-          <t>CoQ-PP-2026-0039</t>
+          <t>(assigned on issue)</t>
         </is>
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t>additional testing (12-month)</t>
+          <t>additional testing (12-month) — predicted</t>
         </is>
       </c>
       <c r="C101" s="11" t="inlineStr">
         <is>
-          <t>≥ 25.08.2026</t>
+          <t>≥ 10.08.2026</t>
         </is>
       </c>
       <c r="D101" s="11" t="inlineStr">
         <is>
-          <t>P050112</t>
+          <t>P050152</t>
         </is>
       </c>
       <c r="E101" s="11" t="inlineStr">
         <is>
-          <t>MB0824_05</t>
+          <t>GP052501</t>
         </is>
       </c>
       <c r="F101" s="11" t="inlineStr">
         <is>
-          <t>Motor Breath</t>
+          <t>Grape Pie</t>
         </is>
       </c>
       <c r="G101" s="9" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>IV</t>
         </is>
       </c>
       <c r="H101" s="9" t="inlineStr">
@@ -29963,24 +29971,24 @@
       </c>
       <c r="I101" s="9" t="inlineStr">
         <is>
-          <t>17.93</t>
+          <t>18.52</t>
         </is>
       </c>
       <c r="J101" s="12" t="inlineStr">
         <is>
-          <t>16.20 – 19.79 %  (grade I, class THC 18, nominal 18.00 ± 1.80)</t>
+          <t>16.20 – 19.79 %  (grade IV, class THC 18, nominal 18.00 ± 1.80)</t>
         </is>
       </c>
       <c r="K101" s="11" t="inlineStr">
         <is>
-          <t>iCoA-PP-2025-0013</t>
+          <t>iCoA-PP-2025-0014</t>
         </is>
       </c>
       <c r="L101" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M101" s="9" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="N101" s="9" t="n">
         <v>0</v>
@@ -29989,9 +29997,13 @@
         <v>0</v>
       </c>
       <c r="P101" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q101" s="12" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="Q101" s="12" t="inlineStr">
+        <is>
+          <t>197-10-К/26; 197-10-М/26</t>
+        </is>
+      </c>
       <c r="R101" s="12" t="inlineStr">
         <is>
           <t>Farmahem — Ident A + B + C with the Assay, at retest; Purely Plant laboratory — iCoA covering Foreign matter</t>
@@ -30017,42 +30029,42 @@
       </c>
       <c r="D102" s="6" t="inlineStr">
         <is>
-          <t>P050152</t>
+          <t>P050162</t>
         </is>
       </c>
       <c r="E102" s="6" t="inlineStr">
         <is>
-          <t>GP052501</t>
+          <t>CJ052501/01</t>
         </is>
       </c>
       <c r="F102" s="6" t="inlineStr">
         <is>
-          <t>Grape Pie</t>
+          <t>Cap Junky</t>
         </is>
       </c>
       <c r="G102" s="5" t="inlineStr">
         <is>
-          <t>IV</t>
+          <t>III</t>
         </is>
       </c>
       <c r="H102" s="5" t="inlineStr">
         <is>
-          <t>THC 18</t>
+          <t>THC 24</t>
         </is>
       </c>
       <c r="I102" s="5" t="inlineStr">
         <is>
-          <t>18.52</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="J102" s="7" t="inlineStr">
         <is>
-          <t>16.20 – 19.79 %  (grade IV, class THC 18, nominal 18.00 ± 1.80)</t>
+          <t>21.60 – 26.39 %  (grade III, class THC 24, nominal 24.00 ± 2.40)</t>
         </is>
       </c>
       <c r="K102" s="6" t="inlineStr">
         <is>
-          <t>iCoA-PP-2025-0014</t>
+          <t>iCoA-PP-2025-0015</t>
         </is>
       </c>
       <c r="L102" s="5" t="n">
@@ -30072,7 +30084,7 @@
       </c>
       <c r="Q102" s="7" t="inlineStr">
         <is>
-          <t>197-10-К/26; 197-10-М/26</t>
+          <t>197-3-К/26; 197-3-М/26</t>
         </is>
       </c>
       <c r="R102" s="7" t="inlineStr">
@@ -30080,7 +30092,11 @@
           <t>Farmahem — Ident A + B + C with the Assay, at retest; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
-      <c r="S102" s="7" t="inlineStr"/>
+      <c r="S102" s="17" t="inlineStr">
+        <is>
+          <t>QCSP 001 prints 23.00 – 25.00 % for this lot; the issue plan's grade range is 21.60 – 26.39 %. Recorded, not resolved.</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="11" t="inlineStr">
@@ -30095,54 +30111,54 @@
       </c>
       <c r="C103" s="11" t="inlineStr">
         <is>
-          <t>≥ 10.08.2026</t>
+          <t>≥ 03.10.2026</t>
         </is>
       </c>
       <c r="D103" s="11" t="inlineStr">
         <is>
-          <t>P050162</t>
+          <t>P050182</t>
         </is>
       </c>
       <c r="E103" s="11" t="inlineStr">
         <is>
-          <t>CJ052501/01</t>
+          <t>HPA052501</t>
         </is>
       </c>
       <c r="F103" s="11" t="inlineStr">
         <is>
-          <t>Cap Junky</t>
+          <t>High Pro Amnesia</t>
         </is>
       </c>
       <c r="G103" s="9" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>II</t>
         </is>
       </c>
       <c r="H103" s="9" t="inlineStr">
         <is>
-          <t>THC 24</t>
+          <t>THC 20</t>
         </is>
       </c>
       <c r="I103" s="9" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>19.69</t>
         </is>
       </c>
       <c r="J103" s="12" t="inlineStr">
         <is>
-          <t>21.60 – 26.39 %  (grade III, class THC 24, nominal 24.00 ± 2.40)</t>
+          <t>18.00 – 21.99 %  (grade II, class THC 20, nominal 20.00 ± 2.00)</t>
         </is>
       </c>
       <c r="K103" s="11" t="inlineStr">
         <is>
-          <t>iCoA-PP-2025-0015</t>
+          <t>iCoA-PP-2025-0016</t>
         </is>
       </c>
       <c r="L103" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M103" s="9" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="N103" s="9" t="n">
         <v>0</v>
@@ -30151,13 +30167,9 @@
         <v>0</v>
       </c>
       <c r="P103" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q103" s="12" t="inlineStr">
-        <is>
-          <t>197-3-К/26; 197-3-М/26</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q103" s="12" t="inlineStr"/>
       <c r="R103" s="12" t="inlineStr">
         <is>
           <t>Farmahem — Ident A + B + C with the Assay, at retest; Purely Plant laboratory — iCoA covering Foreign matter</t>
@@ -30165,7 +30177,7 @@
       </c>
       <c r="S103" s="17" t="inlineStr">
         <is>
-          <t>QCSP 001 prints 23.00 – 25.00 % for this lot; the issue plan's grade range is 21.60 – 26.39 %. Recorded, not resolved.</t>
+          <t>QCSP 001 prints 19.01 – 20.99 % for this lot; the issue plan's grade range is 18.00 – 21.99 %. Recorded, not resolved.</t>
         </is>
       </c>
     </row>
@@ -30182,22 +30194,22 @@
       </c>
       <c r="C104" s="6" t="inlineStr">
         <is>
-          <t>≥ 03.10.2026</t>
+          <t>≥ 10.10.2026</t>
         </is>
       </c>
       <c r="D104" s="6" t="inlineStr">
         <is>
-          <t>P050182</t>
+          <t>P050192</t>
         </is>
       </c>
       <c r="E104" s="6" t="inlineStr">
         <is>
-          <t>HPA052501</t>
+          <t>BSS052501</t>
         </is>
       </c>
       <c r="F104" s="6" t="inlineStr">
         <is>
-          <t>High Pro Amnesia</t>
+          <t>Blue Sunset Sherbet</t>
         </is>
       </c>
       <c r="G104" s="5" t="inlineStr">
@@ -30212,7 +30224,7 @@
       </c>
       <c r="I104" s="5" t="inlineStr">
         <is>
-          <t>19.69</t>
+          <t>20.52</t>
         </is>
       </c>
       <c r="J104" s="7" t="inlineStr">
@@ -30222,7 +30234,7 @@
       </c>
       <c r="K104" s="6" t="inlineStr">
         <is>
-          <t>iCoA-PP-2025-0016</t>
+          <t>iCoA-PP-2025-0017</t>
         </is>
       </c>
       <c r="L104" s="5" t="n">
@@ -30246,11 +30258,7 @@
           <t>Farmahem — Ident A + B + C with the Assay, at retest; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
-      <c r="S104" s="17" t="inlineStr">
-        <is>
-          <t>QCSP 001 prints 19.01 – 20.99 % for this lot; the issue plan's grade range is 18.00 – 21.99 %. Recorded, not resolved.</t>
-        </is>
-      </c>
+      <c r="S104" s="7" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="11" t="inlineStr">
@@ -30265,47 +30273,47 @@
       </c>
       <c r="C105" s="11" t="inlineStr">
         <is>
-          <t>≥ 10.10.2026</t>
+          <t>≥ 24.11.2026</t>
         </is>
       </c>
       <c r="D105" s="11" t="inlineStr">
         <is>
-          <t>P050192</t>
+          <t>P050222</t>
         </is>
       </c>
       <c r="E105" s="11" t="inlineStr">
         <is>
-          <t>BSS052501</t>
+          <t>CJ062501/1</t>
         </is>
       </c>
       <c r="F105" s="11" t="inlineStr">
         <is>
-          <t>Blue Sunset Sherbet</t>
+          <t>Cap Junky</t>
         </is>
       </c>
       <c r="G105" s="9" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>III</t>
         </is>
       </c>
       <c r="H105" s="9" t="inlineStr">
         <is>
-          <t>THC 20</t>
+          <t>THC 24</t>
         </is>
       </c>
       <c r="I105" s="9" t="inlineStr">
         <is>
-          <t>20.52</t>
+          <t>24.80</t>
         </is>
       </c>
       <c r="J105" s="12" t="inlineStr">
         <is>
-          <t>18.00 – 21.99 %  (grade II, class THC 20, nominal 20.00 ± 2.00)</t>
+          <t>21.60 – 26.39 %  (grade III, class THC 24, nominal 24.00 ± 2.40)</t>
         </is>
       </c>
       <c r="K105" s="11" t="inlineStr">
         <is>
-          <t>iCoA-PP-2025-0017</t>
+          <t>iCoA-PP-2025-0018</t>
         </is>
       </c>
       <c r="L105" s="9" t="n">
@@ -30329,7 +30337,11 @@
           <t>Farmahem — Ident A + B + C with the Assay, at retest; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
-      <c r="S105" s="12" t="inlineStr"/>
+      <c r="S105" s="17" t="inlineStr">
+        <is>
+          <t>QCSP 001 prints 23.00 – 25.00 % for this lot; the issue plan's grade range is 21.60 – 26.39 %. Recorded, not resolved.</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="6" t="inlineStr">
@@ -30344,47 +30356,47 @@
       </c>
       <c r="C106" s="6" t="inlineStr">
         <is>
-          <t>≥ 24.11.2026</t>
+          <t>≥ 03.12.2026</t>
         </is>
       </c>
       <c r="D106" s="6" t="inlineStr">
         <is>
-          <t>P050222</t>
+          <t>P050282</t>
         </is>
       </c>
       <c r="E106" s="6" t="inlineStr">
         <is>
-          <t>CJ062501/1</t>
+          <t>CLE072501</t>
         </is>
       </c>
       <c r="F106" s="6" t="inlineStr">
         <is>
-          <t>Cap Junky</t>
+          <t>Clemosa A Bud</t>
         </is>
       </c>
       <c r="G106" s="5" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>I</t>
         </is>
       </c>
       <c r="H106" s="5" t="inlineStr">
         <is>
-          <t>THC 24</t>
+          <t>THC 8</t>
         </is>
       </c>
       <c r="I106" s="5" t="inlineStr">
         <is>
-          <t>24.80</t>
+          <t>8.65</t>
         </is>
       </c>
       <c r="J106" s="7" t="inlineStr">
         <is>
-          <t>21.60 – 26.39 %  (grade III, class THC 24, nominal 24.00 ± 2.40)</t>
+          <t>7.20 – 8.79 %  (grade I, class THC 8, nominal 8.00 ± 0.80)</t>
         </is>
       </c>
       <c r="K106" s="6" t="inlineStr">
         <is>
-          <t>iCoA-PP-2025-0018</t>
+          <t>iCoA-PP-2025-0019</t>
         </is>
       </c>
       <c r="L106" s="5" t="n">
@@ -30408,11 +30420,7 @@
           <t>Farmahem — Ident A + B + C with the Assay, at retest; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
-      <c r="S106" s="17" t="inlineStr">
-        <is>
-          <t>QCSP 001 prints 23.00 – 25.00 % for this lot; the issue plan's grade range is 21.60 – 26.39 %. Recorded, not resolved.</t>
-        </is>
-      </c>
+      <c r="S106" s="7" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="11" t="inlineStr">
@@ -30427,47 +30435,47 @@
       </c>
       <c r="C107" s="11" t="inlineStr">
         <is>
-          <t>≥ 03.12.2026</t>
+          <t>≥ 22.12.2026</t>
         </is>
       </c>
       <c r="D107" s="11" t="inlineStr">
         <is>
-          <t>P050282</t>
+          <t>P050302</t>
         </is>
       </c>
       <c r="E107" s="11" t="inlineStr">
         <is>
-          <t>CLE072501</t>
+          <t>GP072501/2</t>
         </is>
       </c>
       <c r="F107" s="11" t="inlineStr">
         <is>
-          <t>Clemosa A Bud</t>
+          <t>Grape Pie</t>
         </is>
       </c>
       <c r="G107" s="9" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>IV</t>
         </is>
       </c>
       <c r="H107" s="9" t="inlineStr">
         <is>
-          <t>THC 8</t>
+          <t>THC 18</t>
         </is>
       </c>
       <c r="I107" s="9" t="inlineStr">
         <is>
-          <t>8.65</t>
+          <t>18.29</t>
         </is>
       </c>
       <c r="J107" s="12" t="inlineStr">
         <is>
-          <t>7.20 – 8.79 %  (grade I, class THC 8, nominal 8.00 ± 0.80)</t>
+          <t>16.20 – 19.79 %  (grade IV, class THC 18, nominal 18.00 ± 1.80)</t>
         </is>
       </c>
       <c r="K107" s="11" t="inlineStr">
         <is>
-          <t>iCoA-PP-2025-0019</t>
+          <t>iCoA-PP-2025-0020</t>
         </is>
       </c>
       <c r="L107" s="9" t="n">
@@ -30491,7 +30499,11 @@
           <t>Farmahem — Ident A + B + C with the Assay, at retest; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
-      <c r="S107" s="12" t="inlineStr"/>
+      <c r="S107" s="17" t="inlineStr">
+        <is>
+          <t>QCSP 001 prints 18.00 – 22.00 % for this lot; the issue plan's grade range is 16.20 – 19.79 %. Recorded, not resolved.</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="6" t="inlineStr">
@@ -30506,17 +30518,17 @@
       </c>
       <c r="C108" s="6" t="inlineStr">
         <is>
-          <t>≥ 22.12.2026</t>
+          <t>≥ 23.12.2026</t>
         </is>
       </c>
       <c r="D108" s="6" t="inlineStr">
         <is>
-          <t>P050302</t>
+          <t>P050312</t>
         </is>
       </c>
       <c r="E108" s="6" t="inlineStr">
         <is>
-          <t>GP072501/2</t>
+          <t>GP082501/1</t>
         </is>
       </c>
       <c r="F108" s="6" t="inlineStr">
@@ -30526,27 +30538,27 @@
       </c>
       <c r="G108" s="5" t="inlineStr">
         <is>
-          <t>IV</t>
+          <t>II</t>
         </is>
       </c>
       <c r="H108" s="5" t="inlineStr">
         <is>
-          <t>THC 18</t>
+          <t>THC 26</t>
         </is>
       </c>
       <c r="I108" s="5" t="inlineStr">
         <is>
-          <t>18.29</t>
+          <t>25.13</t>
         </is>
       </c>
       <c r="J108" s="7" t="inlineStr">
         <is>
-          <t>16.20 – 19.79 %  (grade IV, class THC 18, nominal 18.00 ± 1.80)</t>
+          <t>23.40 – 28.59 %  (grade II, class THC 26, nominal 26.00 ± 2.60)</t>
         </is>
       </c>
       <c r="K108" s="6" t="inlineStr">
         <is>
-          <t>iCoA-PP-2025-0020</t>
+          <t>iCoA-PP-2025-0021</t>
         </is>
       </c>
       <c r="L108" s="5" t="n">
@@ -30572,7 +30584,7 @@
       </c>
       <c r="S108" s="17" t="inlineStr">
         <is>
-          <t>QCSP 001 prints 18.00 – 22.00 % for this lot; the issue plan's grade range is 16.20 – 19.79 %. Recorded, not resolved.</t>
+          <t>QCSP 001 prints 25.40 – 26.60 % for this lot; the issue plan's grade range is 23.40 – 28.59 %. Recorded, not resolved.</t>
         </is>
       </c>
     </row>
@@ -30589,17 +30601,17 @@
       </c>
       <c r="C109" s="11" t="inlineStr">
         <is>
-          <t>≥ 23.12.2026</t>
+          <t>≥ 10.08.2026</t>
         </is>
       </c>
       <c r="D109" s="11" t="inlineStr">
         <is>
-          <t>P050312</t>
+          <t>P050322</t>
         </is>
       </c>
       <c r="E109" s="11" t="inlineStr">
         <is>
-          <t>GP082501/1</t>
+          <t>GP082501/2</t>
         </is>
       </c>
       <c r="F109" s="11" t="inlineStr">
@@ -30609,34 +30621,34 @@
       </c>
       <c r="G109" s="9" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H109" s="9" t="inlineStr">
         <is>
-          <t>THC 26</t>
+          <t>THC 16</t>
         </is>
       </c>
       <c r="I109" s="9" t="inlineStr">
         <is>
-          <t>25.13</t>
+          <t>15.70</t>
         </is>
       </c>
       <c r="J109" s="12" t="inlineStr">
         <is>
-          <t>23.40 – 28.59 %  (grade II, class THC 26, nominal 26.00 ± 2.60)</t>
+          <t>14.40 – 17.59 %  (grade V, class THC 16, nominal 16.00 ± 1.60)</t>
         </is>
       </c>
       <c r="K109" s="11" t="inlineStr">
         <is>
-          <t>iCoA-PP-2025-0021</t>
+          <t>iCoA-PP-2025-0022</t>
         </is>
       </c>
       <c r="L109" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M109" s="9" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="N109" s="9" t="n">
         <v>0</v>
@@ -30645,19 +30657,19 @@
         <v>0</v>
       </c>
       <c r="P109" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q109" s="12" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="Q109" s="12" t="inlineStr">
+        <is>
+          <t>197-12-К/26; 197-12-М/26</t>
+        </is>
+      </c>
       <c r="R109" s="12" t="inlineStr">
         <is>
           <t>Farmahem — Ident A + B + C with the Assay, at retest; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
-      <c r="S109" s="17" t="inlineStr">
-        <is>
-          <t>QCSP 001 prints 25.40 – 26.60 % for this lot; the issue plan's grade range is 23.40 – 28.59 %. Recorded, not resolved.</t>
-        </is>
-      </c>
+      <c r="S109" s="12" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="6" t="inlineStr">
@@ -30672,54 +30684,54 @@
       </c>
       <c r="C110" s="6" t="inlineStr">
         <is>
-          <t>≥ 10.08.2026</t>
+          <t>≥ 13.01.2027</t>
         </is>
       </c>
       <c r="D110" s="6" t="inlineStr">
         <is>
-          <t>P050322</t>
+          <t>P060012</t>
         </is>
       </c>
       <c r="E110" s="6" t="inlineStr">
         <is>
-          <t>GP082501/2</t>
+          <t>WC082501</t>
         </is>
       </c>
       <c r="F110" s="6" t="inlineStr">
         <is>
-          <t>Grape Pie</t>
+          <t>Wedding Crusher</t>
         </is>
       </c>
       <c r="G110" s="5" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>I</t>
         </is>
       </c>
       <c r="H110" s="5" t="inlineStr">
         <is>
-          <t>THC 16</t>
+          <t>THC 24</t>
         </is>
       </c>
       <c r="I110" s="5" t="inlineStr">
         <is>
-          <t>15.70</t>
+          <t>23.48</t>
         </is>
       </c>
       <c r="J110" s="7" t="inlineStr">
         <is>
-          <t>14.40 – 17.59 %  (grade V, class THC 16, nominal 16.00 ± 1.60)</t>
+          <t>21.60 – 26.39 %  (grade I, class THC 24, nominal 24.00 ± 2.40)</t>
         </is>
       </c>
       <c r="K110" s="6" t="inlineStr">
         <is>
-          <t>iCoA-PP-2025-0022</t>
+          <t>iCoA-PP-2026-0001</t>
         </is>
       </c>
       <c r="L110" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M110" s="5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="N110" s="5" t="n">
         <v>0</v>
@@ -30728,19 +30740,19 @@
         <v>0</v>
       </c>
       <c r="P110" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q110" s="7" t="inlineStr">
-        <is>
-          <t>197-12-К/26; 197-12-М/26</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q110" s="7" t="inlineStr"/>
       <c r="R110" s="7" t="inlineStr">
         <is>
           <t>Farmahem — Ident A + B + C with the Assay, at retest; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
-      <c r="S110" s="7" t="inlineStr"/>
+      <c r="S110" s="17" t="inlineStr">
+        <is>
+          <t>QCSP 001 prints 19.80 – 24.20 % for this lot; the issue plan's grade range is 21.60 – 26.39 %. Recorded, not resolved.</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="11" t="inlineStr">
@@ -30755,22 +30767,22 @@
       </c>
       <c r="C111" s="11" t="inlineStr">
         <is>
-          <t>≥ 13.01.2027</t>
+          <t>≥ 16.01.2027</t>
         </is>
       </c>
       <c r="D111" s="11" t="inlineStr">
         <is>
-          <t>P060012</t>
+          <t>P060022</t>
         </is>
       </c>
       <c r="E111" s="11" t="inlineStr">
         <is>
-          <t>WC082501</t>
+          <t>CJ082501/1</t>
         </is>
       </c>
       <c r="F111" s="11" t="inlineStr">
         <is>
-          <t>Wedding Crusher</t>
+          <t>Cap Junky</t>
         </is>
       </c>
       <c r="G111" s="9" t="inlineStr">
@@ -30780,22 +30792,22 @@
       </c>
       <c r="H111" s="9" t="inlineStr">
         <is>
-          <t>THC 24</t>
+          <t>THC 28</t>
         </is>
       </c>
       <c r="I111" s="9" t="inlineStr">
         <is>
-          <t>23.48</t>
+          <t>28.34</t>
         </is>
       </c>
       <c r="J111" s="12" t="inlineStr">
         <is>
-          <t>21.60 – 26.39 %  (grade I, class THC 24, nominal 24.00 ± 2.40)</t>
+          <t>25.20 – 30.79 %  (grade I, class THC 28, nominal 28.00 ± 2.80)</t>
         </is>
       </c>
       <c r="K111" s="11" t="inlineStr">
         <is>
-          <t>iCoA-PP-2026-0001</t>
+          <t>iCoA-PP-2026-0002</t>
         </is>
       </c>
       <c r="L111" s="9" t="n">
@@ -30821,7 +30833,7 @@
       </c>
       <c r="S111" s="17" t="inlineStr">
         <is>
-          <t>QCSP 001 prints 19.80 – 24.20 % for this lot; the issue plan's grade range is 21.60 – 26.39 %. Recorded, not resolved.</t>
+          <t>QCSP 001 prints 27.00 – 29.00 % for this lot; the issue plan's grade range is 25.20 – 30.79 %. Recorded, not resolved.</t>
         </is>
       </c>
     </row>
@@ -30838,17 +30850,17 @@
       </c>
       <c r="C112" s="6" t="inlineStr">
         <is>
-          <t>≥ 16.01.2027</t>
+          <t>≥ 10.08.2026</t>
         </is>
       </c>
       <c r="D112" s="6" t="inlineStr">
         <is>
-          <t>P060022</t>
+          <t>P060032</t>
         </is>
       </c>
       <c r="E112" s="6" t="inlineStr">
         <is>
-          <t>CJ082501/1</t>
+          <t>CJ082501/2</t>
         </is>
       </c>
       <c r="F112" s="6" t="inlineStr">
@@ -30858,34 +30870,34 @@
       </c>
       <c r="G112" s="5" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>IV</t>
         </is>
       </c>
       <c r="H112" s="5" t="inlineStr">
         <is>
-          <t>THC 28</t>
+          <t>THC 20</t>
         </is>
       </c>
       <c r="I112" s="5" t="inlineStr">
         <is>
-          <t>28.34</t>
+          <t>18.29</t>
         </is>
       </c>
       <c r="J112" s="7" t="inlineStr">
         <is>
-          <t>25.20 – 30.79 %  (grade I, class THC 28, nominal 28.00 ± 2.80)</t>
+          <t>18.00 – 21.99 %  (grade IV, class THC 20, nominal 20.00 ± 2.00)</t>
         </is>
       </c>
       <c r="K112" s="6" t="inlineStr">
         <is>
-          <t>iCoA-PP-2026-0002</t>
+          <t>iCoA-PP-2026-0003</t>
         </is>
       </c>
       <c r="L112" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M112" s="5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="N112" s="5" t="n">
         <v>0</v>
@@ -30894,19 +30906,19 @@
         <v>0</v>
       </c>
       <c r="P112" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q112" s="7" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="Q112" s="7" t="inlineStr">
+        <is>
+          <t>197-5-К/26; 197-5-М/26</t>
+        </is>
+      </c>
       <c r="R112" s="7" t="inlineStr">
         <is>
           <t>Farmahem — Ident A + B + C with the Assay, at retest; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
-      <c r="S112" s="17" t="inlineStr">
-        <is>
-          <t>QCSP 001 prints 27.00 – 29.00 % for this lot; the issue plan's grade range is 25.20 – 30.79 %. Recorded, not resolved.</t>
-        </is>
-      </c>
+      <c r="S112" s="7" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="11" t="inlineStr">
@@ -30921,22 +30933,22 @@
       </c>
       <c r="C113" s="11" t="inlineStr">
         <is>
-          <t>≥ 10.08.2026</t>
+          <t>≥ 29.01.2027</t>
         </is>
       </c>
       <c r="D113" s="11" t="inlineStr">
         <is>
-          <t>P060032</t>
+          <t>P060042</t>
         </is>
       </c>
       <c r="E113" s="11" t="inlineStr">
         <is>
-          <t>CJ082501/2</t>
+          <t>OPM092501</t>
         </is>
       </c>
       <c r="F113" s="11" t="inlineStr">
         <is>
-          <t>Cap Junky</t>
+          <t>Orange Punch Mimosa</t>
         </is>
       </c>
       <c r="G113" s="9" t="inlineStr">
@@ -30946,29 +30958,29 @@
       </c>
       <c r="H113" s="9" t="inlineStr">
         <is>
-          <t>THC 20</t>
+          <t>THC 10</t>
         </is>
       </c>
       <c r="I113" s="9" t="inlineStr">
         <is>
-          <t>18.29</t>
+          <t>10.18</t>
         </is>
       </c>
       <c r="J113" s="12" t="inlineStr">
         <is>
-          <t>18.00 – 21.99 %  (grade IV, class THC 20, nominal 20.00 ± 2.00)</t>
+          <t>9.00 – 10.99 %  (grade IV, class THC 10, nominal 10.00 ± 1.00)</t>
         </is>
       </c>
       <c r="K113" s="11" t="inlineStr">
         <is>
-          <t>iCoA-PP-2026-0003</t>
+          <t>iCoA-PP-2026-0004</t>
         </is>
       </c>
       <c r="L113" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M113" s="9" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="N113" s="9" t="n">
         <v>0</v>
@@ -30977,13 +30989,9 @@
         <v>0</v>
       </c>
       <c r="P113" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q113" s="12" t="inlineStr">
-        <is>
-          <t>197-5-К/26; 197-5-М/26</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q113" s="12" t="inlineStr"/>
       <c r="R113" s="12" t="inlineStr">
         <is>
           <t>Farmahem — Ident A + B + C with the Assay, at retest; Purely Plant laboratory — iCoA covering Foreign matter</t>
@@ -31004,54 +31012,54 @@
       </c>
       <c r="C114" s="6" t="inlineStr">
         <is>
-          <t>≥ 29.01.2027</t>
+          <t>≥ 10.08.2026</t>
         </is>
       </c>
       <c r="D114" s="6" t="inlineStr">
         <is>
-          <t>P060042</t>
+          <t>P060062</t>
         </is>
       </c>
       <c r="E114" s="6" t="inlineStr">
         <is>
-          <t>OPM092501</t>
+          <t>PM092501</t>
         </is>
       </c>
       <c r="F114" s="6" t="inlineStr">
         <is>
-          <t>Orange Punch Mimosa</t>
+          <t>Permanent Marker</t>
         </is>
       </c>
       <c r="G114" s="5" t="inlineStr">
         <is>
-          <t>IV</t>
+          <t>I</t>
         </is>
       </c>
       <c r="H114" s="5" t="inlineStr">
         <is>
-          <t>THC 10</t>
+          <t>THC 12</t>
         </is>
       </c>
       <c r="I114" s="5" t="inlineStr">
         <is>
-          <t>10.18</t>
+          <t>12.25</t>
         </is>
       </c>
       <c r="J114" s="7" t="inlineStr">
         <is>
-          <t>9.00 – 10.99 %  (grade IV, class THC 10, nominal 10.00 ± 1.00)</t>
+          <t>10.80 – 13.19 %  (grade I, class THC 12, nominal 12.00 ± 1.20)</t>
         </is>
       </c>
       <c r="K114" s="6" t="inlineStr">
         <is>
-          <t>iCoA-PP-2026-0004</t>
+          <t>iCoA-PP-2026-0005</t>
         </is>
       </c>
       <c r="L114" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M114" s="5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="N114" s="5" t="n">
         <v>0</v>
@@ -31060,15 +31068,23 @@
         <v>0</v>
       </c>
       <c r="P114" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q114" s="7" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="Q114" s="7" t="inlineStr">
+        <is>
+          <t>197-20-К/26; 197-20-М/26</t>
+        </is>
+      </c>
       <c r="R114" s="7" t="inlineStr">
         <is>
           <t>Farmahem — Ident A + B + C with the Assay, at retest; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
-      <c r="S114" s="7" t="inlineStr"/>
+      <c r="S114" s="17" t="inlineStr">
+        <is>
+          <t>QCSP 001 prints 11.01 – 12.99 % for this lot; the issue plan's grade range is 10.80 – 13.19 %. Recorded, not resolved.</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="11" t="inlineStr">
@@ -31083,54 +31099,54 @@
       </c>
       <c r="C115" s="11" t="inlineStr">
         <is>
-          <t>≥ 10.08.2026</t>
+          <t>≥ 02.02.2027</t>
         </is>
       </c>
       <c r="D115" s="11" t="inlineStr">
         <is>
-          <t>P060062</t>
+          <t>P060072</t>
         </is>
       </c>
       <c r="E115" s="11" t="inlineStr">
         <is>
-          <t>PM092501</t>
+          <t>CJ092501</t>
         </is>
       </c>
       <c r="F115" s="11" t="inlineStr">
         <is>
-          <t>Permanent Marker</t>
+          <t>Cap Junky</t>
         </is>
       </c>
       <c r="G115" s="9" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
       <c r="H115" s="9" t="inlineStr">
         <is>
-          <t>THC 12</t>
+          <t>THC 26</t>
         </is>
       </c>
       <c r="I115" s="9" t="inlineStr">
         <is>
-          <t>12.25</t>
+          <t>25.65</t>
         </is>
       </c>
       <c r="J115" s="12" t="inlineStr">
         <is>
-          <t>10.80 – 13.19 %  (grade I, class THC 12, nominal 12.00 ± 1.20)</t>
+          <t>23.40 – 28.59 %  (grade II, class THC 26, nominal 26.00 ± 2.60)</t>
         </is>
       </c>
       <c r="K115" s="11" t="inlineStr">
         <is>
-          <t>iCoA-PP-2026-0005</t>
+          <t>iCoA-PP-2026-0006</t>
         </is>
       </c>
       <c r="L115" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M115" s="9" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="N115" s="9" t="n">
         <v>0</v>
@@ -31139,13 +31155,9 @@
         <v>0</v>
       </c>
       <c r="P115" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q115" s="12" t="inlineStr">
-        <is>
-          <t>197-20-К/26; 197-20-М/26</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q115" s="12" t="inlineStr"/>
       <c r="R115" s="12" t="inlineStr">
         <is>
           <t>Farmahem — Ident A + B + C with the Assay, at retest; Purely Plant laboratory — iCoA covering Foreign matter</t>
@@ -31153,7 +31165,7 @@
       </c>
       <c r="S115" s="17" t="inlineStr">
         <is>
-          <t>QCSP 001 prints 11.01 – 12.99 % for this lot; the issue plan's grade range is 10.80 – 13.19 %. Recorded, not resolved.</t>
+          <t>QCSP 001 prints 25.01 – 26.99 % for this lot; the issue plan's grade range is 23.40 – 28.59 %. Recorded, not resolved.</t>
         </is>
       </c>
     </row>
@@ -31175,42 +31187,42 @@
       </c>
       <c r="D116" s="6" t="inlineStr">
         <is>
-          <t>P060072</t>
+          <t>P060082</t>
         </is>
       </c>
       <c r="E116" s="6" t="inlineStr">
         <is>
-          <t>CJ092501</t>
+          <t>SJ092501</t>
         </is>
       </c>
       <c r="F116" s="6" t="inlineStr">
         <is>
-          <t>Cap Junky</t>
+          <t>Sleepy Joe</t>
         </is>
       </c>
       <c r="G116" s="5" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
       <c r="H116" s="5" t="inlineStr">
         <is>
-          <t>THC 26</t>
+          <t>THC 10</t>
         </is>
       </c>
       <c r="I116" s="5" t="inlineStr">
         <is>
-          <t>25.65</t>
+          <t>10.39</t>
         </is>
       </c>
       <c r="J116" s="7" t="inlineStr">
         <is>
-          <t>23.40 – 28.59 %  (grade II, class THC 26, nominal 26.00 ± 2.60)</t>
+          <t>9.00 – 10.99 %  (grade I, class THC 10, nominal 10.00 ± 1.00)</t>
         </is>
       </c>
       <c r="K116" s="6" t="inlineStr">
         <is>
-          <t>iCoA-PP-2026-0006</t>
+          <t>iCoA-PP-2026-0007</t>
         </is>
       </c>
       <c r="L116" s="5" t="n">
@@ -31234,11 +31246,7 @@
           <t>Farmahem — Ident A + B + C with the Assay, at retest; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
-      <c r="S116" s="17" t="inlineStr">
-        <is>
-          <t>QCSP 001 prints 25.01 – 26.99 % for this lot; the issue plan's grade range is 23.40 – 28.59 %. Recorded, not resolved.</t>
-        </is>
-      </c>
+      <c r="S116" s="7" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="11" t="inlineStr">
@@ -31253,47 +31261,47 @@
       </c>
       <c r="C117" s="11" t="inlineStr">
         <is>
-          <t>≥ 02.02.2027</t>
+          <t>≥ 03.02.2027</t>
         </is>
       </c>
       <c r="D117" s="11" t="inlineStr">
         <is>
-          <t>P060082</t>
+          <t>P060092</t>
         </is>
       </c>
       <c r="E117" s="11" t="inlineStr">
         <is>
-          <t>SJ092501</t>
+          <t>GP092501</t>
         </is>
       </c>
       <c r="F117" s="11" t="inlineStr">
         <is>
-          <t>Sleepy Joe</t>
+          <t>Grape Pie</t>
         </is>
       </c>
       <c r="G117" s="9" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
       <c r="H117" s="9" t="inlineStr">
         <is>
-          <t>THC 10</t>
+          <t>THC 26</t>
         </is>
       </c>
       <c r="I117" s="9" t="inlineStr">
         <is>
-          <t>10.39</t>
+          <t>25.24</t>
         </is>
       </c>
       <c r="J117" s="12" t="inlineStr">
         <is>
-          <t>9.00 – 10.99 %  (grade I, class THC 10, nominal 10.00 ± 1.00)</t>
+          <t>23.40 – 28.59 %  (grade II, class THC 26, nominal 26.00 ± 2.60)</t>
         </is>
       </c>
       <c r="K117" s="11" t="inlineStr">
         <is>
-          <t>iCoA-PP-2026-0007</t>
+          <t>iCoA-PP-2026-0008</t>
         </is>
       </c>
       <c r="L117" s="9" t="n">
@@ -31317,7 +31325,11 @@
           <t>Farmahem — Ident A + B + C with the Assay, at retest; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
-      <c r="S117" s="12" t="inlineStr"/>
+      <c r="S117" s="17" t="inlineStr">
+        <is>
+          <t>QCSP 001 prints 25.40 – 26.60 % for this lot; the issue plan's grade range is 23.40 – 28.59 %. Recorded, not resolved.</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="6" t="inlineStr">
@@ -31332,47 +31344,47 @@
       </c>
       <c r="C118" s="6" t="inlineStr">
         <is>
-          <t>≥ 03.02.2027</t>
+          <t>≥ 17.02.2027</t>
         </is>
       </c>
       <c r="D118" s="6" t="inlineStr">
         <is>
-          <t>P060092</t>
+          <t>P060112</t>
         </is>
       </c>
       <c r="E118" s="6" t="inlineStr">
         <is>
-          <t>GP092501</t>
+          <t>PUM102501</t>
         </is>
       </c>
       <c r="F118" s="6" t="inlineStr">
         <is>
-          <t>Grape Pie</t>
+          <t>Pure Michigen</t>
         </is>
       </c>
       <c r="G118" s="5" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
       <c r="H118" s="5" t="inlineStr">
         <is>
-          <t>THC 26</t>
+          <t>THC 14</t>
         </is>
       </c>
       <c r="I118" s="5" t="inlineStr">
         <is>
-          <t>25.24</t>
+          <t>13.95</t>
         </is>
       </c>
       <c r="J118" s="7" t="inlineStr">
         <is>
-          <t>23.40 – 28.59 %  (grade II, class THC 26, nominal 26.00 ± 2.60)</t>
+          <t>12.60 – 15.39 %  (grade I, class THC 14, nominal 14.00 ± 1.40)</t>
         </is>
       </c>
       <c r="K118" s="6" t="inlineStr">
         <is>
-          <t>iCoA-PP-2026-0008</t>
+          <t>iCoA-PP-2026-0009</t>
         </is>
       </c>
       <c r="L118" s="5" t="n">
@@ -31396,9 +31408,9 @@
           <t>Farmahem — Ident A + B + C with the Assay, at retest; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
-      <c r="S118" s="17" t="inlineStr">
-        <is>
-          <t>QCSP 001 prints 25.40 – 26.60 % for this lot; the issue plan's grade range is 23.40 – 28.59 %. Recorded, not resolved.</t>
+      <c r="S118" s="18" t="inlineStr">
+        <is>
+          <t>No eCoA on file for this cultivation batch — locate the physical certificates, scan and upload.</t>
         </is>
       </c>
     </row>
@@ -31415,22 +31427,22 @@
       </c>
       <c r="C119" s="11" t="inlineStr">
         <is>
-          <t>≥ 17.02.2027</t>
+          <t>≥ 18.02.2027</t>
         </is>
       </c>
       <c r="D119" s="11" t="inlineStr">
         <is>
-          <t>P060112</t>
+          <t>P060122</t>
         </is>
       </c>
       <c r="E119" s="11" t="inlineStr">
         <is>
-          <t>PUM102501</t>
+          <t>ACC102501</t>
         </is>
       </c>
       <c r="F119" s="11" t="inlineStr">
         <is>
-          <t>Pure Michigen</t>
+          <t>Amnesia Core Cut</t>
         </is>
       </c>
       <c r="G119" s="9" t="inlineStr">
@@ -31440,22 +31452,22 @@
       </c>
       <c r="H119" s="9" t="inlineStr">
         <is>
-          <t>THC 14</t>
+          <t>THC 12</t>
         </is>
       </c>
       <c r="I119" s="9" t="inlineStr">
         <is>
-          <t>13.95</t>
+          <t>12.09</t>
         </is>
       </c>
       <c r="J119" s="12" t="inlineStr">
         <is>
-          <t>12.60 – 15.39 %  (grade I, class THC 14, nominal 14.00 ± 1.40)</t>
+          <t>10.80 – 13.19 %  (grade I, class THC 12, nominal 12.00 ± 1.20)</t>
         </is>
       </c>
       <c r="K119" s="11" t="inlineStr">
         <is>
-          <t>iCoA-PP-2026-0009</t>
+          <t>iCoA-PP-2026-0010</t>
         </is>
       </c>
       <c r="L119" s="9" t="n">
@@ -31498,22 +31510,22 @@
       </c>
       <c r="C120" s="6" t="inlineStr">
         <is>
-          <t>≥ 18.02.2027</t>
+          <t>≥ 19.02.2027</t>
         </is>
       </c>
       <c r="D120" s="6" t="inlineStr">
         <is>
-          <t>P060122</t>
+          <t>P060132</t>
         </is>
       </c>
       <c r="E120" s="6" t="inlineStr">
         <is>
-          <t>ACC102501</t>
+          <t>CF102501</t>
         </is>
       </c>
       <c r="F120" s="6" t="inlineStr">
         <is>
-          <t>Amnesia Core Cut</t>
+          <t>Chem Flyer</t>
         </is>
       </c>
       <c r="G120" s="5" t="inlineStr">
@@ -31523,22 +31535,22 @@
       </c>
       <c r="H120" s="5" t="inlineStr">
         <is>
-          <t>THC 12</t>
+          <t>THC 10</t>
         </is>
       </c>
       <c r="I120" s="5" t="inlineStr">
         <is>
-          <t>12.09</t>
+          <t>9.55</t>
         </is>
       </c>
       <c r="J120" s="7" t="inlineStr">
         <is>
-          <t>10.80 – 13.19 %  (grade I, class THC 12, nominal 12.00 ± 1.20)</t>
+          <t>9.00 – 10.99 %  (grade I, class THC 10, nominal 10.00 ± 1.00)</t>
         </is>
       </c>
       <c r="K120" s="6" t="inlineStr">
         <is>
-          <t>iCoA-PP-2026-0010</t>
+          <t>iCoA-PP-2026-0011</t>
         </is>
       </c>
       <c r="L120" s="5" t="n">
@@ -31581,22 +31593,22 @@
       </c>
       <c r="C121" s="11" t="inlineStr">
         <is>
-          <t>≥ 19.02.2027</t>
+          <t>≥ 10.08.2026</t>
         </is>
       </c>
       <c r="D121" s="11" t="inlineStr">
         <is>
-          <t>P060132</t>
+          <t>P060152</t>
         </is>
       </c>
       <c r="E121" s="11" t="inlineStr">
         <is>
-          <t>CF102501</t>
+          <t>J31102501</t>
         </is>
       </c>
       <c r="F121" s="11" t="inlineStr">
         <is>
-          <t>Chem Flyer</t>
+          <t>Jokerz 31</t>
         </is>
       </c>
       <c r="G121" s="9" t="inlineStr">
@@ -31606,29 +31618,29 @@
       </c>
       <c r="H121" s="9" t="inlineStr">
         <is>
-          <t>THC 10</t>
+          <t>THC 18</t>
         </is>
       </c>
       <c r="I121" s="9" t="inlineStr">
         <is>
-          <t>9.55</t>
+          <t>17.32</t>
         </is>
       </c>
       <c r="J121" s="12" t="inlineStr">
         <is>
-          <t>9.00 – 10.99 %  (grade I, class THC 10, nominal 10.00 ± 1.00)</t>
+          <t>16.20 – 19.79 %  (grade I, class THC 18, nominal 18.00 ± 1.80)</t>
         </is>
       </c>
       <c r="K121" s="11" t="inlineStr">
         <is>
-          <t>iCoA-PP-2026-0011</t>
+          <t>iCoA-PP-2026-0012</t>
         </is>
       </c>
       <c r="L121" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M121" s="9" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="N121" s="9" t="n">
         <v>0</v>
@@ -31637,19 +31649,19 @@
         <v>0</v>
       </c>
       <c r="P121" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q121" s="12" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="Q121" s="12" t="inlineStr">
+        <is>
+          <t>197-16-К/26; 197-16-М/26</t>
+        </is>
+      </c>
       <c r="R121" s="12" t="inlineStr">
         <is>
           <t>Farmahem — Ident A + B + C with the Assay, at retest; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
-      <c r="S121" s="18" t="inlineStr">
-        <is>
-          <t>No eCoA on file for this cultivation batch — locate the physical certificates, scan and upload.</t>
-        </is>
-      </c>
+      <c r="S121" s="12" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="6" t="inlineStr">
@@ -31664,22 +31676,22 @@
       </c>
       <c r="C122" s="6" t="inlineStr">
         <is>
-          <t>≥ 10.08.2026</t>
+          <t>≥ 12.03.2027</t>
         </is>
       </c>
       <c r="D122" s="6" t="inlineStr">
         <is>
-          <t>P060152</t>
+          <t>P060172</t>
         </is>
       </c>
       <c r="E122" s="6" t="inlineStr">
         <is>
-          <t>J31102501</t>
+          <t>KC102501</t>
         </is>
       </c>
       <c r="F122" s="6" t="inlineStr">
         <is>
-          <t>Jokerz 31</t>
+          <t>Kush Crasher</t>
         </is>
       </c>
       <c r="G122" s="5" t="inlineStr">
@@ -31689,29 +31701,29 @@
       </c>
       <c r="H122" s="5" t="inlineStr">
         <is>
-          <t>THC 18</t>
+          <t>THC 16</t>
         </is>
       </c>
       <c r="I122" s="5" t="inlineStr">
         <is>
-          <t>17.32</t>
+          <t>17.06</t>
         </is>
       </c>
       <c r="J122" s="7" t="inlineStr">
         <is>
-          <t>16.20 – 19.79 %  (grade I, class THC 18, nominal 18.00 ± 1.80)</t>
+          <t>14.40 – 17.59 %  (grade I, class THC 16, nominal 16.00 ± 1.60)</t>
         </is>
       </c>
       <c r="K122" s="6" t="inlineStr">
         <is>
-          <t>iCoA-PP-2026-0012</t>
+          <t>iCoA-PP-2026-0013</t>
         </is>
       </c>
       <c r="L122" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M122" s="5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="N122" s="5" t="n">
         <v>0</v>
@@ -31720,19 +31732,19 @@
         <v>0</v>
       </c>
       <c r="P122" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q122" s="7" t="inlineStr">
-        <is>
-          <t>197-16-К/26; 197-16-М/26</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q122" s="7" t="inlineStr"/>
       <c r="R122" s="7" t="inlineStr">
         <is>
           <t>Farmahem — Ident A + B + C with the Assay, at retest; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
-      <c r="S122" s="7" t="inlineStr"/>
+      <c r="S122" s="17" t="inlineStr">
+        <is>
+          <t>QCSP 001 prints 16.20 – 19.80 % for this lot; the issue plan's grade range is 14.40 – 17.59 %. Recorded, not resolved.</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="11" t="inlineStr">
@@ -31747,22 +31759,22 @@
       </c>
       <c r="C123" s="11" t="inlineStr">
         <is>
-          <t>≥ 12.03.2027</t>
+          <t>≥ 14.03.2027</t>
         </is>
       </c>
       <c r="D123" s="11" t="inlineStr">
         <is>
-          <t>P060172</t>
+          <t>P060182</t>
         </is>
       </c>
       <c r="E123" s="11" t="inlineStr">
         <is>
-          <t>KC102501</t>
+          <t>GRC102501/2</t>
         </is>
       </c>
       <c r="F123" s="11" t="inlineStr">
         <is>
-          <t>Kush Crasher</t>
+          <t>Grapes and Cream</t>
         </is>
       </c>
       <c r="G123" s="9" t="inlineStr">
@@ -31772,22 +31784,22 @@
       </c>
       <c r="H123" s="9" t="inlineStr">
         <is>
-          <t>THC 16</t>
+          <t>THC 10</t>
         </is>
       </c>
       <c r="I123" s="9" t="inlineStr">
         <is>
-          <t>17.06</t>
+          <t>9.80</t>
         </is>
       </c>
       <c r="J123" s="12" t="inlineStr">
         <is>
-          <t>14.40 – 17.59 %  (grade I, class THC 16, nominal 16.00 ± 1.60)</t>
+          <t>9.00 – 10.99 %  (grade I, class THC 10, nominal 10.00 ± 1.00)</t>
         </is>
       </c>
       <c r="K123" s="11" t="inlineStr">
         <is>
-          <t>iCoA-PP-2026-0013</t>
+          <t>iCoA-PP-2026-0014</t>
         </is>
       </c>
       <c r="L123" s="9" t="n">
@@ -31813,7 +31825,7 @@
       </c>
       <c r="S123" s="17" t="inlineStr">
         <is>
-          <t>QCSP 001 prints 16.20 – 19.80 % for this lot; the issue plan's grade range is 14.40 – 17.59 %. Recorded, not resolved.</t>
+          <t>QCSP 001 prints 10.80 – 13.20 % for this lot; the issue plan's grade range is 9.00 – 10.99 %. Recorded, not resolved.</t>
         </is>
       </c>
     </row>
@@ -31830,54 +31842,54 @@
       </c>
       <c r="C124" s="6" t="inlineStr">
         <is>
-          <t>≥ 14.03.2027</t>
+          <t>≥ 10.08.2026</t>
         </is>
       </c>
       <c r="D124" s="6" t="inlineStr">
         <is>
-          <t>P060182</t>
+          <t>P060212</t>
         </is>
       </c>
       <c r="E124" s="6" t="inlineStr">
         <is>
-          <t>GRC102501/2</t>
+          <t>JD112501</t>
         </is>
       </c>
       <c r="F124" s="6" t="inlineStr">
         <is>
-          <t>Grapes and Cream</t>
+          <t>Jelly Donuts</t>
         </is>
       </c>
       <c r="G124" s="5" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
       <c r="H124" s="5" t="inlineStr">
         <is>
-          <t>THC 10</t>
+          <t>THC 20</t>
         </is>
       </c>
       <c r="I124" s="5" t="inlineStr">
         <is>
-          <t>9.80</t>
+          <t>20.32</t>
         </is>
       </c>
       <c r="J124" s="7" t="inlineStr">
         <is>
-          <t>9.00 – 10.99 %  (grade I, class THC 10, nominal 10.00 ± 1.00)</t>
+          <t>18.00 – 21.99 %  (grade II, class THC 20, nominal 20.00 ± 2.00)</t>
         </is>
       </c>
       <c r="K124" s="6" t="inlineStr">
         <is>
-          <t>iCoA-PP-2026-0014</t>
+          <t>iCoA-PP-2026-0015</t>
         </is>
       </c>
       <c r="L124" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M124" s="5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="N124" s="5" t="n">
         <v>0</v>
@@ -31886,19 +31898,19 @@
         <v>0</v>
       </c>
       <c r="P124" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q124" s="7" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="Q124" s="7" t="inlineStr">
+        <is>
+          <t>197-15-К/26; 197-15-М/26</t>
+        </is>
+      </c>
       <c r="R124" s="7" t="inlineStr">
         <is>
           <t>Farmahem — Ident A + B + C with the Assay, at retest; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
-      <c r="S124" s="17" t="inlineStr">
-        <is>
-          <t>QCSP 001 prints 10.80 – 13.20 % for this lot; the issue plan's grade range is 9.00 – 10.99 %. Recorded, not resolved.</t>
-        </is>
-      </c>
+      <c r="S124" s="7" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="11" t="inlineStr">
@@ -31913,22 +31925,22 @@
       </c>
       <c r="C125" s="11" t="inlineStr">
         <is>
-          <t>≥ 10.08.2026</t>
+          <t>≥ 27.04.2027</t>
         </is>
       </c>
       <c r="D125" s="11" t="inlineStr">
         <is>
-          <t>P060212</t>
+          <t>P060232</t>
         </is>
       </c>
       <c r="E125" s="11" t="inlineStr">
         <is>
-          <t>JD112501</t>
+          <t>PM112501</t>
         </is>
       </c>
       <c r="F125" s="11" t="inlineStr">
         <is>
-          <t>Jelly Donuts</t>
+          <t>Permanent Marker</t>
         </is>
       </c>
       <c r="G125" s="9" t="inlineStr">
@@ -31938,29 +31950,29 @@
       </c>
       <c r="H125" s="9" t="inlineStr">
         <is>
-          <t>THC 20</t>
+          <t>THC 10</t>
         </is>
       </c>
       <c r="I125" s="9" t="inlineStr">
         <is>
-          <t>20.32</t>
+          <t>10.79</t>
         </is>
       </c>
       <c r="J125" s="12" t="inlineStr">
         <is>
-          <t>18.00 – 21.99 %  (grade II, class THC 20, nominal 20.00 ± 2.00)</t>
+          <t>9.00 – 10.99 %  (grade II, class THC 10, nominal 10.00 ± 1.00)</t>
         </is>
       </c>
       <c r="K125" s="11" t="inlineStr">
         <is>
-          <t>iCoA-PP-2026-0015</t>
+          <t>iCoA-PP-2026-0016</t>
         </is>
       </c>
       <c r="L125" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M125" s="9" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="N125" s="9" t="n">
         <v>0</v>
@@ -31969,13 +31981,9 @@
         <v>0</v>
       </c>
       <c r="P125" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q125" s="12" t="inlineStr">
-        <is>
-          <t>197-15-К/26; 197-15-М/26</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q125" s="12" t="inlineStr"/>
       <c r="R125" s="12" t="inlineStr">
         <is>
           <t>Farmahem — Ident A + B + C with the Assay, at retest; Purely Plant laboratory — iCoA covering Foreign matter</t>
@@ -31996,54 +32004,54 @@
       </c>
       <c r="C126" s="6" t="inlineStr">
         <is>
-          <t>≥ 27.04.2027</t>
+          <t>≥ 10.08.2026</t>
         </is>
       </c>
       <c r="D126" s="6" t="inlineStr">
         <is>
-          <t>P060232</t>
+          <t>P060242</t>
         </is>
       </c>
       <c r="E126" s="6" t="inlineStr">
         <is>
-          <t>PM112501</t>
+          <t>OPM122501</t>
         </is>
       </c>
       <c r="F126" s="6" t="inlineStr">
         <is>
-          <t>Permanent Marker</t>
+          <t>Orange Punch Mimosa</t>
         </is>
       </c>
       <c r="G126" s="5" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H126" s="5" t="inlineStr">
         <is>
-          <t>THC 10</t>
+          <t>THC 8</t>
         </is>
       </c>
       <c r="I126" s="5" t="inlineStr">
         <is>
-          <t>10.79</t>
+          <t>7.91</t>
         </is>
       </c>
       <c r="J126" s="7" t="inlineStr">
         <is>
-          <t>9.00 – 10.99 %  (grade II, class THC 10, nominal 10.00 ± 1.00)</t>
+          <t>7.20 – 8.79 %  (grade V, class THC 8, nominal 8.00 ± 0.80)</t>
         </is>
       </c>
       <c r="K126" s="6" t="inlineStr">
         <is>
-          <t>iCoA-PP-2026-0016</t>
+          <t>iCoA-PP-2026-0017</t>
         </is>
       </c>
       <c r="L126" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M126" s="5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="N126" s="5" t="n">
         <v>0</v>
@@ -32052,9 +32060,13 @@
         <v>0</v>
       </c>
       <c r="P126" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q126" s="7" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="Q126" s="7" t="inlineStr">
+        <is>
+          <t>197-19-К/26; 197-19-М/26</t>
+        </is>
+      </c>
       <c r="R126" s="7" t="inlineStr">
         <is>
           <t>Farmahem — Ident A + B + C with the Assay, at retest; Purely Plant laboratory — iCoA covering Foreign matter</t>
@@ -32075,54 +32087,54 @@
       </c>
       <c r="C127" s="11" t="inlineStr">
         <is>
-          <t>≥ 10.08.2026</t>
+          <t>≥ 18.05.2027</t>
         </is>
       </c>
       <c r="D127" s="11" t="inlineStr">
         <is>
-          <t>P060242</t>
+          <t>P060282</t>
         </is>
       </c>
       <c r="E127" s="11" t="inlineStr">
         <is>
-          <t>OPM122501</t>
+          <t>SCR112501</t>
         </is>
       </c>
       <c r="F127" s="11" t="inlineStr">
         <is>
-          <t>Orange Punch Mimosa</t>
+          <t>Scrambler</t>
         </is>
       </c>
       <c r="G127" s="9" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>I</t>
         </is>
       </c>
       <c r="H127" s="9" t="inlineStr">
         <is>
-          <t>THC 8</t>
+          <t>THC 20</t>
         </is>
       </c>
       <c r="I127" s="9" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>19.73</t>
         </is>
       </c>
       <c r="J127" s="12" t="inlineStr">
         <is>
-          <t>7.20 – 8.79 %  (grade V, class THC 8, nominal 8.00 ± 0.80)</t>
+          <t>18.00 – 21.99 %  (grade I, class THC 20, nominal 20.00 ± 2.00)</t>
         </is>
       </c>
       <c r="K127" s="11" t="inlineStr">
         <is>
-          <t>iCoA-PP-2026-0017</t>
+          <t>iCoA-PP-2026-0018</t>
         </is>
       </c>
       <c r="L127" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M127" s="9" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="N127" s="9" t="n">
         <v>0</v>
@@ -32131,19 +32143,19 @@
         <v>0</v>
       </c>
       <c r="P127" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q127" s="12" t="inlineStr">
-        <is>
-          <t>197-19-К/26; 197-19-М/26</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q127" s="12" t="inlineStr"/>
       <c r="R127" s="12" t="inlineStr">
         <is>
           <t>Farmahem — Ident A + B + C with the Assay, at retest; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
-      <c r="S127" s="12" t="inlineStr"/>
+      <c r="S127" s="17" t="inlineStr">
+        <is>
+          <t>QCSP 001 prints 16.20 – 19.80 % for this lot; the issue plan's grade range is 18.00 – 21.99 %. Recorded, not resolved.</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="6" t="inlineStr">
@@ -32158,22 +32170,22 @@
       </c>
       <c r="C128" s="6" t="inlineStr">
         <is>
-          <t>≥ 18.05.2027</t>
+          <t>≥ 22.05.2027</t>
         </is>
       </c>
       <c r="D128" s="6" t="inlineStr">
         <is>
-          <t>P060282</t>
+          <t>P060322</t>
         </is>
       </c>
       <c r="E128" s="6" t="inlineStr">
         <is>
-          <t>SCR112501</t>
+          <t>FB012601/1</t>
         </is>
       </c>
       <c r="F128" s="6" t="inlineStr">
         <is>
-          <t>Scrambler</t>
+          <t>Fat Bastard</t>
         </is>
       </c>
       <c r="G128" s="5" t="inlineStr">
@@ -32183,22 +32195,22 @@
       </c>
       <c r="H128" s="5" t="inlineStr">
         <is>
-          <t>THC 20</t>
+          <t>THC 18</t>
         </is>
       </c>
       <c r="I128" s="5" t="inlineStr">
         <is>
-          <t>19.73</t>
+          <t>17.99</t>
         </is>
       </c>
       <c r="J128" s="7" t="inlineStr">
         <is>
-          <t>18.00 – 21.99 %  (grade I, class THC 20, nominal 20.00 ± 2.00)</t>
+          <t>16.20 – 19.79 %  (grade I, class THC 18, nominal 18.00 ± 1.80)</t>
         </is>
       </c>
       <c r="K128" s="6" t="inlineStr">
         <is>
-          <t>iCoA-PP-2026-0018</t>
+          <t>iCoA-PP-2026-0019</t>
         </is>
       </c>
       <c r="L128" s="5" t="n">
@@ -32224,7 +32236,7 @@
       </c>
       <c r="S128" s="17" t="inlineStr">
         <is>
-          <t>QCSP 001 prints 16.20 – 19.80 % for this lot; the issue plan's grade range is 18.00 – 21.99 %. Recorded, not resolved.</t>
+          <t>QCSP 001 prints 14.86 – 17.14 % for this lot; the issue plan's grade range is 16.20 – 19.79 %. Recorded, not resolved.</t>
         </is>
       </c>
     </row>
@@ -32241,22 +32253,22 @@
       </c>
       <c r="C129" s="11" t="inlineStr">
         <is>
-          <t>≥ 22.05.2027</t>
+          <t>≥ 23.05.2027</t>
         </is>
       </c>
       <c r="D129" s="11" t="inlineStr">
         <is>
-          <t>P060322</t>
+          <t>P060362</t>
         </is>
       </c>
       <c r="E129" s="11" t="inlineStr">
         <is>
-          <t>FB012601/1</t>
+          <t>JD012603/01</t>
         </is>
       </c>
       <c r="F129" s="11" t="inlineStr">
         <is>
-          <t>Fat Bastard</t>
+          <t>Jelly Donuts</t>
         </is>
       </c>
       <c r="G129" s="9" t="inlineStr">
@@ -32266,22 +32278,22 @@
       </c>
       <c r="H129" s="9" t="inlineStr">
         <is>
-          <t>THC 18</t>
+          <t>THC 22</t>
         </is>
       </c>
       <c r="I129" s="9" t="inlineStr">
         <is>
-          <t>17.99</t>
+          <t>21.01</t>
         </is>
       </c>
       <c r="J129" s="12" t="inlineStr">
         <is>
-          <t>16.20 – 19.79 %  (grade I, class THC 18, nominal 18.00 ± 1.80)</t>
+          <t>19.80 – 24.19 %  (grade I, class THC 22, nominal 22.00 ± 2.20)</t>
         </is>
       </c>
       <c r="K129" s="11" t="inlineStr">
         <is>
-          <t>iCoA-PP-2026-0019</t>
+          <t>iCoA-PP-2026-0020</t>
         </is>
       </c>
       <c r="L129" s="9" t="n">
@@ -32307,7 +32319,7 @@
       </c>
       <c r="S129" s="18" t="inlineStr">
         <is>
-          <t>No eCoA on file for this cultivation batch — locate the physical certificates, scan and upload. QCSP 001 prints 14.86 – 17.14 % for this lot; the issue plan's grade range is 16.20 – 19.79 %. Recorded, not resolved.</t>
+          <t>No eCoA on file for this cultivation batch — locate the physical certificates, scan and upload. QCSP 001 prints 18.00 – 22.00 % for this lot; the issue plan's grade range is 19.80 – 24.19 %. Recorded, not resolved.</t>
         </is>
       </c>
     </row>
@@ -32324,22 +32336,22 @@
       </c>
       <c r="C130" s="6" t="inlineStr">
         <is>
-          <t>≥ 23.05.2027</t>
+          <t>≥ 10.08.2026</t>
         </is>
       </c>
       <c r="D130" s="6" t="inlineStr">
         <is>
-          <t>P060362</t>
+          <t>P060352</t>
         </is>
       </c>
       <c r="E130" s="6" t="inlineStr">
         <is>
-          <t>JD012603/01</t>
+          <t>FB012602</t>
         </is>
       </c>
       <c r="F130" s="6" t="inlineStr">
         <is>
-          <t>Jelly Donuts</t>
+          <t>Fat Bastard</t>
         </is>
       </c>
       <c r="G130" s="5" t="inlineStr">
@@ -32349,29 +32361,29 @@
       </c>
       <c r="H130" s="5" t="inlineStr">
         <is>
-          <t>THC 22</t>
+          <t>THC 18</t>
         </is>
       </c>
       <c r="I130" s="5" t="inlineStr">
         <is>
-          <t>21.01</t>
+          <t>18.86</t>
         </is>
       </c>
       <c r="J130" s="7" t="inlineStr">
         <is>
-          <t>19.80 – 24.19 %  (grade I, class THC 22, nominal 22.00 ± 2.20)</t>
+          <t>16.20 – 19.79 %  (grade I, class THC 18, nominal 18.00 ± 1.80)</t>
         </is>
       </c>
       <c r="K130" s="6" t="inlineStr">
         <is>
-          <t>iCoA-PP-2026-0020</t>
+          <t>iCoA-PP-2026-0021</t>
         </is>
       </c>
       <c r="L130" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M130" s="5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="N130" s="5" t="n">
         <v>0</v>
@@ -32380,17 +32392,21 @@
         <v>0</v>
       </c>
       <c r="P130" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q130" s="7" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="Q130" s="7" t="inlineStr">
+        <is>
+          <t>197-7-К/26; 197-7-М/26</t>
+        </is>
+      </c>
       <c r="R130" s="7" t="inlineStr">
         <is>
           <t>Farmahem — Ident A + B + C with the Assay, at retest; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
-      <c r="S130" s="18" t="inlineStr">
-        <is>
-          <t>No eCoA on file for this cultivation batch — locate the physical certificates, scan and upload. QCSP 001 prints 18.00 – 22.00 % for this lot; the issue plan's grade range is 19.80 – 24.19 %. Recorded, not resolved.</t>
+      <c r="S130" s="17" t="inlineStr">
+        <is>
+          <t>QCSP 001 prints 17.15 – 18.85 % for this lot; the issue plan's grade range is 16.20 – 19.79 %. Recorded, not resolved.</t>
         </is>
       </c>
     </row>
@@ -32407,54 +32423,54 @@
       </c>
       <c r="C131" s="11" t="inlineStr">
         <is>
-          <t>≥ 10.08.2026</t>
+          <t>≥ 23.05.2027</t>
         </is>
       </c>
       <c r="D131" s="11" t="inlineStr">
         <is>
-          <t>P060352</t>
+          <t>P060422</t>
         </is>
       </c>
       <c r="E131" s="11" t="inlineStr">
         <is>
-          <t>FB012602</t>
+          <t>JD012603/02V</t>
         </is>
       </c>
       <c r="F131" s="11" t="inlineStr">
         <is>
-          <t>Fat Bastard</t>
+          <t>Jelly Donuts</t>
         </is>
       </c>
       <c r="G131" s="9" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>III</t>
         </is>
       </c>
       <c r="H131" s="9" t="inlineStr">
         <is>
-          <t>THC 18</t>
+          <t>THC 16</t>
         </is>
       </c>
       <c r="I131" s="9" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>17.09</t>
         </is>
       </c>
       <c r="J131" s="12" t="inlineStr">
         <is>
-          <t>16.20 – 19.79 %  (grade I, class THC 18, nominal 18.00 ± 1.80)</t>
+          <t>14.40 – 17.59 %  (grade III, class THC 16, nominal 16.00 ± 1.60)</t>
         </is>
       </c>
       <c r="K131" s="11" t="inlineStr">
         <is>
-          <t>iCoA-PP-2026-0021</t>
+          <t>iCoA-PP-2026-0022</t>
         </is>
       </c>
       <c r="L131" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M131" s="9" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="N131" s="9" t="n">
         <v>0</v>
@@ -32463,13 +32479,9 @@
         <v>0</v>
       </c>
       <c r="P131" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q131" s="12" t="inlineStr">
-        <is>
-          <t>197-7-К/26; 197-7-М/26</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q131" s="12" t="inlineStr"/>
       <c r="R131" s="12" t="inlineStr">
         <is>
           <t>Farmahem — Ident A + B + C with the Assay, at retest; Purely Plant laboratory — iCoA covering Foreign matter</t>
@@ -32477,7 +32489,7 @@
       </c>
       <c r="S131" s="17" t="inlineStr">
         <is>
-          <t>QCSP 001 prints 17.15 – 18.85 % for this lot; the issue plan's grade range is 16.20 – 19.79 %. Recorded, not resolved.</t>
+          <t>QCSP 001 prints 14.91 – 17.09 % for this lot; the issue plan's grade range is 14.40 – 17.59 %. Recorded, not resolved.</t>
         </is>
       </c>
     </row>
@@ -32494,27 +32506,27 @@
       </c>
       <c r="C132" s="6" t="inlineStr">
         <is>
-          <t>≥ 23.05.2027</t>
+          <t>≥ 10.08.2026</t>
         </is>
       </c>
       <c r="D132" s="6" t="inlineStr">
         <is>
-          <t>P060422</t>
+          <t>P060402</t>
         </is>
       </c>
       <c r="E132" s="6" t="inlineStr">
         <is>
-          <t>JD012603/02V</t>
+          <t>GG012603</t>
         </is>
       </c>
       <c r="F132" s="6" t="inlineStr">
         <is>
-          <t>Jelly Donuts</t>
+          <t>Gorilla Glue</t>
         </is>
       </c>
       <c r="G132" s="5" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>II</t>
         </is>
       </c>
       <c r="H132" s="5" t="inlineStr">
@@ -32524,24 +32536,24 @@
       </c>
       <c r="I132" s="5" t="inlineStr">
         <is>
-          <t>17.09</t>
+          <t>16.70</t>
         </is>
       </c>
       <c r="J132" s="7" t="inlineStr">
         <is>
-          <t>14.40 – 17.59 %  (grade III, class THC 16, nominal 16.00 ± 1.60)</t>
+          <t>14.40 – 17.59 %  (grade II, class THC 16, nominal 16.00 ± 1.60)</t>
         </is>
       </c>
       <c r="K132" s="6" t="inlineStr">
         <is>
-          <t>iCoA-PP-2026-0022</t>
+          <t>iCoA-PP-2026-0023</t>
         </is>
       </c>
       <c r="L132" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M132" s="5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="N132" s="5" t="n">
         <v>0</v>
@@ -32550,9 +32562,13 @@
         <v>0</v>
       </c>
       <c r="P132" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q132" s="7" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="Q132" s="7" t="inlineStr">
+        <is>
+          <t>197-8-К/26; 197-8-М/26</t>
+        </is>
+      </c>
       <c r="R132" s="7" t="inlineStr">
         <is>
           <t>Farmahem — Ident A + B + C with the Assay, at retest; Purely Plant laboratory — iCoA covering Foreign matter</t>
@@ -32560,7 +32576,7 @@
       </c>
       <c r="S132" s="17" t="inlineStr">
         <is>
-          <t>QCSP 001 prints 14.91 – 17.09 % for this lot; the issue plan's grade range is 14.40 – 17.59 %. Recorded, not resolved.</t>
+          <t>QCSP 001 prints 15.00 – 17.00 % for this lot; the issue plan's grade range is 14.40 – 17.59 %. Recorded, not resolved.</t>
         </is>
       </c>
     </row>
@@ -32577,54 +32593,54 @@
       </c>
       <c r="C133" s="11" t="inlineStr">
         <is>
-          <t>≥ 10.08.2026</t>
+          <t>≥ 24.05.2027</t>
         </is>
       </c>
       <c r="D133" s="11" t="inlineStr">
         <is>
-          <t>P060402</t>
+          <t>P060372</t>
         </is>
       </c>
       <c r="E133" s="11" t="inlineStr">
         <is>
-          <t>GG012603</t>
+          <t>CC012603</t>
         </is>
       </c>
       <c r="F133" s="11" t="inlineStr">
         <is>
-          <t>Gorilla Glue</t>
+          <t>Cash Cow</t>
         </is>
       </c>
       <c r="G133" s="9" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
       <c r="H133" s="9" t="inlineStr">
         <is>
-          <t>THC 16</t>
+          <t>THC 14</t>
         </is>
       </c>
       <c r="I133" s="9" t="inlineStr">
         <is>
-          <t>16.70</t>
+          <t>14.76</t>
         </is>
       </c>
       <c r="J133" s="12" t="inlineStr">
         <is>
-          <t>14.40 – 17.59 %  (grade II, class THC 16, nominal 16.00 ± 1.60)</t>
+          <t>12.60 – 15.39 %  (grade I, class THC 14, nominal 14.00 ± 1.40)</t>
         </is>
       </c>
       <c r="K133" s="11" t="inlineStr">
         <is>
-          <t>iCoA-PP-2026-0023</t>
+          <t>iCoA-PP-2026-0024</t>
         </is>
       </c>
       <c r="L133" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M133" s="9" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="N133" s="9" t="n">
         <v>0</v>
@@ -32633,21 +32649,17 @@
         <v>0</v>
       </c>
       <c r="P133" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q133" s="12" t="inlineStr">
-        <is>
-          <t>197-8-К/26; 197-8-М/26</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q133" s="12" t="inlineStr"/>
       <c r="R133" s="12" t="inlineStr">
         <is>
           <t>Farmahem — Ident A + B + C with the Assay, at retest; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
-      <c r="S133" s="17" t="inlineStr">
-        <is>
-          <t>QCSP 001 prints 15.00 – 17.00 % for this lot; the issue plan's grade range is 14.40 – 17.59 %. Recorded, not resolved.</t>
+      <c r="S133" s="18" t="inlineStr">
+        <is>
+          <t>No eCoA on file for this cultivation batch — locate the physical certificates, scan and upload.</t>
         </is>
       </c>
     </row>
@@ -32669,22 +32681,22 @@
       </c>
       <c r="D134" s="6" t="inlineStr">
         <is>
-          <t>P060372</t>
+          <t>P060412</t>
         </is>
       </c>
       <c r="E134" s="6" t="inlineStr">
         <is>
-          <t>CC012603</t>
+          <t>JD012603/02</t>
         </is>
       </c>
       <c r="F134" s="6" t="inlineStr">
         <is>
-          <t>Cash Cow</t>
+          <t>Jelly Donuts</t>
         </is>
       </c>
       <c r="G134" s="5" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>IV</t>
         </is>
       </c>
       <c r="H134" s="5" t="inlineStr">
@@ -32694,17 +32706,17 @@
       </c>
       <c r="I134" s="5" t="inlineStr">
         <is>
-          <t>14.76</t>
+          <t>14.43</t>
         </is>
       </c>
       <c r="J134" s="7" t="inlineStr">
         <is>
-          <t>12.60 – 15.39 %  (grade I, class THC 14, nominal 14.00 ± 1.40)</t>
+          <t>12.60 – 15.39 %  (grade IV, class THC 14, nominal 14.00 ± 1.40)</t>
         </is>
       </c>
       <c r="K134" s="6" t="inlineStr">
         <is>
-          <t>iCoA-PP-2026-0024</t>
+          <t>iCoA-PP-2026-0025</t>
         </is>
       </c>
       <c r="L134" s="5" t="n">
@@ -32728,9 +32740,9 @@
           <t>Farmahem — Ident A + B + C with the Assay, at retest; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
-      <c r="S134" s="18" t="inlineStr">
-        <is>
-          <t>No eCoA on file for this cultivation batch — locate the physical certificates, scan and upload.</t>
+      <c r="S134" s="17" t="inlineStr">
+        <is>
+          <t>QCSP 001 prints 18.00 – 22.00 % for this lot; the issue plan's grade range is 12.60 – 15.39 %. Recorded, not resolved.</t>
         </is>
       </c>
     </row>
@@ -32747,54 +32759,54 @@
       </c>
       <c r="C135" s="11" t="inlineStr">
         <is>
-          <t>≥ 24.05.2027</t>
+          <t>≥ 10.08.2026</t>
         </is>
       </c>
       <c r="D135" s="11" t="inlineStr">
         <is>
-          <t>P060412</t>
+          <t>P060382</t>
         </is>
       </c>
       <c r="E135" s="11" t="inlineStr">
         <is>
-          <t>JD012603/02</t>
+          <t>SCR012603</t>
         </is>
       </c>
       <c r="F135" s="11" t="inlineStr">
         <is>
-          <t>Jelly Donuts</t>
+          <t>Scrambler</t>
         </is>
       </c>
       <c r="G135" s="9" t="inlineStr">
         <is>
-          <t>IV</t>
+          <t>II</t>
         </is>
       </c>
       <c r="H135" s="9" t="inlineStr">
         <is>
-          <t>THC 14</t>
+          <t>THC 18</t>
         </is>
       </c>
       <c r="I135" s="9" t="inlineStr">
         <is>
-          <t>14.43</t>
+          <t>17.84</t>
         </is>
       </c>
       <c r="J135" s="12" t="inlineStr">
         <is>
-          <t>12.60 – 15.39 %  (grade IV, class THC 14, nominal 14.00 ± 1.40)</t>
+          <t>16.20 – 19.79 %  (grade II, class THC 18, nominal 18.00 ± 1.80)</t>
         </is>
       </c>
       <c r="K135" s="11" t="inlineStr">
         <is>
-          <t>iCoA-PP-2026-0025</t>
+          <t>iCoA-PP-2026-0026</t>
         </is>
       </c>
       <c r="L135" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M135" s="9" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="N135" s="9" t="n">
         <v>0</v>
@@ -32803,19 +32815,19 @@
         <v>0</v>
       </c>
       <c r="P135" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q135" s="12" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="Q135" s="12" t="inlineStr">
+        <is>
+          <t>197-21-К/26; 197-21-М/26</t>
+        </is>
+      </c>
       <c r="R135" s="12" t="inlineStr">
         <is>
           <t>Farmahem — Ident A + B + C with the Assay, at retest; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
-      <c r="S135" s="17" t="inlineStr">
-        <is>
-          <t>QCSP 001 prints 18.00 – 22.00 % for this lot; the issue plan's grade range is 12.60 – 15.39 %. Recorded, not resolved.</t>
-        </is>
-      </c>
+      <c r="S135" s="12" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="6" t="inlineStr">
@@ -32830,54 +32842,42 @@
       </c>
       <c r="C136" s="6" t="inlineStr">
         <is>
-          <t>≥ 10.08.2026</t>
-        </is>
-      </c>
-      <c r="D136" s="6" t="inlineStr">
-        <is>
-          <t>P060382</t>
-        </is>
-      </c>
+          <t>≥ 11.05.2026</t>
+        </is>
+      </c>
+      <c r="D136" s="6" t="inlineStr"/>
       <c r="E136" s="6" t="inlineStr">
         <is>
-          <t>SCR012603</t>
+          <t>CJ1024</t>
         </is>
       </c>
       <c r="F136" s="6" t="inlineStr">
         <is>
-          <t>Scrambler</t>
-        </is>
-      </c>
-      <c r="G136" s="5" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
+          <t>Cup Junky</t>
+        </is>
+      </c>
+      <c r="G136" s="5" t="inlineStr"/>
       <c r="H136" s="5" t="inlineStr">
         <is>
-          <t>THC 18</t>
-        </is>
-      </c>
-      <c r="I136" s="5" t="inlineStr">
-        <is>
-          <t>17.84</t>
-        </is>
-      </c>
+          <t xml:space="preserve">THC </t>
+        </is>
+      </c>
+      <c r="I136" s="5" t="inlineStr"/>
       <c r="J136" s="7" t="inlineStr">
         <is>
-          <t>16.20 – 19.79 %  (grade II, class THC 18, nominal 18.00 ± 1.80)</t>
+          <t>Per target grade — no packaged lot or grade assigned in the master spec yet</t>
         </is>
       </c>
       <c r="K136" s="6" t="inlineStr">
         <is>
-          <t>iCoA-PP-2026-0026</t>
+          <t>(assigned on issue)</t>
         </is>
       </c>
       <c r="L136" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M136" s="5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="N136" s="5" t="n">
         <v>0</v>
@@ -32886,13 +32886,9 @@
         <v>0</v>
       </c>
       <c r="P136" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q136" s="7" t="inlineStr">
-        <is>
-          <t>197-21-К/26; 197-21-М/26</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q136" s="7" t="inlineStr"/>
       <c r="R136" s="7" t="inlineStr">
         <is>
           <t>Farmahem — Ident A + B + C with the Assay, at retest; Purely Plant laboratory — iCoA covering Foreign matter</t>
@@ -32919,12 +32915,12 @@
       <c r="D137" s="11" t="inlineStr"/>
       <c r="E137" s="11" t="inlineStr">
         <is>
-          <t>CJ1024</t>
+          <t>GP0824_01</t>
         </is>
       </c>
       <c r="F137" s="11" t="inlineStr">
         <is>
-          <t>Cup Junky</t>
+          <t>Grape Pie</t>
         </is>
       </c>
       <c r="G137" s="9" t="inlineStr"/>
@@ -32986,12 +32982,12 @@
       <c r="D138" s="6" t="inlineStr"/>
       <c r="E138" s="6" t="inlineStr">
         <is>
-          <t>GP0824_01</t>
+          <t>MB0824_04</t>
         </is>
       </c>
       <c r="F138" s="6" t="inlineStr">
         <is>
-          <t>Grape Pie</t>
+          <t>Motor Breath</t>
         </is>
       </c>
       <c r="G138" s="5" t="inlineStr"/>
@@ -33047,18 +33043,18 @@
       </c>
       <c r="C139" s="11" t="inlineStr">
         <is>
-          <t>≥ 11.05.2026</t>
+          <t>≥ 30.05.2026</t>
         </is>
       </c>
       <c r="D139" s="11" t="inlineStr"/>
       <c r="E139" s="11" t="inlineStr">
         <is>
-          <t>MB0824_04</t>
+          <t>GG1024_02</t>
         </is>
       </c>
       <c r="F139" s="11" t="inlineStr">
         <is>
-          <t>Motor Breath</t>
+          <t>Gorilla Glue</t>
         </is>
       </c>
       <c r="G139" s="9" t="inlineStr"/>
@@ -33114,18 +33110,18 @@
       </c>
       <c r="C140" s="6" t="inlineStr">
         <is>
-          <t>≥ 30.05.2026</t>
+          <t>≥ 10.07.2026</t>
         </is>
       </c>
       <c r="D140" s="6" t="inlineStr"/>
       <c r="E140" s="6" t="inlineStr">
         <is>
-          <t>GG1024_02</t>
+          <t>BSS1024_01</t>
         </is>
       </c>
       <c r="F140" s="6" t="inlineStr">
         <is>
-          <t>Gorilla Glue</t>
+          <t>Blue Sunset Sherbet</t>
         </is>
       </c>
       <c r="G140" s="5" t="inlineStr"/>
@@ -33181,18 +33177,18 @@
       </c>
       <c r="C141" s="11" t="inlineStr">
         <is>
-          <t>≥ 10.07.2026</t>
+          <t>≥ 05.09.2026</t>
         </is>
       </c>
       <c r="D141" s="11" t="inlineStr"/>
       <c r="E141" s="11" t="inlineStr">
         <is>
-          <t>BSS1024_01</t>
+          <t>OPM052501</t>
         </is>
       </c>
       <c r="F141" s="11" t="inlineStr">
         <is>
-          <t>Blue Sunset Sherbet</t>
+          <t>Orange Punch Mimosa</t>
         </is>
       </c>
       <c r="G141" s="9" t="inlineStr"/>
@@ -33248,18 +33244,18 @@
       </c>
       <c r="C142" s="6" t="inlineStr">
         <is>
-          <t>≥ 05.09.2026</t>
+          <t>≥ 17.09.2026</t>
         </is>
       </c>
       <c r="D142" s="6" t="inlineStr"/>
       <c r="E142" s="6" t="inlineStr">
         <is>
-          <t>OPM052501</t>
+          <t>CJ052501-2</t>
         </is>
       </c>
       <c r="F142" s="6" t="inlineStr">
         <is>
-          <t>Orange Punch Mimosa</t>
+          <t>Cup Junky</t>
         </is>
       </c>
       <c r="G142" s="5" t="inlineStr"/>
@@ -33315,13 +33311,13 @@
       </c>
       <c r="C143" s="11" t="inlineStr">
         <is>
-          <t>≥ 17.09.2026</t>
+          <t>≥ 02.12.2026</t>
         </is>
       </c>
       <c r="D143" s="11" t="inlineStr"/>
       <c r="E143" s="11" t="inlineStr">
         <is>
-          <t>CJ052501-2</t>
+          <t>CJ072501</t>
         </is>
       </c>
       <c r="F143" s="11" t="inlineStr">
@@ -33388,12 +33384,12 @@
       <c r="D144" s="6" t="inlineStr"/>
       <c r="E144" s="6" t="inlineStr">
         <is>
-          <t>CJ072501</t>
+          <t>WC072501</t>
         </is>
       </c>
       <c r="F144" s="6" t="inlineStr">
         <is>
-          <t>Cup Junky</t>
+          <t>Wedding Crasher</t>
         </is>
       </c>
       <c r="G144" s="5" t="inlineStr"/>
@@ -33449,18 +33445,18 @@
       </c>
       <c r="C145" s="11" t="inlineStr">
         <is>
-          <t>≥ 02.12.2026</t>
+          <t>≥ 21.01.2027</t>
         </is>
       </c>
       <c r="D145" s="11" t="inlineStr"/>
       <c r="E145" s="11" t="inlineStr">
         <is>
-          <t>WC072501</t>
+          <t>PM072501</t>
         </is>
       </c>
       <c r="F145" s="11" t="inlineStr">
         <is>
-          <t>Wedding Crasher</t>
+          <t>Permanent Market</t>
         </is>
       </c>
       <c r="G145" s="9" t="inlineStr"/>
@@ -33522,12 +33518,12 @@
       <c r="D146" s="6" t="inlineStr"/>
       <c r="E146" s="6" t="inlineStr">
         <is>
-          <t>PM072501</t>
+          <t>GP072501-1</t>
         </is>
       </c>
       <c r="F146" s="6" t="inlineStr">
         <is>
-          <t>Permanent Market</t>
+          <t>Grape Pie</t>
         </is>
       </c>
       <c r="G146" s="5" t="inlineStr"/>
@@ -33583,18 +33579,18 @@
       </c>
       <c r="C147" s="11" t="inlineStr">
         <is>
-          <t>≥ 21.01.2027</t>
+          <t>≥ 10.08.2026</t>
         </is>
       </c>
       <c r="D147" s="11" t="inlineStr"/>
       <c r="E147" s="11" t="inlineStr">
         <is>
-          <t>GP072501-1</t>
+          <t>CJ062501-2</t>
         </is>
       </c>
       <c r="F147" s="11" t="inlineStr">
         <is>
-          <t>Grape Pie</t>
+          <t>Cap Junkie</t>
         </is>
       </c>
       <c r="G147" s="9" t="inlineStr"/>
@@ -33615,10 +33611,10 @@
         </is>
       </c>
       <c r="L147" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M147" s="9" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="N147" s="9" t="n">
         <v>0</v>
@@ -33627,9 +33623,13 @@
         <v>0</v>
       </c>
       <c r="P147" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q147" s="12" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="Q147" s="12" t="inlineStr">
+        <is>
+          <t>197-4-К/26; 197-4-М/26</t>
+        </is>
+      </c>
       <c r="R147" s="12" t="inlineStr">
         <is>
           <t>Farmahem — Ident A + B + C with the Assay, at retest; Purely Plant laboratory — iCoA covering Foreign matter</t>
@@ -33650,18 +33650,18 @@
       </c>
       <c r="C148" s="6" t="inlineStr">
         <is>
-          <t>≥ 10.08.2026</t>
+          <t>≥ 20.02.2027</t>
         </is>
       </c>
       <c r="D148" s="6" t="inlineStr"/>
       <c r="E148" s="6" t="inlineStr">
         <is>
-          <t>CJ062501-2</t>
+          <t>AB092501</t>
         </is>
       </c>
       <c r="F148" s="6" t="inlineStr">
         <is>
-          <t>Cap Junkie</t>
+          <t>Apple and Banana</t>
         </is>
       </c>
       <c r="G148" s="5" t="inlineStr"/>
@@ -33682,10 +33682,10 @@
         </is>
       </c>
       <c r="L148" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M148" s="5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="N148" s="5" t="n">
         <v>0</v>
@@ -33694,13 +33694,9 @@
         <v>0</v>
       </c>
       <c r="P148" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q148" s="7" t="inlineStr">
-        <is>
-          <t>197-4-К/26; 197-4-М/26</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q148" s="7" t="inlineStr"/>
       <c r="R148" s="7" t="inlineStr">
         <is>
           <t>Farmahem — Ident A + B + C with the Assay, at retest; Purely Plant laboratory — iCoA covering Foreign matter</t>
@@ -33721,18 +33717,18 @@
       </c>
       <c r="C149" s="11" t="inlineStr">
         <is>
-          <t>≥ 20.02.2027</t>
+          <t>≥ 04.03.2027</t>
         </is>
       </c>
       <c r="D149" s="11" t="inlineStr"/>
       <c r="E149" s="11" t="inlineStr">
         <is>
-          <t>AB092501</t>
+          <t>SJ102501</t>
         </is>
       </c>
       <c r="F149" s="11" t="inlineStr">
         <is>
-          <t>Apple and Banana</t>
+          <t>Sleepy Joy</t>
         </is>
       </c>
       <c r="G149" s="9" t="inlineStr"/>
@@ -33794,7 +33790,7 @@
       <c r="D150" s="6" t="inlineStr"/>
       <c r="E150" s="6" t="inlineStr">
         <is>
-          <t>SJ102501</t>
+          <t>SJ112501</t>
         </is>
       </c>
       <c r="F150" s="6" t="inlineStr">
@@ -33855,18 +33851,18 @@
       </c>
       <c r="C151" s="11" t="inlineStr">
         <is>
-          <t>≥ 04.03.2027</t>
+          <t>≥ 05.03.2027</t>
         </is>
       </c>
       <c r="D151" s="11" t="inlineStr"/>
       <c r="E151" s="11" t="inlineStr">
         <is>
-          <t>SJ112501</t>
+          <t>OPM112501</t>
         </is>
       </c>
       <c r="F151" s="11" t="inlineStr">
         <is>
-          <t>Sleepy Joy</t>
+          <t>Orange Punch Mimosa</t>
         </is>
       </c>
       <c r="G151" s="9" t="inlineStr"/>
@@ -33922,18 +33918,18 @@
       </c>
       <c r="C152" s="6" t="inlineStr">
         <is>
-          <t>≥ 05.03.2027</t>
+          <t>≥ 09.04.2027</t>
         </is>
       </c>
       <c r="D152" s="6" t="inlineStr"/>
       <c r="E152" s="6" t="inlineStr">
         <is>
-          <t>OPM112501</t>
+          <t>J31112501</t>
         </is>
       </c>
       <c r="F152" s="6" t="inlineStr">
         <is>
-          <t>Orange Punch Mimosa</t>
+          <t>Jokerz 31</t>
         </is>
       </c>
       <c r="G152" s="5" t="inlineStr"/>
@@ -33989,13 +33985,13 @@
       </c>
       <c r="C153" s="11" t="inlineStr">
         <is>
-          <t>≥ 09.04.2027</t>
+          <t>≥ 23.04.2027</t>
         </is>
       </c>
       <c r="D153" s="11" t="inlineStr"/>
       <c r="E153" s="11" t="inlineStr">
         <is>
-          <t>J31112501</t>
+          <t>J31122501</t>
         </is>
       </c>
       <c r="F153" s="11" t="inlineStr">
@@ -34056,18 +34052,18 @@
       </c>
       <c r="C154" s="6" t="inlineStr">
         <is>
-          <t>≥ 23.04.2027</t>
+          <t>≥ 11.05.2027</t>
         </is>
       </c>
       <c r="D154" s="6" t="inlineStr"/>
       <c r="E154" s="6" t="inlineStr">
         <is>
-          <t>J31122501</t>
+          <t>GP062501</t>
         </is>
       </c>
       <c r="F154" s="6" t="inlineStr">
         <is>
-          <t>Jokerz 31</t>
+          <t>Grape Pie</t>
         </is>
       </c>
       <c r="G154" s="5" t="inlineStr"/>
@@ -34129,12 +34125,12 @@
       <c r="D155" s="11" t="inlineStr"/>
       <c r="E155" s="11" t="inlineStr">
         <is>
-          <t>GP062501</t>
+          <t>CC112501</t>
         </is>
       </c>
       <c r="F155" s="11" t="inlineStr">
         <is>
-          <t>Grape Pie</t>
+          <t>Cash Cow</t>
         </is>
       </c>
       <c r="G155" s="9" t="inlineStr"/>
@@ -34196,12 +34192,12 @@
       <c r="D156" s="6" t="inlineStr"/>
       <c r="E156" s="6" t="inlineStr">
         <is>
-          <t>CC112501</t>
+          <t>FB112501</t>
         </is>
       </c>
       <c r="F156" s="6" t="inlineStr">
         <is>
-          <t>Cash Cow</t>
+          <t>Fat Bastard</t>
         </is>
       </c>
       <c r="G156" s="5" t="inlineStr"/>
@@ -34263,12 +34259,12 @@
       <c r="D157" s="11" t="inlineStr"/>
       <c r="E157" s="11" t="inlineStr">
         <is>
-          <t>FB012601</t>
+          <t>GG012601</t>
         </is>
       </c>
       <c r="F157" s="11" t="inlineStr">
         <is>
-          <t>Fat Bastard</t>
+          <t>Gorilla Glue</t>
         </is>
       </c>
       <c r="G157" s="9" t="inlineStr"/>
@@ -34330,12 +34326,12 @@
       <c r="D158" s="6" t="inlineStr"/>
       <c r="E158" s="6" t="inlineStr">
         <is>
-          <t>FB112501</t>
+          <t>GG112501</t>
         </is>
       </c>
       <c r="F158" s="6" t="inlineStr">
         <is>
-          <t>Fat Bastard</t>
+          <t>Gorilla Glue</t>
         </is>
       </c>
       <c r="G158" s="5" t="inlineStr"/>
@@ -34397,12 +34393,12 @@
       <c r="D159" s="11" t="inlineStr"/>
       <c r="E159" s="11" t="inlineStr">
         <is>
-          <t>GG012601</t>
+          <t>JD012601</t>
         </is>
       </c>
       <c r="F159" s="11" t="inlineStr">
         <is>
-          <t>Gorilla Glue</t>
+          <t>Jelly Donutz</t>
         </is>
       </c>
       <c r="G159" s="9" t="inlineStr"/>
@@ -34458,18 +34454,18 @@
       </c>
       <c r="C160" s="6" t="inlineStr">
         <is>
-          <t>≥ 11.05.2027</t>
+          <t>≥ 30.06.2027</t>
         </is>
       </c>
       <c r="D160" s="6" t="inlineStr"/>
       <c r="E160" s="6" t="inlineStr">
         <is>
-          <t>GG112501</t>
+          <t>FB012603</t>
         </is>
       </c>
       <c r="F160" s="6" t="inlineStr">
         <is>
-          <t>Gorilla Glue</t>
+          <t>Fat Bastard</t>
         </is>
       </c>
       <c r="G160" s="5" t="inlineStr"/>
@@ -34525,18 +34521,18 @@
       </c>
       <c r="C161" s="11" t="inlineStr">
         <is>
-          <t>≥ 11.05.2027</t>
+          <t>≥ 30.06.2027</t>
         </is>
       </c>
       <c r="D161" s="11" t="inlineStr"/>
       <c r="E161" s="11" t="inlineStr">
         <is>
-          <t>JD012601</t>
+          <t>FB012603V</t>
         </is>
       </c>
       <c r="F161" s="11" t="inlineStr">
         <is>
-          <t>Jelly Donutz</t>
+          <t>FatBastard</t>
         </is>
       </c>
       <c r="G161" s="9" t="inlineStr"/>
@@ -34598,12 +34594,12 @@
       <c r="D162" s="6" t="inlineStr"/>
       <c r="E162" s="6" t="inlineStr">
         <is>
-          <t>FB012603</t>
+          <t>JD022601</t>
         </is>
       </c>
       <c r="F162" s="6" t="inlineStr">
         <is>
-          <t>Fat Bastard</t>
+          <t>JellyDonutz</t>
         </is>
       </c>
       <c r="G162" s="5" t="inlineStr"/>
@@ -34659,18 +34655,18 @@
       </c>
       <c r="C163" s="11" t="inlineStr">
         <is>
-          <t>≥ 30.06.2027</t>
+          <t>≥ 06.07.2027</t>
         </is>
       </c>
       <c r="D163" s="11" t="inlineStr"/>
       <c r="E163" s="11" t="inlineStr">
         <is>
-          <t>FB012603V</t>
+          <t>P160012</t>
         </is>
       </c>
       <c r="F163" s="11" t="inlineStr">
         <is>
-          <t>FatBastard</t>
+          <t>GrapePie</t>
         </is>
       </c>
       <c r="G163" s="9" t="inlineStr"/>
@@ -34726,18 +34722,18 @@
       </c>
       <c r="C164" s="6" t="inlineStr">
         <is>
-          <t>≥ 30.06.2027</t>
+          <t>≥ 06.07.2027</t>
         </is>
       </c>
       <c r="D164" s="6" t="inlineStr"/>
       <c r="E164" s="6" t="inlineStr">
         <is>
-          <t>JD022601</t>
+          <t>P160022</t>
         </is>
       </c>
       <c r="F164" s="6" t="inlineStr">
         <is>
-          <t>JellyDonutz</t>
+          <t>GrapePie</t>
         </is>
       </c>
       <c r="G164" s="5" t="inlineStr"/>
@@ -34799,7 +34795,7 @@
       <c r="D165" s="11" t="inlineStr"/>
       <c r="E165" s="11" t="inlineStr">
         <is>
-          <t>P160012</t>
+          <t>P160032</t>
         </is>
       </c>
       <c r="F165" s="11" t="inlineStr">
@@ -34866,12 +34862,12 @@
       <c r="D166" s="6" t="inlineStr"/>
       <c r="E166" s="6" t="inlineStr">
         <is>
-          <t>P160022</t>
+          <t>SCR022601</t>
         </is>
       </c>
       <c r="F166" s="6" t="inlineStr">
         <is>
-          <t>GrapePie</t>
+          <t>Scrambler</t>
         </is>
       </c>
       <c r="G166" s="5" t="inlineStr"/>
@@ -34927,18 +34923,18 @@
       </c>
       <c r="C167" s="11" t="inlineStr">
         <is>
-          <t>≥ 06.07.2027</t>
+          <t>≥ 21.07.2027</t>
         </is>
       </c>
       <c r="D167" s="11" t="inlineStr"/>
       <c r="E167" s="11" t="inlineStr">
         <is>
-          <t>P160032</t>
+          <t>FB032601</t>
         </is>
       </c>
       <c r="F167" s="11" t="inlineStr">
         <is>
-          <t>GrapePie</t>
+          <t>FatBastard</t>
         </is>
       </c>
       <c r="G167" s="9" t="inlineStr"/>
@@ -34976,7 +34972,7 @@
       <c r="Q167" s="12" t="inlineStr"/>
       <c r="R167" s="12" t="inlineStr">
         <is>
-          <t>Farmahem — Ident A + B + C with the Assay, at retest; Purely Plant laboratory — iCoA covering Foreign matter</t>
+          <t>Farmahem — Ident A + B + C with the Assay, at retest</t>
         </is>
       </c>
       <c r="S167" s="12" t="inlineStr"/>
@@ -34994,18 +34990,18 @@
       </c>
       <c r="C168" s="6" t="inlineStr">
         <is>
-          <t>≥ 06.07.2027</t>
+          <t>≥ 21.07.2027</t>
         </is>
       </c>
       <c r="D168" s="6" t="inlineStr"/>
       <c r="E168" s="6" t="inlineStr">
         <is>
-          <t>SCR022601</t>
+          <t>GG032601</t>
         </is>
       </c>
       <c r="F168" s="6" t="inlineStr">
         <is>
-          <t>Scrambler</t>
+          <t>GorillaGlue</t>
         </is>
       </c>
       <c r="G168" s="5" t="inlineStr"/>
@@ -35061,18 +35057,18 @@
       </c>
       <c r="C169" s="11" t="inlineStr">
         <is>
-          <t>≥ 21.07.2027</t>
+          <t>≥ 10.08.2026</t>
         </is>
       </c>
       <c r="D169" s="11" t="inlineStr"/>
       <c r="E169" s="11" t="inlineStr">
         <is>
-          <t>FB032601</t>
+          <t>P060332</t>
         </is>
       </c>
       <c r="F169" s="11" t="inlineStr">
         <is>
-          <t>FatBastard</t>
+          <t>CashCow</t>
         </is>
       </c>
       <c r="G169" s="9" t="inlineStr"/>
@@ -35093,10 +35089,10 @@
         </is>
       </c>
       <c r="L169" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M169" s="9" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="N169" s="9" t="n">
         <v>0</v>
@@ -35105,156 +35101,22 @@
         <v>0</v>
       </c>
       <c r="P169" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q169" s="12" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="Q169" s="12" t="inlineStr">
+        <is>
+          <t>197-6-К/26; 197-6-М/26</t>
+        </is>
+      </c>
       <c r="R169" s="12" t="inlineStr">
         <is>
-          <t>Farmahem — Ident A + B + C with the Assay, at retest</t>
+          <t>Farmahem — Ident A + B + C with the Assay, at retest; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
       <c r="S169" s="12" t="inlineStr"/>
     </row>
-    <row r="170">
-      <c r="A170" s="6" t="inlineStr">
-        <is>
-          <t>(assigned on issue)</t>
-        </is>
-      </c>
-      <c r="B170" s="6" t="inlineStr">
-        <is>
-          <t>additional testing (12-month) — predicted</t>
-        </is>
-      </c>
-      <c r="C170" s="6" t="inlineStr">
-        <is>
-          <t>≥ 21.07.2027</t>
-        </is>
-      </c>
-      <c r="D170" s="6" t="inlineStr"/>
-      <c r="E170" s="6" t="inlineStr">
-        <is>
-          <t>GG032601</t>
-        </is>
-      </c>
-      <c r="F170" s="6" t="inlineStr">
-        <is>
-          <t>GorillaGlue</t>
-        </is>
-      </c>
-      <c r="G170" s="5" t="inlineStr"/>
-      <c r="H170" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">THC </t>
-        </is>
-      </c>
-      <c r="I170" s="5" t="inlineStr"/>
-      <c r="J170" s="7" t="inlineStr">
-        <is>
-          <t>Per target grade — no packaged lot or grade assigned in the master spec yet</t>
-        </is>
-      </c>
-      <c r="K170" s="6" t="inlineStr">
-        <is>
-          <t>(assigned on issue)</t>
-        </is>
-      </c>
-      <c r="L170" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M170" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="N170" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O170" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P170" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q170" s="7" t="inlineStr"/>
-      <c r="R170" s="7" t="inlineStr">
-        <is>
-          <t>Farmahem — Ident A + B + C with the Assay, at retest; Purely Plant laboratory — iCoA covering Foreign matter</t>
-        </is>
-      </c>
-      <c r="S170" s="7" t="inlineStr"/>
-    </row>
-    <row r="171">
-      <c r="A171" s="11" t="inlineStr">
-        <is>
-          <t>(assigned on issue)</t>
-        </is>
-      </c>
-      <c r="B171" s="11" t="inlineStr">
-        <is>
-          <t>additional testing (12-month) — predicted</t>
-        </is>
-      </c>
-      <c r="C171" s="11" t="inlineStr">
-        <is>
-          <t>≥ 10.08.2026</t>
-        </is>
-      </c>
-      <c r="D171" s="11" t="inlineStr"/>
-      <c r="E171" s="11" t="inlineStr">
-        <is>
-          <t>P060332</t>
-        </is>
-      </c>
-      <c r="F171" s="11" t="inlineStr">
-        <is>
-          <t>CashCow</t>
-        </is>
-      </c>
-      <c r="G171" s="9" t="inlineStr"/>
-      <c r="H171" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">THC </t>
-        </is>
-      </c>
-      <c r="I171" s="9" t="inlineStr"/>
-      <c r="J171" s="12" t="inlineStr">
-        <is>
-          <t>Per target grade — no packaged lot or grade assigned in the master spec yet</t>
-        </is>
-      </c>
-      <c r="K171" s="11" t="inlineStr">
-        <is>
-          <t>(assigned on issue)</t>
-        </is>
-      </c>
-      <c r="L171" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="M171" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="N171" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O171" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P171" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q171" s="12" t="inlineStr">
-        <is>
-          <t>197-6-К/26; 197-6-М/26</t>
-        </is>
-      </c>
-      <c r="R171" s="12" t="inlineStr">
-        <is>
-          <t>Farmahem — Ident A + B + C with the Assay, at retest; Purely Plant laboratory — iCoA covering Foreign matter</t>
-        </is>
-      </c>
-      <c r="S171" s="12" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A5:S171"/>
+  <autoFilter ref="A5:S169"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -35382,7 +35244,7 @@
         </is>
       </c>
       <c r="B12" s="20" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
@@ -35412,7 +35274,7 @@
         </is>
       </c>
       <c r="B14" s="20" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
@@ -35442,7 +35304,7 @@
         </is>
       </c>
       <c r="B16" s="20" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
@@ -35468,7 +35330,7 @@
         </is>
       </c>
       <c r="B18" s="20" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
@@ -35518,7 +35380,7 @@
         </is>
       </c>
       <c r="B22" s="20" t="n">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
@@ -35543,11 +35405,11 @@
         </is>
       </c>
       <c r="B25" s="20" t="n">
-        <v>3818</v>
+        <v>3772</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>166 CoQs x 23 determinations</t>
+          <t>164 CoQs x 23 determinations</t>
         </is>
       </c>
     </row>
@@ -35558,7 +35420,7 @@
         </is>
       </c>
       <c r="B26" s="20" t="n">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
@@ -35573,7 +35435,7 @@
         </is>
       </c>
       <c r="B27" s="20" t="n">
-        <v>625</v>
+        <v>617</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
@@ -35588,7 +35450,7 @@
         </is>
       </c>
       <c r="B28" s="20" t="n">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
@@ -35603,7 +35465,7 @@
         </is>
       </c>
       <c r="B29" s="20" t="n">
-        <v>913</v>
+        <v>902</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
@@ -35618,7 +35480,7 @@
         </is>
       </c>
       <c r="B30" s="20" t="n">
-        <v>662</v>
+        <v>646</v>
       </c>
       <c r="C30" s="2" t="inlineStr"/>
     </row>
@@ -35644,7 +35506,7 @@
         </is>
       </c>
       <c r="B32" s="20" t="n">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
@@ -35718,7 +35580,7 @@
         </is>
       </c>
       <c r="B38" s="20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C38" s="2" t="inlineStr"/>
     </row>
@@ -35736,7 +35598,7 @@
       <c r="B40" s="20" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>per CoQ, over 166 CoQs</t>
+          <t>per CoQ, over 164 CoQs</t>
         </is>
       </c>
     </row>
@@ -35747,7 +35609,7 @@
         </is>
       </c>
       <c r="B41" s="20" t="n">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
@@ -35762,7 +35624,7 @@
         </is>
       </c>
       <c r="B42" s="20" t="n">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
@@ -35777,7 +35639,7 @@
         </is>
       </c>
       <c r="B43" s="20" t="n">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
@@ -35792,7 +35654,7 @@
         </is>
       </c>
       <c r="B44" s="20" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
@@ -35807,7 +35669,7 @@
         </is>
       </c>
       <c r="B45" s="20" t="n">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
@@ -35822,7 +35684,7 @@
         </is>
       </c>
       <c r="B46" s="20" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
@@ -35837,7 +35699,7 @@
         </is>
       </c>
       <c r="B47" s="20" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>

--- a/deliverables/qc_gap_analysis/PP_QC_Document_Registers_2026-08-31.xlsx
+++ b/deliverables/qc_gap_analysis/PP_QC_Document_Registers_2026-08-31.xlsx
@@ -960,7 +960,7 @@
       <c r="H9" s="11" t="inlineStr"/>
       <c r="I9" s="12" t="inlineStr">
         <is>
-          <t>THC %, CBD %, Loss on drying %</t>
+          <t>THC %, CBD %, Loss on drying %, Ident C</t>
         </is>
       </c>
       <c r="J9" s="8" t="inlineStr">
@@ -1020,7 +1020,7 @@
       <c r="H10" s="6" t="inlineStr"/>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>THC %, CBD %, Loss on drying %</t>
+          <t>THC %, CBD %, Loss on drying %, Ident C</t>
         </is>
       </c>
       <c r="J10" s="8" t="inlineStr">
@@ -1080,7 +1080,7 @@
       <c r="H11" s="11" t="inlineStr"/>
       <c r="I11" s="12" t="inlineStr">
         <is>
-          <t>THC %, CBD %, Loss on drying %</t>
+          <t>THC %, CBD %, Loss on drying %, Ident C</t>
         </is>
       </c>
       <c r="J11" s="8" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="I19" s="12" t="inlineStr">
         <is>
-          <t>THC %, CBD %, Loss on drying %</t>
+          <t>THC %, CBD %, Loss on drying %, Ident C</t>
         </is>
       </c>
       <c r="J19" s="8" t="inlineStr">
@@ -1644,7 +1644,7 @@
       </c>
       <c r="I20" s="7" t="inlineStr">
         <is>
-          <t>THC %, CBD %, Loss on drying %</t>
+          <t>THC %, CBD %, Loss on drying %, Ident C</t>
         </is>
       </c>
       <c r="J20" s="8" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="I22" s="7" t="inlineStr">
         <is>
-          <t>THC %, CBD %, Loss on drying %</t>
+          <t>THC %, CBD %, Loss on drying %, Ident C</t>
         </is>
       </c>
       <c r="J22" s="8" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="I23" s="12" t="inlineStr">
         <is>
-          <t>THC %, CBD %, Loss on drying %</t>
+          <t>THC %, CBD %, Loss on drying %, Ident C</t>
         </is>
       </c>
       <c r="J23" s="8" t="inlineStr">
@@ -2092,7 +2092,7 @@
       </c>
       <c r="I27" s="12" t="inlineStr">
         <is>
-          <t>THC %, CBD %, Loss on drying %</t>
+          <t>THC %, CBD %, Loss on drying %, Ident C</t>
         </is>
       </c>
       <c r="J27" s="8" t="inlineStr">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="I29" s="12" t="inlineStr">
         <is>
-          <t>THC %, CBD %, CBN %, Loss on drying %</t>
+          <t>THC %, CBD %, CBN %, Loss on drying %, Ident C</t>
         </is>
       </c>
       <c r="J29" s="8" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I35" s="12" t="inlineStr">
         <is>
-          <t>THC %, CBD %, Loss on drying %</t>
+          <t>THC %, CBD %, Loss on drying %, Ident C</t>
         </is>
       </c>
       <c r="J35" s="8" t="inlineStr">
@@ -2668,7 +2668,7 @@
       </c>
       <c r="I36" s="7" t="inlineStr">
         <is>
-          <t>THC %, CBD %, Loss on drying %</t>
+          <t>THC %, CBD %, Loss on drying %, Ident C</t>
         </is>
       </c>
       <c r="J36" s="8" t="inlineStr">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="I43" s="12" t="inlineStr">
         <is>
-          <t>THC %, CBD %, Loss on drying %</t>
+          <t>THC %, CBD %, Loss on drying %, Ident C</t>
         </is>
       </c>
       <c r="J43" s="8" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="I44" s="7" t="inlineStr">
         <is>
-          <t>THC %, CBD %, Loss on drying %</t>
+          <t>THC %, CBD %, Loss on drying %, Ident C</t>
         </is>
       </c>
       <c r="J44" s="8" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="I45" s="12" t="inlineStr">
         <is>
-          <t>THC %, CBD %, Loss on drying %</t>
+          <t>THC %, CBD %, Loss on drying %, Ident C</t>
         </is>
       </c>
       <c r="J45" s="8" t="inlineStr">
@@ -3308,7 +3308,7 @@
       </c>
       <c r="I46" s="7" t="inlineStr">
         <is>
-          <t>THC %, CBD %, Loss on drying %</t>
+          <t>THC %, CBD %, Loss on drying %, Ident C</t>
         </is>
       </c>
       <c r="J46" s="8" t="inlineStr">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="I48" s="7" t="inlineStr">
         <is>
-          <t>THC %, CBD %, Loss on drying %</t>
+          <t>THC %, CBD %, Loss on drying %, Ident C</t>
         </is>
       </c>
       <c r="J48" s="8" t="inlineStr">
@@ -3820,7 +3820,7 @@
       </c>
       <c r="I54" s="7" t="inlineStr">
         <is>
-          <t>THC %, CBD %, Loss on drying %</t>
+          <t>THC %, CBD %, Loss on drying %, Ident C</t>
         </is>
       </c>
       <c r="J54" s="8" t="inlineStr">
@@ -4140,7 +4140,7 @@
       </c>
       <c r="I59" s="12" t="inlineStr">
         <is>
-          <t>THC %, CBD %, Loss on drying %</t>
+          <t>THC %, CBD %, Loss on drying %, Ident C</t>
         </is>
       </c>
       <c r="J59" s="8" t="inlineStr">
@@ -4268,7 +4268,7 @@
       </c>
       <c r="I61" s="12" t="inlineStr">
         <is>
-          <t>THC %, CBD %, Loss on drying %</t>
+          <t>THC %, CBD %, Loss on drying %, Ident C</t>
         </is>
       </c>
       <c r="J61" s="8" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="I65" s="12" t="inlineStr">
         <is>
-          <t>THC %, CBD %, Loss on drying %</t>
+          <t>THC %, CBD %, Loss on drying %, Ident C</t>
         </is>
       </c>
       <c r="J65" s="8" t="inlineStr">
@@ -4588,7 +4588,7 @@
       </c>
       <c r="I66" s="7" t="inlineStr">
         <is>
-          <t>THC %, CBD %, Loss on drying %</t>
+          <t>THC %, CBD %, Loss on drying %, Ident C</t>
         </is>
       </c>
       <c r="J66" s="8" t="inlineStr">
@@ -4908,7 +4908,7 @@
       </c>
       <c r="I71" s="12" t="inlineStr">
         <is>
-          <t>THC %, THC spec, CBD %, Loss on drying %</t>
+          <t>THC %, THC spec, CBD %, Loss on drying %, Ident C</t>
         </is>
       </c>
       <c r="J71" s="8" t="inlineStr">
@@ -4972,7 +4972,7 @@
       </c>
       <c r="I72" s="7" t="inlineStr">
         <is>
-          <t>THC %, THC spec, CBD %, Loss on drying %</t>
+          <t>THC %, THC spec, CBD %, Loss on drying %, Ident C</t>
         </is>
       </c>
       <c r="J72" s="8" t="inlineStr">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="I78" s="7" t="inlineStr">
         <is>
-          <t>THC %, THC spec, CBD %, Loss on drying %</t>
+          <t>THC %, THC spec, CBD %, Loss on drying %, Ident C</t>
         </is>
       </c>
       <c r="J78" s="9" t="inlineStr">
@@ -5420,7 +5420,7 @@
       </c>
       <c r="I79" s="12" t="inlineStr">
         <is>
-          <t>THC %, THC spec, CBD %, Loss on drying %</t>
+          <t>THC %, THC spec, CBD %, Loss on drying %, Ident C</t>
         </is>
       </c>
       <c r="J79" s="9" t="inlineStr">
@@ -5484,7 +5484,7 @@
       </c>
       <c r="I80" s="7" t="inlineStr">
         <is>
-          <t>THC %, THC spec, CBD %, Loss on drying %</t>
+          <t>THC %, THC spec, CBD %, Loss on drying %, Ident C</t>
         </is>
       </c>
       <c r="J80" s="8" t="inlineStr">
@@ -5548,7 +5548,7 @@
       </c>
       <c r="I81" s="12" t="inlineStr">
         <is>
-          <t>THC %, THC spec, CBD %, Loss on drying %</t>
+          <t>THC %, THC spec, CBD %, Loss on drying %, Ident C</t>
         </is>
       </c>
       <c r="J81" s="8" t="inlineStr">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="I82" s="7" t="inlineStr">
         <is>
-          <t>THC %, THC spec, CBD %, Loss on drying %</t>
+          <t>THC %, THC spec, CBD %, Loss on drying %, Ident C</t>
         </is>
       </c>
       <c r="J82" s="8" t="inlineStr">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="I118" s="7" t="inlineStr">
         <is>
-          <t>THC %, THC spec, CBD %, Loss on drying %</t>
+          <t>THC %, THC spec, CBD %, Loss on drying %, Ident C</t>
         </is>
       </c>
       <c r="J118" s="8" t="inlineStr">
@@ -7980,7 +7980,7 @@
       </c>
       <c r="I119" s="12" t="inlineStr">
         <is>
-          <t>THC %, THC spec, CBD %, Loss on drying %</t>
+          <t>THC %, THC spec, CBD %, Loss on drying %, Ident C</t>
         </is>
       </c>
       <c r="J119" s="8" t="inlineStr">
@@ -8044,7 +8044,7 @@
       </c>
       <c r="I120" s="7" t="inlineStr">
         <is>
-          <t>THC %, THC spec, CBD %, Loss on drying %</t>
+          <t>THC %, THC spec, CBD %, Loss on drying %, Ident C</t>
         </is>
       </c>
       <c r="J120" s="8" t="inlineStr">
@@ -8108,7 +8108,7 @@
       </c>
       <c r="I121" s="12" t="inlineStr">
         <is>
-          <t>THC %, THC spec, CBD %, Loss on drying %</t>
+          <t>THC %, THC spec, CBD %, Loss on drying %, Ident C</t>
         </is>
       </c>
       <c r="J121" s="8" t="inlineStr">
@@ -8172,7 +8172,7 @@
       </c>
       <c r="I122" s="7" t="inlineStr">
         <is>
-          <t>THC %, THC spec, CBD %, Loss on drying %</t>
+          <t>THC %, THC spec, CBD %, Loss on drying %, Ident C</t>
         </is>
       </c>
       <c r="J122" s="8" t="inlineStr">
@@ -8236,7 +8236,7 @@
       </c>
       <c r="I123" s="12" t="inlineStr">
         <is>
-          <t>THC %, THC spec, CBD %, Loss on drying %</t>
+          <t>THC %, THC spec, CBD %, Loss on drying %, Ident C</t>
         </is>
       </c>
       <c r="J123" s="8" t="inlineStr">
@@ -8300,7 +8300,7 @@
       </c>
       <c r="I124" s="7" t="inlineStr">
         <is>
-          <t>THC %, THC spec, CBD %, Loss on drying %</t>
+          <t>THC %, THC spec, CBD %, Loss on drying %, Ident C</t>
         </is>
       </c>
       <c r="J124" s="8" t="inlineStr">
@@ -8364,7 +8364,7 @@
       </c>
       <c r="I125" s="12" t="inlineStr">
         <is>
-          <t>THC %, THC spec, CBD %, Loss on drying %</t>
+          <t>THC %, THC spec, CBD %, Loss on drying %, Ident C</t>
         </is>
       </c>
       <c r="J125" s="8" t="inlineStr">
@@ -8428,7 +8428,7 @@
       </c>
       <c r="I126" s="7" t="inlineStr">
         <is>
-          <t>THC %, THC spec, CBD %, Loss on drying %</t>
+          <t>THC %, THC spec, CBD %, Loss on drying %, Ident C</t>
         </is>
       </c>
       <c r="J126" s="8" t="inlineStr">
@@ -8492,7 +8492,7 @@
       </c>
       <c r="I127" s="12" t="inlineStr">
         <is>
-          <t>THC %, THC spec, CBD %, Loss on drying %</t>
+          <t>THC %, THC spec, CBD %, Loss on drying %, Ident C</t>
         </is>
       </c>
       <c r="J127" s="8" t="inlineStr">
@@ -8620,7 +8620,7 @@
       </c>
       <c r="I129" s="12" t="inlineStr">
         <is>
-          <t>THC %, THC spec, CBD %, Loss on drying %</t>
+          <t>THC %, THC spec, CBD %, Loss on drying %, Ident C</t>
         </is>
       </c>
       <c r="J129" s="8" t="inlineStr">
@@ -8684,7 +8684,7 @@
       </c>
       <c r="I130" s="7" t="inlineStr">
         <is>
-          <t>THC %, THC spec, CBD %, Loss on drying %</t>
+          <t>THC %, THC spec, CBD %, Loss on drying %, Ident C</t>
         </is>
       </c>
       <c r="J130" s="8" t="inlineStr">
@@ -8748,7 +8748,7 @@
       </c>
       <c r="I131" s="12" t="inlineStr">
         <is>
-          <t>THC %, THC spec, CBD %, Loss on drying %</t>
+          <t>THC %, THC spec, CBD %, Loss on drying %, Ident C</t>
         </is>
       </c>
       <c r="J131" s="8" t="inlineStr">
@@ -8812,7 +8812,7 @@
       </c>
       <c r="I132" s="7" t="inlineStr">
         <is>
-          <t>THC %, THC spec, CBD %, Loss on drying %</t>
+          <t>THC %, THC spec, CBD %, Loss on drying %, Ident C</t>
         </is>
       </c>
       <c r="J132" s="8" t="inlineStr">
@@ -10448,7 +10448,7 @@
       <c r="H158" s="6" t="inlineStr"/>
       <c r="I158" s="7" t="inlineStr">
         <is>
-          <t>THC %, CBD %, CBN %</t>
+          <t>THC %, CBD %, CBN %, Ident C</t>
         </is>
       </c>
       <c r="J158" s="8" t="inlineStr">
@@ -10508,7 +10508,7 @@
       <c r="H159" s="11" t="inlineStr"/>
       <c r="I159" s="12" t="inlineStr">
         <is>
-          <t>THC %, CBD %, CBN %</t>
+          <t>THC %, CBD %, CBN %, Ident C</t>
         </is>
       </c>
       <c r="J159" s="8" t="inlineStr">
@@ -10568,7 +10568,7 @@
       <c r="H160" s="6" t="inlineStr"/>
       <c r="I160" s="7" t="inlineStr">
         <is>
-          <t>THC %, CBD %, CBN %</t>
+          <t>THC %, CBD %, CBN %, Ident C</t>
         </is>
       </c>
       <c r="J160" s="8" t="inlineStr">
@@ -10628,7 +10628,7 @@
       <c r="H161" s="11" t="inlineStr"/>
       <c r="I161" s="12" t="inlineStr">
         <is>
-          <t>THC %, CBD %, CBN %</t>
+          <t>THC %, CBD %, CBN %, Ident C</t>
         </is>
       </c>
       <c r="J161" s="8" t="inlineStr">
@@ -10688,7 +10688,7 @@
       <c r="H162" s="6" t="inlineStr"/>
       <c r="I162" s="7" t="inlineStr">
         <is>
-          <t>THC %, CBD %, CBN %</t>
+          <t>THC %, CBD %, CBN %, Ident C</t>
         </is>
       </c>
       <c r="J162" s="8" t="inlineStr">
@@ -10748,7 +10748,7 @@
       <c r="H163" s="11" t="inlineStr"/>
       <c r="I163" s="12" t="inlineStr">
         <is>
-          <t>THC %, CBD %, CBN %</t>
+          <t>THC %, CBD %, CBN %, Ident C</t>
         </is>
       </c>
       <c r="J163" s="8" t="inlineStr">
@@ -10812,7 +10812,7 @@
       </c>
       <c r="I164" s="7" t="inlineStr">
         <is>
-          <t>THC %, CBD %, CBN %, Loss on drying %</t>
+          <t>THC %, CBD %, CBN %, Loss on drying %, Ident C</t>
         </is>
       </c>
       <c r="J164" s="8" t="inlineStr">
@@ -10876,7 +10876,7 @@
       </c>
       <c r="I165" s="12" t="inlineStr">
         <is>
-          <t>THC %, CBD %, CBN %, Loss on drying %</t>
+          <t>THC %, CBD %, CBN %, Loss on drying %, Ident C</t>
         </is>
       </c>
       <c r="J165" s="8" t="inlineStr">
@@ -10940,7 +10940,7 @@
       </c>
       <c r="I166" s="7" t="inlineStr">
         <is>
-          <t>THC %, CBD %, CBN %, Loss on drying %</t>
+          <t>THC %, CBD %, CBN %, Loss on drying %, Ident C</t>
         </is>
       </c>
       <c r="J166" s="8" t="inlineStr">
@@ -11004,7 +11004,7 @@
       </c>
       <c r="I167" s="12" t="inlineStr">
         <is>
-          <t>THC %, CBD %, CBN %, Loss on drying %</t>
+          <t>THC %, CBD %, CBN %, Loss on drying %, Ident C</t>
         </is>
       </c>
       <c r="J167" s="8" t="inlineStr">
@@ -11068,7 +11068,7 @@
       </c>
       <c r="I168" s="7" t="inlineStr">
         <is>
-          <t>THC %, CBD %, CBN %, Loss on drying %</t>
+          <t>THC %, CBD %, CBN %, Loss on drying %, Ident C</t>
         </is>
       </c>
       <c r="J168" s="8" t="inlineStr">
@@ -11132,7 +11132,7 @@
       </c>
       <c r="I169" s="12" t="inlineStr">
         <is>
-          <t>THC %, CBD %, CBN %, Loss on drying %</t>
+          <t>THC %, CBD %, CBN %, Loss on drying %, Ident C</t>
         </is>
       </c>
       <c r="J169" s="8" t="inlineStr">
@@ -11192,7 +11192,7 @@
       <c r="H170" s="6" t="inlineStr"/>
       <c r="I170" s="7" t="inlineStr">
         <is>
-          <t>THC %, CBD %, Loss on drying %</t>
+          <t>THC %, CBD %, Loss on drying %, Ident C</t>
         </is>
       </c>
       <c r="J170" s="8" t="inlineStr">
@@ -11252,7 +11252,7 @@
       <c r="H171" s="11" t="inlineStr"/>
       <c r="I171" s="12" t="inlineStr">
         <is>
-          <t>THC %, CBD %, Loss on drying %</t>
+          <t>THC %, CBD %, Loss on drying %, Ident C</t>
         </is>
       </c>
       <c r="J171" s="8" t="inlineStr">
@@ -11552,7 +11552,7 @@
       <c r="H176" s="6" t="inlineStr"/>
       <c r="I176" s="7" t="inlineStr">
         <is>
-          <t>THC %, CBD %, CBN %</t>
+          <t>THC %, CBD %, CBN %, Ident C</t>
         </is>
       </c>
       <c r="J176" s="8" t="inlineStr">
@@ -11612,7 +11612,7 @@
       <c r="H177" s="11" t="inlineStr"/>
       <c r="I177" s="12" t="inlineStr">
         <is>
-          <t>THC %, CBD %, CBN %</t>
+          <t>THC %, CBD %, CBN %, Ident C</t>
         </is>
       </c>
       <c r="J177" s="8" t="inlineStr">
@@ -11732,7 +11732,7 @@
       <c r="H179" s="11" t="inlineStr"/>
       <c r="I179" s="12" t="inlineStr">
         <is>
-          <t>THC %, CBD %, CBN %</t>
+          <t>THC %, CBD %, CBN %, Ident C</t>
         </is>
       </c>
       <c r="J179" s="8" t="inlineStr">
@@ -11852,7 +11852,7 @@
       <c r="H181" s="11" t="inlineStr"/>
       <c r="I181" s="12" t="inlineStr">
         <is>
-          <t>THC %, CBD %, CBN %</t>
+          <t>THC %, CBD %, CBN %, Ident C</t>
         </is>
       </c>
       <c r="J181" s="8" t="inlineStr">
@@ -12156,7 +12156,7 @@
       </c>
       <c r="I186" s="7" t="inlineStr">
         <is>
-          <t>THC %, CBD %, CBN %, Loss on drying %</t>
+          <t>THC %, CBD %, CBN %, Loss on drying %, Ident C</t>
         </is>
       </c>
       <c r="J186" s="8" t="inlineStr">
@@ -12220,7 +12220,7 @@
       </c>
       <c r="I187" s="12" t="inlineStr">
         <is>
-          <t>THC %, CBD %, CBN %, Loss on drying %</t>
+          <t>THC %, CBD %, CBN %, Loss on drying %, Ident C</t>
         </is>
       </c>
       <c r="J187" s="8" t="inlineStr">
@@ -12284,7 +12284,7 @@
       </c>
       <c r="I188" s="7" t="inlineStr">
         <is>
-          <t>THC %, CBD %, CBN %, Loss on drying %</t>
+          <t>THC %, CBD %, CBN %, Loss on drying %, Ident C</t>
         </is>
       </c>
       <c r="J188" s="8" t="inlineStr">
@@ -12348,7 +12348,7 @@
       </c>
       <c r="I189" s="12" t="inlineStr">
         <is>
-          <t>THC %, CBD %, CBN %, Loss on drying %</t>
+          <t>THC %, CBD %, CBN %, Loss on drying %, Ident C</t>
         </is>
       </c>
       <c r="J189" s="8" t="inlineStr">
@@ -12408,7 +12408,7 @@
       <c r="H190" s="6" t="inlineStr"/>
       <c r="I190" s="7" t="inlineStr">
         <is>
-          <t>THC %, CBD %, Loss on drying %</t>
+          <t>THC %, CBD %, Loss on drying %, Ident C</t>
         </is>
       </c>
       <c r="J190" s="8" t="inlineStr">
@@ -12468,7 +12468,7 @@
       <c r="H191" s="11" t="inlineStr"/>
       <c r="I191" s="12" t="inlineStr">
         <is>
-          <t>THC %, CBD %, Loss on drying %</t>
+          <t>THC %, CBD %, Loss on drying %, Ident C</t>
         </is>
       </c>
       <c r="J191" s="8" t="inlineStr">
@@ -12528,7 +12528,7 @@
       <c r="H192" s="6" t="inlineStr"/>
       <c r="I192" s="7" t="inlineStr">
         <is>
-          <t>THC %, CBD %, Loss on drying %</t>
+          <t>THC %, CBD %, Loss on drying %, Ident C</t>
         </is>
       </c>
       <c r="J192" s="8" t="inlineStr">
@@ -12588,7 +12588,7 @@
       <c r="H193" s="11" t="inlineStr"/>
       <c r="I193" s="12" t="inlineStr">
         <is>
-          <t>THC %, CBD %, Loss on drying %</t>
+          <t>THC %, CBD %, Loss on drying %, Ident C</t>
         </is>
       </c>
       <c r="J193" s="8" t="inlineStr">
@@ -12648,7 +12648,7 @@
       <c r="H194" s="6" t="inlineStr"/>
       <c r="I194" s="7" t="inlineStr">
         <is>
-          <t>THC %, CBD %, Loss on drying %</t>
+          <t>THC %, CBD %, Loss on drying %, Ident C</t>
         </is>
       </c>
       <c r="J194" s="8" t="inlineStr">
@@ -12708,7 +12708,7 @@
       <c r="H195" s="11" t="inlineStr"/>
       <c r="I195" s="12" t="inlineStr">
         <is>
-          <t>THC %, CBD %, Loss on drying %</t>
+          <t>THC %, CBD %, Loss on drying %, Ident C</t>
         </is>
       </c>
       <c r="J195" s="8" t="inlineStr">
@@ -12768,7 +12768,7 @@
       <c r="H196" s="6" t="inlineStr"/>
       <c r="I196" s="7" t="inlineStr">
         <is>
-          <t>THC %, CBD %, Loss on drying %</t>
+          <t>THC %, CBD %, Loss on drying %, Ident C</t>
         </is>
       </c>
       <c r="J196" s="8" t="inlineStr">
@@ -12828,7 +12828,7 @@
       <c r="H197" s="11" t="inlineStr"/>
       <c r="I197" s="12" t="inlineStr">
         <is>
-          <t>THC %, CBD %, Loss on drying %</t>
+          <t>THC %, CBD %, Loss on drying %, Ident C</t>
         </is>
       </c>
       <c r="J197" s="8" t="inlineStr">
@@ -12888,7 +12888,7 @@
       <c r="H198" s="6" t="inlineStr"/>
       <c r="I198" s="7" t="inlineStr">
         <is>
-          <t>THC %, CBD %, Loss on drying %</t>
+          <t>THC %, CBD %, Loss on drying %, Ident C</t>
         </is>
       </c>
       <c r="J198" s="8" t="inlineStr">
@@ -12948,7 +12948,7 @@
       <c r="H199" s="11" t="inlineStr"/>
       <c r="I199" s="12" t="inlineStr">
         <is>
-          <t>THC %, THC spec, CBD %, CBN %, Loss on drying %, Ident A + B, Foreign matter</t>
+          <t>THC %, THC spec, CBD %, CBN %, Loss on drying %, Ident A + B, Foreign matter, Ident C</t>
         </is>
       </c>
       <c r="J199" s="8" t="inlineStr">
@@ -13008,7 +13008,7 @@
       <c r="H200" s="6" t="inlineStr"/>
       <c r="I200" s="7" t="inlineStr">
         <is>
-          <t>THC %, THC spec, CBD %, CBN %, Loss on drying %, Ident A + B, Foreign matter</t>
+          <t>THC %, THC spec, CBD %, CBN %, Loss on drying %, Ident A + B, Foreign matter, Ident C</t>
         </is>
       </c>
       <c r="J200" s="8" t="inlineStr">
@@ -13068,7 +13068,7 @@
       <c r="H201" s="11" t="inlineStr"/>
       <c r="I201" s="12" t="inlineStr">
         <is>
-          <t>THC %, THC spec, CBD %, CBN %, Loss on drying %, Ident A + B, Foreign matter</t>
+          <t>THC %, THC spec, CBD %, CBN %, Loss on drying %, Ident A + B, Foreign matter, Ident C</t>
         </is>
       </c>
       <c r="J201" s="8" t="inlineStr">
@@ -13128,7 +13128,7 @@
       <c r="H202" s="6" t="inlineStr"/>
       <c r="I202" s="7" t="inlineStr">
         <is>
-          <t>THC %, THC spec, CBD %, CBN %, Loss on drying %, Ident A + B, Foreign matter</t>
+          <t>THC %, THC spec, CBD %, CBN %, Loss on drying %, Ident A + B, Foreign matter, Ident C</t>
         </is>
       </c>
       <c r="J202" s="8" t="inlineStr">
@@ -13188,7 +13188,7 @@
       <c r="H203" s="11" t="inlineStr"/>
       <c r="I203" s="12" t="inlineStr">
         <is>
-          <t>THC %, THC spec, CBD %, CBN %, Loss on drying %, Ident A + B, Foreign matter</t>
+          <t>THC %, THC spec, CBD %, CBN %, Loss on drying %, Ident A + B, Foreign matter, Ident C</t>
         </is>
       </c>
       <c r="J203" s="8" t="inlineStr">
@@ -13248,7 +13248,7 @@
       <c r="H204" s="6" t="inlineStr"/>
       <c r="I204" s="7" t="inlineStr">
         <is>
-          <t>THC %, THC spec, CBD %, CBN %, Loss on drying %, Ident A + B, Foreign matter</t>
+          <t>THC %, THC spec, CBD %, CBN %, Loss on drying %, Ident A + B, Foreign matter, Ident C</t>
         </is>
       </c>
       <c r="J204" s="8" t="inlineStr">
@@ -13312,7 +13312,7 @@
       </c>
       <c r="I205" s="12" t="inlineStr">
         <is>
-          <t>THC %, THC spec, CBD %, CBN %, Loss on drying %, Ident A + B, Foreign matter</t>
+          <t>THC %, THC spec, CBD %, CBN %, Loss on drying %, Ident A + B, Foreign matter, Ident C</t>
         </is>
       </c>
       <c r="J205" s="8" t="inlineStr">
@@ -13376,7 +13376,7 @@
       </c>
       <c r="I206" s="7" t="inlineStr">
         <is>
-          <t>THC %, THC spec, CBD %, CBN %, Loss on drying %, Ident A + B, Foreign matter</t>
+          <t>THC %, THC spec, CBD %, CBN %, Loss on drying %, Ident A + B, Foreign matter, Ident C</t>
         </is>
       </c>
       <c r="J206" s="8" t="inlineStr">
@@ -13440,7 +13440,7 @@
       </c>
       <c r="I207" s="12" t="inlineStr">
         <is>
-          <t>THC %, THC spec, CBD %, CBN %, Loss on drying %, Ident A + B, Foreign matter</t>
+          <t>THC %, THC spec, CBD %, CBN %, Loss on drying %, Ident A + B, Foreign matter, Ident C</t>
         </is>
       </c>
       <c r="J207" s="8" t="inlineStr">
@@ -13500,7 +13500,7 @@
       <c r="H208" s="6" t="inlineStr"/>
       <c r="I208" s="7" t="inlineStr">
         <is>
-          <t>THC %, THC spec, CBD %, CBN %, Loss on drying %, Ident A + B, Foreign matter</t>
+          <t>THC %, THC spec, CBD %, CBN %, Loss on drying %, Ident A + B, Foreign matter, Ident C</t>
         </is>
       </c>
       <c r="J208" s="8" t="inlineStr">
@@ -13560,7 +13560,7 @@
       <c r="H209" s="11" t="inlineStr"/>
       <c r="I209" s="12" t="inlineStr">
         <is>
-          <t>THC %, THC spec, CBD %, CBN %, Loss on drying %, Ident A + B, Foreign matter</t>
+          <t>THC %, THC spec, CBD %, CBN %, Loss on drying %, Ident A + B, Foreign matter, Ident C</t>
         </is>
       </c>
       <c r="J209" s="8" t="inlineStr">
@@ -13620,7 +13620,7 @@
       <c r="H210" s="6" t="inlineStr"/>
       <c r="I210" s="7" t="inlineStr">
         <is>
-          <t>THC %, THC spec, CBD %, CBN %, Loss on drying %, Ident A + B, Foreign matter</t>
+          <t>THC %, THC spec, CBD %, CBN %, Loss on drying %, Ident A + B, Foreign matter, Ident C</t>
         </is>
       </c>
       <c r="J210" s="8" t="inlineStr">
@@ -13680,7 +13680,7 @@
       <c r="H211" s="11" t="inlineStr"/>
       <c r="I211" s="12" t="inlineStr">
         <is>
-          <t>THC %, THC spec, CBD %, CBN %</t>
+          <t>THC %, THC spec, CBD %, CBN %, Ident C</t>
         </is>
       </c>
       <c r="J211" s="8" t="inlineStr">
@@ -13740,7 +13740,7 @@
       <c r="H212" s="6" t="inlineStr"/>
       <c r="I212" s="7" t="inlineStr">
         <is>
-          <t>THC %, THC spec, CBD %, CBN %</t>
+          <t>THC %, THC spec, CBD %, CBN %, Ident C</t>
         </is>
       </c>
       <c r="J212" s="8" t="inlineStr">
@@ -13804,7 +13804,7 @@
       </c>
       <c r="I213" s="12" t="inlineStr">
         <is>
-          <t>THC %, THC spec, CBD %, CBN %</t>
+          <t>THC %, THC spec, CBD %, CBN %, Ident C</t>
         </is>
       </c>
       <c r="J213" s="8" t="inlineStr">
@@ -13868,7 +13868,7 @@
       </c>
       <c r="I214" s="7" t="inlineStr">
         <is>
-          <t>THC %, THC spec, CBD %, CBN %</t>
+          <t>THC %, THC spec, CBD %, CBN %, Ident C</t>
         </is>
       </c>
       <c r="J214" s="8" t="inlineStr">
@@ -13932,7 +13932,7 @@
       </c>
       <c r="I215" s="12" t="inlineStr">
         <is>
-          <t>THC %, THC spec, CBD %, CBN %</t>
+          <t>THC %, THC spec, CBD %, CBN %, Ident C</t>
         </is>
       </c>
       <c r="J215" s="8" t="inlineStr">
@@ -13996,7 +13996,7 @@
       </c>
       <c r="I216" s="7" t="inlineStr">
         <is>
-          <t>THC %, THC spec, CBD %, CBN %</t>
+          <t>THC %, THC spec, CBD %, CBN %, Ident C</t>
         </is>
       </c>
       <c r="J216" s="8" t="inlineStr">
@@ -14060,7 +14060,7 @@
       </c>
       <c r="I217" s="12" t="inlineStr">
         <is>
-          <t>THC %, THC spec, CBD %, CBN %</t>
+          <t>THC %, THC spec, CBD %, CBN %, Ident C</t>
         </is>
       </c>
       <c r="J217" s="8" t="inlineStr">
@@ -14124,7 +14124,7 @@
       </c>
       <c r="I218" s="7" t="inlineStr">
         <is>
-          <t>THC %, THC spec, CBD %, CBN %</t>
+          <t>THC %, THC spec, CBD %, CBN %, Ident C</t>
         </is>
       </c>
       <c r="J218" s="8" t="inlineStr">
@@ -14188,7 +14188,7 @@
       </c>
       <c r="I219" s="12" t="inlineStr">
         <is>
-          <t>THC %, THC spec, CBD %, CBN %</t>
+          <t>THC %, THC spec, CBD %, CBN %, Ident C</t>
         </is>
       </c>
       <c r="J219" s="8" t="inlineStr">
@@ -14252,7 +14252,7 @@
       </c>
       <c r="I220" s="7" t="inlineStr">
         <is>
-          <t>THC %, THC spec, CBD %, CBN %</t>
+          <t>THC %, THC spec, CBD %, CBN %, Ident C</t>
         </is>
       </c>
       <c r="J220" s="8" t="inlineStr">
@@ -14316,7 +14316,7 @@
       </c>
       <c r="I221" s="12" t="inlineStr">
         <is>
-          <t>THC %, THC spec, CBD %, CBN %</t>
+          <t>THC %, THC spec, CBD %, CBN %, Ident C</t>
         </is>
       </c>
       <c r="J221" s="8" t="inlineStr">
@@ -14380,7 +14380,7 @@
       </c>
       <c r="I222" s="7" t="inlineStr">
         <is>
-          <t>THC %, THC spec, CBD %, CBN %</t>
+          <t>THC %, THC spec, CBD %, CBN %, Ident C</t>
         </is>
       </c>
       <c r="J222" s="8" t="inlineStr">
@@ -14444,7 +14444,7 @@
       </c>
       <c r="I223" s="12" t="inlineStr">
         <is>
-          <t>THC %, THC spec, CBD %, CBN %</t>
+          <t>THC %, THC spec, CBD %, CBN %, Ident C</t>
         </is>
       </c>
       <c r="J223" s="8" t="inlineStr">
@@ -14512,7 +14512,7 @@
       </c>
       <c r="I224" s="7" t="inlineStr">
         <is>
-          <t>THC %, THC spec, CBD %, CBN %</t>
+          <t>THC %, THC spec, CBD %, CBN %, Ident C</t>
         </is>
       </c>
       <c r="J224" s="8" t="inlineStr">
@@ -14580,7 +14580,7 @@
       </c>
       <c r="I225" s="12" t="inlineStr">
         <is>
-          <t>THC %, THC spec, CBD %, CBN %</t>
+          <t>THC %, THC spec, CBD %, CBN %, Ident C</t>
         </is>
       </c>
       <c r="J225" s="8" t="inlineStr">
@@ -14648,7 +14648,7 @@
       </c>
       <c r="I226" s="7" t="inlineStr">
         <is>
-          <t>THC %, THC spec, CBD %, CBN %</t>
+          <t>THC %, THC spec, CBD %, CBN %, Ident C</t>
         </is>
       </c>
       <c r="J226" s="8" t="inlineStr">
@@ -14712,7 +14712,7 @@
       </c>
       <c r="I227" s="12" t="inlineStr">
         <is>
-          <t>THC %, THC spec, CBD %, CBN %</t>
+          <t>THC %, THC spec, CBD %, CBN %, Ident C</t>
         </is>
       </c>
       <c r="J227" s="8" t="inlineStr">
@@ -14780,7 +14780,7 @@
       </c>
       <c r="I228" s="7" t="inlineStr">
         <is>
-          <t>THC %, THC spec, CBD %, CBN %</t>
+          <t>THC %, THC spec, CBD %, CBN %, Ident C</t>
         </is>
       </c>
       <c r="J228" s="8" t="inlineStr">
@@ -14848,7 +14848,7 @@
       </c>
       <c r="I229" s="12" t="inlineStr">
         <is>
-          <t>THC %, THC spec, CBD %, CBN %</t>
+          <t>THC %, THC spec, CBD %, CBN %, Ident C</t>
         </is>
       </c>
       <c r="J229" s="8" t="inlineStr">
@@ -14912,7 +14912,7 @@
       <c r="H230" s="6" t="inlineStr"/>
       <c r="I230" s="7" t="inlineStr">
         <is>
-          <t>THC %, THC spec, CBD %, CBN %</t>
+          <t>THC %, THC spec, CBD %, CBN %, Ident C</t>
         </is>
       </c>
       <c r="J230" s="8" t="inlineStr">
@@ -14972,7 +14972,7 @@
       <c r="H231" s="11" t="inlineStr"/>
       <c r="I231" s="12" t="inlineStr">
         <is>
-          <t>THC %, THC spec, CBD %, CBN %</t>
+          <t>THC %, THC spec, CBD %, CBN %, Ident C</t>
         </is>
       </c>
       <c r="J231" s="8" t="inlineStr">
@@ -16904,9 +16904,9 @@
           <t>required</t>
         </is>
       </c>
-      <c r="I6" s="14" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>covered by CNP</t>
         </is>
       </c>
       <c r="J6" s="14" t="inlineStr">
@@ -16974,9 +16974,9 @@
           <t>required</t>
         </is>
       </c>
-      <c r="I7" s="14" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="I7" s="8" t="inlineStr">
+        <is>
+          <t>covered by CNP</t>
         </is>
       </c>
       <c r="J7" s="14" t="inlineStr">
@@ -17040,9 +17040,9 @@
           <t>required</t>
         </is>
       </c>
-      <c r="I8" s="14" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>covered by CNP</t>
         </is>
       </c>
       <c r="J8" s="14" t="inlineStr">
@@ -17106,9 +17106,9 @@
           <t>required</t>
         </is>
       </c>
-      <c r="I9" s="14" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="I9" s="8" t="inlineStr">
+        <is>
+          <t>covered by CNP</t>
         </is>
       </c>
       <c r="J9" s="14" t="inlineStr">
@@ -17168,9 +17168,9 @@
           <t>required</t>
         </is>
       </c>
-      <c r="I10" s="14" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="I10" s="8" t="inlineStr">
+        <is>
+          <t>covered by CNP</t>
         </is>
       </c>
       <c r="J10" s="14" t="inlineStr">
@@ -17234,9 +17234,9 @@
           <t>required</t>
         </is>
       </c>
-      <c r="I11" s="14" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="I11" s="8" t="inlineStr">
+        <is>
+          <t>covered by CNP</t>
         </is>
       </c>
       <c r="J11" s="14" t="inlineStr">
@@ -17296,9 +17296,9 @@
           <t>required</t>
         </is>
       </c>
-      <c r="I12" s="14" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="I12" s="8" t="inlineStr">
+        <is>
+          <t>covered by CNP</t>
         </is>
       </c>
       <c r="J12" s="14" t="inlineStr">
@@ -17366,9 +17366,9 @@
           <t>required</t>
         </is>
       </c>
-      <c r="I13" s="14" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="I13" s="8" t="inlineStr">
+        <is>
+          <t>covered by CNP</t>
         </is>
       </c>
       <c r="J13" s="14" t="inlineStr">
@@ -17428,9 +17428,9 @@
           <t>required</t>
         </is>
       </c>
-      <c r="I14" s="14" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="I14" s="8" t="inlineStr">
+        <is>
+          <t>covered by CNP</t>
         </is>
       </c>
       <c r="J14" s="14" t="inlineStr">
@@ -17494,9 +17494,9 @@
           <t>required</t>
         </is>
       </c>
-      <c r="I15" s="14" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="I15" s="8" t="inlineStr">
+        <is>
+          <t>covered by CNP</t>
         </is>
       </c>
       <c r="J15" s="14" t="inlineStr">
@@ -17556,9 +17556,9 @@
           <t>required</t>
         </is>
       </c>
-      <c r="I16" s="14" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="I16" s="8" t="inlineStr">
+        <is>
+          <t>covered by CNP</t>
         </is>
       </c>
       <c r="J16" s="14" t="inlineStr">
@@ -17622,9 +17622,9 @@
           <t>required</t>
         </is>
       </c>
-      <c r="I17" s="14" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="I17" s="8" t="inlineStr">
+        <is>
+          <t>covered by CNP</t>
         </is>
       </c>
       <c r="J17" s="14" t="inlineStr">
@@ -17688,9 +17688,9 @@
           <t>required</t>
         </is>
       </c>
-      <c r="I18" s="14" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="I18" s="8" t="inlineStr">
+        <is>
+          <t>covered by CNP</t>
         </is>
       </c>
       <c r="J18" s="14" t="inlineStr">
@@ -17750,9 +17750,9 @@
           <t>required</t>
         </is>
       </c>
-      <c r="I19" s="14" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="I19" s="8" t="inlineStr">
+        <is>
+          <t>covered by CNP</t>
         </is>
       </c>
       <c r="J19" s="14" t="inlineStr">
@@ -17812,9 +17812,9 @@
           <t>required</t>
         </is>
       </c>
-      <c r="I20" s="14" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="I20" s="8" t="inlineStr">
+        <is>
+          <t>covered by CNP</t>
         </is>
       </c>
       <c r="J20" s="14" t="inlineStr">
@@ -17874,9 +17874,9 @@
           <t>required</t>
         </is>
       </c>
-      <c r="I21" s="14" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="I21" s="8" t="inlineStr">
+        <is>
+          <t>covered by CNP</t>
         </is>
       </c>
       <c r="J21" s="14" t="inlineStr">
@@ -17936,9 +17936,9 @@
           <t>required</t>
         </is>
       </c>
-      <c r="I22" s="14" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="I22" s="8" t="inlineStr">
+        <is>
+          <t>covered by CNP</t>
         </is>
       </c>
       <c r="J22" s="14" t="inlineStr">
@@ -18002,9 +18002,9 @@
           <t>required</t>
         </is>
       </c>
-      <c r="I23" s="14" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="I23" s="8" t="inlineStr">
+        <is>
+          <t>covered by CNP</t>
         </is>
       </c>
       <c r="J23" s="14" t="inlineStr">
@@ -18064,9 +18064,9 @@
           <t>required</t>
         </is>
       </c>
-      <c r="I24" s="14" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="I24" s="8" t="inlineStr">
+        <is>
+          <t>covered by CNP</t>
         </is>
       </c>
       <c r="J24" s="14" t="inlineStr">
@@ -18130,9 +18130,9 @@
           <t>required</t>
         </is>
       </c>
-      <c r="I25" s="14" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="I25" s="8" t="inlineStr">
+        <is>
+          <t>covered by CNP</t>
         </is>
       </c>
       <c r="J25" s="14" t="inlineStr">
@@ -18192,9 +18192,9 @@
           <t>required</t>
         </is>
       </c>
-      <c r="I26" s="14" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="I26" s="8" t="inlineStr">
+        <is>
+          <t>covered by CNP</t>
         </is>
       </c>
       <c r="J26" s="14" t="inlineStr">
@@ -18254,9 +18254,9 @@
           <t>required</t>
         </is>
       </c>
-      <c r="I27" s="14" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="I27" s="8" t="inlineStr">
+        <is>
+          <t>covered by CNP</t>
         </is>
       </c>
       <c r="J27" s="14" t="inlineStr">
@@ -18316,9 +18316,9 @@
           <t>required</t>
         </is>
       </c>
-      <c r="I28" s="14" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="I28" s="8" t="inlineStr">
+        <is>
+          <t>covered by CNP</t>
         </is>
       </c>
       <c r="J28" s="14" t="inlineStr">
@@ -18378,9 +18378,9 @@
           <t>required</t>
         </is>
       </c>
-      <c r="I29" s="14" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="I29" s="8" t="inlineStr">
+        <is>
+          <t>covered by CNP</t>
         </is>
       </c>
       <c r="J29" s="14" t="inlineStr">
@@ -18440,9 +18440,9 @@
           <t>required</t>
         </is>
       </c>
-      <c r="I30" s="14" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="I30" s="8" t="inlineStr">
+        <is>
+          <t>covered by CNP</t>
         </is>
       </c>
       <c r="J30" s="14" t="inlineStr">
@@ -18502,9 +18502,9 @@
           <t>required</t>
         </is>
       </c>
-      <c r="I31" s="14" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="I31" s="8" t="inlineStr">
+        <is>
+          <t>covered by CNP</t>
         </is>
       </c>
       <c r="J31" s="14" t="inlineStr">
@@ -18564,9 +18564,9 @@
           <t>required</t>
         </is>
       </c>
-      <c r="I32" s="14" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="I32" s="8" t="inlineStr">
+        <is>
+          <t>covered by CNP</t>
         </is>
       </c>
       <c r="J32" s="14" t="inlineStr">
@@ -18626,9 +18626,9 @@
           <t>required</t>
         </is>
       </c>
-      <c r="I33" s="14" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="I33" s="8" t="inlineStr">
+        <is>
+          <t>covered by CNP</t>
         </is>
       </c>
       <c r="J33" s="14" t="inlineStr">
@@ -18688,9 +18688,9 @@
           <t>required</t>
         </is>
       </c>
-      <c r="I34" s="14" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="I34" s="8" t="inlineStr">
+        <is>
+          <t>covered by CNP</t>
         </is>
       </c>
       <c r="J34" s="14" t="inlineStr">
@@ -18750,9 +18750,9 @@
           <t>required</t>
         </is>
       </c>
-      <c r="I35" s="14" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="I35" s="8" t="inlineStr">
+        <is>
+          <t>covered by CNP</t>
         </is>
       </c>
       <c r="J35" s="14" t="inlineStr">
@@ -18816,9 +18816,9 @@
           <t>required</t>
         </is>
       </c>
-      <c r="I36" s="14" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="I36" s="8" t="inlineStr">
+        <is>
+          <t>covered by CNP</t>
         </is>
       </c>
       <c r="J36" s="14" t="inlineStr">
@@ -18882,9 +18882,9 @@
           <t>required</t>
         </is>
       </c>
-      <c r="I37" s="14" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="I37" s="8" t="inlineStr">
+        <is>
+          <t>covered by CNP</t>
         </is>
       </c>
       <c r="J37" s="14" t="inlineStr">
@@ -18944,9 +18944,9 @@
           <t>required</t>
         </is>
       </c>
-      <c r="I38" s="14" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="I38" s="8" t="inlineStr">
+        <is>
+          <t>covered by CNP</t>
         </is>
       </c>
       <c r="J38" s="14" t="inlineStr">
@@ -19006,9 +19006,9 @@
           <t>required</t>
         </is>
       </c>
-      <c r="I39" s="14" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="I39" s="8" t="inlineStr">
+        <is>
+          <t>covered by CNP</t>
         </is>
       </c>
       <c r="J39" s="14" t="inlineStr">
@@ -19072,9 +19072,9 @@
           <t>required</t>
         </is>
       </c>
-      <c r="I40" s="14" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="I40" s="8" t="inlineStr">
+        <is>
+          <t>covered by CNP</t>
         </is>
       </c>
       <c r="J40" s="14" t="inlineStr">
@@ -19134,9 +19134,9 @@
           <t>required</t>
         </is>
       </c>
-      <c r="I41" s="14" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="I41" s="8" t="inlineStr">
+        <is>
+          <t>covered by CNP</t>
         </is>
       </c>
       <c r="J41" s="14" t="inlineStr">
@@ -19196,9 +19196,9 @@
           <t>required</t>
         </is>
       </c>
-      <c r="I42" s="14" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="I42" s="8" t="inlineStr">
+        <is>
+          <t>covered by CNP</t>
         </is>
       </c>
       <c r="J42" s="14" t="inlineStr">
@@ -19262,9 +19262,9 @@
           <t>required</t>
         </is>
       </c>
-      <c r="I43" s="14" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="I43" s="8" t="inlineStr">
+        <is>
+          <t>covered by CNP</t>
         </is>
       </c>
       <c r="J43" s="14" t="inlineStr">
@@ -19324,9 +19324,9 @@
           <t>required</t>
         </is>
       </c>
-      <c r="I44" s="14" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="I44" s="8" t="inlineStr">
+        <is>
+          <t>covered by CNP</t>
         </is>
       </c>
       <c r="J44" s="14" t="inlineStr">
@@ -19386,9 +19386,9 @@
           <t>required</t>
         </is>
       </c>
-      <c r="I45" s="14" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="I45" s="8" t="inlineStr">
+        <is>
+          <t>covered by CNP</t>
         </is>
       </c>
       <c r="J45" s="14" t="inlineStr">
@@ -19448,9 +19448,9 @@
           <t>required</t>
         </is>
       </c>
-      <c r="I46" s="14" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="I46" s="8" t="inlineStr">
+        <is>
+          <t>covered by CNP</t>
         </is>
       </c>
       <c r="J46" s="14" t="inlineStr">
@@ -19514,9 +19514,9 @@
           <t>required</t>
         </is>
       </c>
-      <c r="I47" s="14" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="I47" s="8" t="inlineStr">
+        <is>
+          <t>covered by CNP</t>
         </is>
       </c>
       <c r="J47" s="14" t="inlineStr">
@@ -19580,9 +19580,9 @@
           <t>required</t>
         </is>
       </c>
-      <c r="I48" s="14" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="I48" s="8" t="inlineStr">
+        <is>
+          <t>covered by CNP</t>
         </is>
       </c>
       <c r="J48" s="14" t="inlineStr">
@@ -19646,9 +19646,9 @@
           <t>required</t>
         </is>
       </c>
-      <c r="I49" s="14" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="I49" s="8" t="inlineStr">
+        <is>
+          <t>covered by CNP</t>
         </is>
       </c>
       <c r="J49" s="14" t="inlineStr">
@@ -19712,9 +19712,9 @@
           <t>required</t>
         </is>
       </c>
-      <c r="I50" s="14" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="I50" s="8" t="inlineStr">
+        <is>
+          <t>covered by CNP</t>
         </is>
       </c>
       <c r="J50" s="14" t="inlineStr">
@@ -19778,9 +19778,9 @@
           <t>required</t>
         </is>
       </c>
-      <c r="I51" s="14" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="I51" s="8" t="inlineStr">
+        <is>
+          <t>covered by CNP</t>
         </is>
       </c>
       <c r="J51" s="14" t="inlineStr">
@@ -19844,9 +19844,9 @@
           <t>required</t>
         </is>
       </c>
-      <c r="I52" s="14" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="I52" s="8" t="inlineStr">
+        <is>
+          <t>covered by CNP</t>
         </is>
       </c>
       <c r="J52" s="14" t="inlineStr">
@@ -19910,9 +19910,9 @@
           <t>required</t>
         </is>
       </c>
-      <c r="I53" s="14" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="I53" s="8" t="inlineStr">
+        <is>
+          <t>covered by CNP</t>
         </is>
       </c>
       <c r="J53" s="14" t="inlineStr">
@@ -19976,9 +19976,9 @@
           <t>required</t>
         </is>
       </c>
-      <c r="I54" s="14" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="I54" s="8" t="inlineStr">
+        <is>
+          <t>covered by CNP</t>
         </is>
       </c>
       <c r="J54" s="14" t="inlineStr">
@@ -20038,9 +20038,9 @@
           <t>required</t>
         </is>
       </c>
-      <c r="I55" s="14" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="I55" s="8" t="inlineStr">
+        <is>
+          <t>covered by CNP</t>
         </is>
       </c>
       <c r="J55" s="14" t="inlineStr">
@@ -20100,9 +20100,9 @@
           <t>required</t>
         </is>
       </c>
-      <c r="I56" s="14" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="I56" s="8" t="inlineStr">
+        <is>
+          <t>covered by CNP</t>
         </is>
       </c>
       <c r="J56" s="14" t="inlineStr">
@@ -20166,9 +20166,9 @@
           <t>required</t>
         </is>
       </c>
-      <c r="I57" s="14" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="I57" s="8" t="inlineStr">
+        <is>
+          <t>covered by CNP</t>
         </is>
       </c>
       <c r="J57" s="14" t="inlineStr">
@@ -20228,9 +20228,9 @@
           <t>required</t>
         </is>
       </c>
-      <c r="I58" s="14" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="I58" s="8" t="inlineStr">
+        <is>
+          <t>covered by CNP</t>
         </is>
       </c>
       <c r="J58" s="14" t="inlineStr">
@@ -20290,9 +20290,9 @@
           <t>required</t>
         </is>
       </c>
-      <c r="I59" s="14" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="I59" s="8" t="inlineStr">
+        <is>
+          <t>covered by CNP</t>
         </is>
       </c>
       <c r="J59" s="14" t="inlineStr">
@@ -20356,9 +20356,9 @@
           <t>required</t>
         </is>
       </c>
-      <c r="I60" s="14" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="I60" s="8" t="inlineStr">
+        <is>
+          <t>covered by CNP</t>
         </is>
       </c>
       <c r="J60" s="14" t="inlineStr">
@@ -20422,9 +20422,9 @@
           <t>required</t>
         </is>
       </c>
-      <c r="I61" s="14" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="I61" s="8" t="inlineStr">
+        <is>
+          <t>covered by CNP</t>
         </is>
       </c>
       <c r="J61" s="14" t="inlineStr">
@@ -20488,9 +20488,9 @@
           <t>required</t>
         </is>
       </c>
-      <c r="I62" s="14" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="I62" s="8" t="inlineStr">
+        <is>
+          <t>covered by CNP</t>
         </is>
       </c>
       <c r="J62" s="14" t="inlineStr">
@@ -20554,9 +20554,9 @@
           <t>required</t>
         </is>
       </c>
-      <c r="I63" s="14" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="I63" s="8" t="inlineStr">
+        <is>
+          <t>covered by CNP</t>
         </is>
       </c>
       <c r="J63" s="14" t="inlineStr">
@@ -20620,9 +20620,9 @@
           <t>required</t>
         </is>
       </c>
-      <c r="I64" s="14" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="I64" s="8" t="inlineStr">
+        <is>
+          <t>covered by CNP</t>
         </is>
       </c>
       <c r="J64" s="14" t="inlineStr">
@@ -20686,9 +20686,9 @@
           <t>required</t>
         </is>
       </c>
-      <c r="I65" s="14" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="I65" s="8" t="inlineStr">
+        <is>
+          <t>covered by CNP</t>
         </is>
       </c>
       <c r="J65" s="14" t="inlineStr">
@@ -20752,9 +20752,9 @@
           <t>required</t>
         </is>
       </c>
-      <c r="I66" s="14" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="I66" s="8" t="inlineStr">
+        <is>
+          <t>covered by CNP</t>
         </is>
       </c>
       <c r="J66" s="14" t="inlineStr">
@@ -20818,9 +20818,9 @@
           <t>covered by CNP</t>
         </is>
       </c>
-      <c r="I67" s="14" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="I67" s="8" t="inlineStr">
+        <is>
+          <t>covered by CNP</t>
         </is>
       </c>
       <c r="J67" s="8" t="inlineStr">
@@ -20884,9 +20884,9 @@
           <t>covered by CNP</t>
         </is>
       </c>
-      <c r="I68" s="14" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="I68" s="8" t="inlineStr">
+        <is>
+          <t>covered by CNP</t>
         </is>
       </c>
       <c r="J68" s="8" t="inlineStr">
@@ -20950,9 +20950,9 @@
           <t>covered by CNP</t>
         </is>
       </c>
-      <c r="I69" s="14" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="I69" s="8" t="inlineStr">
+        <is>
+          <t>covered by CNP</t>
         </is>
       </c>
       <c r="J69" s="8" t="inlineStr">
@@ -21016,9 +21016,9 @@
           <t>covered by CNP</t>
         </is>
       </c>
-      <c r="I70" s="14" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="I70" s="8" t="inlineStr">
+        <is>
+          <t>covered by CNP</t>
         </is>
       </c>
       <c r="J70" s="8" t="inlineStr">
@@ -21082,9 +21082,9 @@
           <t>covered by CNP</t>
         </is>
       </c>
-      <c r="I71" s="14" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="I71" s="8" t="inlineStr">
+        <is>
+          <t>covered by CNP</t>
         </is>
       </c>
       <c r="J71" s="8" t="inlineStr">
@@ -21148,9 +21148,9 @@
           <t>covered by CNP</t>
         </is>
       </c>
-      <c r="I72" s="14" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="I72" s="8" t="inlineStr">
+        <is>
+          <t>covered by CNP</t>
         </is>
       </c>
       <c r="J72" s="8" t="inlineStr">
@@ -21214,9 +21214,9 @@
           <t>covered by CNP</t>
         </is>
       </c>
-      <c r="I73" s="14" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="I73" s="8" t="inlineStr">
+        <is>
+          <t>covered by CNP</t>
         </is>
       </c>
       <c r="J73" s="8" t="inlineStr">
@@ -21280,9 +21280,9 @@
           <t>covered by CNP</t>
         </is>
       </c>
-      <c r="I74" s="14" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="I74" s="8" t="inlineStr">
+        <is>
+          <t>covered by CNP</t>
         </is>
       </c>
       <c r="J74" s="8" t="inlineStr">
@@ -21346,9 +21346,9 @@
           <t>covered by CNP</t>
         </is>
       </c>
-      <c r="I75" s="14" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="I75" s="8" t="inlineStr">
+        <is>
+          <t>covered by CNP</t>
         </is>
       </c>
       <c r="J75" s="8" t="inlineStr">
@@ -21412,9 +21412,9 @@
           <t>covered by CNP</t>
         </is>
       </c>
-      <c r="I76" s="14" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="I76" s="8" t="inlineStr">
+        <is>
+          <t>covered by CNP</t>
         </is>
       </c>
       <c r="J76" s="8" t="inlineStr">
@@ -21478,9 +21478,9 @@
           <t>covered by CNP</t>
         </is>
       </c>
-      <c r="I77" s="14" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="I77" s="8" t="inlineStr">
+        <is>
+          <t>covered by CNP</t>
         </is>
       </c>
       <c r="J77" s="16" t="inlineStr">
@@ -21544,9 +21544,9 @@
           <t>covered by CNP</t>
         </is>
       </c>
-      <c r="I78" s="14" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="I78" s="8" t="inlineStr">
+        <is>
+          <t>covered by CNP</t>
         </is>
       </c>
       <c r="J78" s="8" t="inlineStr">
@@ -21610,9 +21610,9 @@
           <t>required</t>
         </is>
       </c>
-      <c r="I79" s="14" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="I79" s="8" t="inlineStr">
+        <is>
+          <t>covered by CNP</t>
         </is>
       </c>
       <c r="J79" s="14" t="inlineStr">
@@ -21684,9 +21684,9 @@
           <t>required</t>
         </is>
       </c>
-      <c r="I80" s="14" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="I80" s="8" t="inlineStr">
+        <is>
+          <t>covered by CNP</t>
         </is>
       </c>
       <c r="J80" s="14" t="inlineStr">
@@ -21758,9 +21758,9 @@
           <t>required</t>
         </is>
       </c>
-      <c r="I81" s="14" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="I81" s="8" t="inlineStr">
+        <is>
+          <t>covered by CNP</t>
         </is>
       </c>
       <c r="J81" s="14" t="inlineStr">
@@ -21832,9 +21832,9 @@
           <t>required</t>
         </is>
       </c>
-      <c r="I82" s="14" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="I82" s="8" t="inlineStr">
+        <is>
+          <t>covered by CNP</t>
         </is>
       </c>
       <c r="J82" s="14" t="inlineStr">
@@ -21902,9 +21902,9 @@
           <t>required</t>
         </is>
       </c>
-      <c r="I83" s="14" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="I83" s="8" t="inlineStr">
+        <is>
+          <t>covered by CNP</t>
         </is>
       </c>
       <c r="J83" s="14" t="inlineStr">
@@ -21976,9 +21976,9 @@
           <t>required</t>
         </is>
       </c>
-      <c r="I84" s="14" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="I84" s="8" t="inlineStr">
+        <is>
+          <t>covered by CNP</t>
         </is>
       </c>
       <c r="J84" s="14" t="inlineStr">
@@ -22050,9 +22050,9 @@
           <t>required</t>
         </is>
       </c>
-      <c r="I85" s="14" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="I85" s="8" t="inlineStr">
+        <is>
+          <t>covered by CNP</t>
         </is>
       </c>
       <c r="J85" s="14" t="inlineStr">
@@ -22124,9 +22124,9 @@
           <t>required</t>
         </is>
       </c>
-      <c r="I86" s="14" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="I86" s="8" t="inlineStr">
+        <is>
+          <t>covered by CNP</t>
         </is>
       </c>
       <c r="J86" s="14" t="inlineStr">
@@ -22404,10 +22404,10 @@
         </is>
       </c>
       <c r="L6" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N6" s="5" t="n">
         <v>3</v>
@@ -22425,7 +22425,7 @@
       </c>
       <c r="R6" s="7" t="inlineStr">
         <is>
-          <t>Purely Plant laboratory — iCoA covering Ident A + B; outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest); Purely Plant laboratory — iCoA covering Foreign matter</t>
+          <t>Purely Plant laboratory — iCoA covering Ident A + B; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
       <c r="S6" s="17" t="inlineStr">
@@ -22491,10 +22491,10 @@
         </is>
       </c>
       <c r="L7" s="9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M7" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N7" s="9" t="n">
         <v>3</v>
@@ -22512,7 +22512,7 @@
       </c>
       <c r="R7" s="12" t="inlineStr">
         <is>
-          <t>Purely Plant laboratory — iCoA covering Ident A + B; outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest); Purely Plant laboratory — iCoA covering Foreign matter</t>
+          <t>Purely Plant laboratory — iCoA covering Ident A + B; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
       <c r="S7" s="12" t="inlineStr"/>
@@ -22595,7 +22595,7 @@
       </c>
       <c r="R8" s="7" t="inlineStr">
         <is>
-          <t>Purely Plant laboratory — iCoA covering Ident A + B; outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest); Purely Plant laboratory — iCoA covering Foreign matter</t>
+          <t>Purely Plant laboratory — iCoA covering Ident A + B; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
       <c r="S8" s="18" t="inlineStr">
@@ -22661,10 +22661,10 @@
         </is>
       </c>
       <c r="L9" s="9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M9" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N9" s="9" t="n">
         <v>4</v>
@@ -22682,7 +22682,7 @@
       </c>
       <c r="R9" s="12" t="inlineStr">
         <is>
-          <t>Purely Plant laboratory — iCoA covering Ident A + B; outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest); Purely Plant laboratory — iCoA covering Foreign matter</t>
+          <t>Purely Plant laboratory — iCoA covering Ident A + B; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
       <c r="S9" s="17" t="inlineStr">
@@ -22748,10 +22748,10 @@
         </is>
       </c>
       <c r="L10" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N10" s="5" t="n">
         <v>4</v>
@@ -22769,7 +22769,7 @@
       </c>
       <c r="R10" s="7" t="inlineStr">
         <is>
-          <t>Purely Plant laboratory — iCoA covering Ident A + B; outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest); Purely Plant laboratory — iCoA covering Foreign matter</t>
+          <t>Purely Plant laboratory — iCoA covering Ident A + B; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
       <c r="S10" s="7" t="inlineStr"/>
@@ -22831,10 +22831,10 @@
         </is>
       </c>
       <c r="L11" s="9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M11" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N11" s="9" t="n">
         <v>2</v>
@@ -22852,7 +22852,7 @@
       </c>
       <c r="R11" s="12" t="inlineStr">
         <is>
-          <t>Purely Plant laboratory — iCoA covering Ident A + B; outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest); Purely Plant laboratory — iCoA covering Foreign matter</t>
+          <t>Purely Plant laboratory — iCoA covering Ident A + B; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
       <c r="S11" s="17" t="inlineStr">
@@ -22918,10 +22918,10 @@
         </is>
       </c>
       <c r="L12" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N12" s="5" t="n">
         <v>3</v>
@@ -22939,7 +22939,7 @@
       </c>
       <c r="R12" s="7" t="inlineStr">
         <is>
-          <t>Purely Plant laboratory — iCoA covering Ident A + B; outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest); Purely Plant laboratory — iCoA covering Foreign matter</t>
+          <t>Purely Plant laboratory — iCoA covering Ident A + B; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
       <c r="S12" s="7" t="inlineStr"/>
@@ -23001,10 +23001,10 @@
         </is>
       </c>
       <c r="L13" s="9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M13" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N13" s="9" t="n">
         <v>3</v>
@@ -23022,7 +23022,7 @@
       </c>
       <c r="R13" s="12" t="inlineStr">
         <is>
-          <t>Purely Plant laboratory — iCoA covering Ident A + B; outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest); Purely Plant laboratory — iCoA covering Foreign matter</t>
+          <t>Purely Plant laboratory — iCoA covering Ident A + B; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
       <c r="S13" s="17" t="inlineStr">
@@ -23088,10 +23088,10 @@
         </is>
       </c>
       <c r="L14" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N14" s="5" t="n">
         <v>3</v>
@@ -23109,7 +23109,7 @@
       </c>
       <c r="R14" s="7" t="inlineStr">
         <is>
-          <t>Purely Plant laboratory — iCoA covering Ident A + B; outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest); Purely Plant laboratory — iCoA covering Foreign matter</t>
+          <t>Purely Plant laboratory — iCoA covering Ident A + B; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
       <c r="S14" s="7" t="inlineStr"/>
@@ -23171,10 +23171,10 @@
         </is>
       </c>
       <c r="L15" s="9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M15" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N15" s="9" t="n">
         <v>3</v>
@@ -23192,7 +23192,7 @@
       </c>
       <c r="R15" s="12" t="inlineStr">
         <is>
-          <t>Purely Plant laboratory — iCoA covering Ident A + B; outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest); Purely Plant laboratory — iCoA covering Foreign matter</t>
+          <t>Purely Plant laboratory — iCoA covering Ident A + B; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
       <c r="S15" s="17" t="inlineStr">
@@ -23258,10 +23258,10 @@
         </is>
       </c>
       <c r="L16" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N16" s="5" t="n">
         <v>3</v>
@@ -23279,7 +23279,7 @@
       </c>
       <c r="R16" s="7" t="inlineStr">
         <is>
-          <t>Purely Plant laboratory — iCoA covering Ident A + B; outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest); Purely Plant laboratory — iCoA covering Foreign matter</t>
+          <t>Purely Plant laboratory — iCoA covering Ident A + B; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
       <c r="S16" s="17" t="inlineStr">
@@ -23345,10 +23345,10 @@
         </is>
       </c>
       <c r="L17" s="9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M17" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N17" s="9" t="n">
         <v>3</v>
@@ -23366,7 +23366,7 @@
       </c>
       <c r="R17" s="12" t="inlineStr">
         <is>
-          <t>Purely Plant laboratory — iCoA covering Ident A + B; outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest); Purely Plant laboratory — iCoA covering Foreign matter</t>
+          <t>Purely Plant laboratory — iCoA covering Ident A + B; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
       <c r="S17" s="17" t="inlineStr">
@@ -23432,10 +23432,10 @@
         </is>
       </c>
       <c r="L18" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N18" s="5" t="n">
         <v>3</v>
@@ -23453,7 +23453,7 @@
       </c>
       <c r="R18" s="7" t="inlineStr">
         <is>
-          <t>Purely Plant laboratory — iCoA covering Ident A + B; outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest); Purely Plant laboratory — iCoA covering Foreign matter</t>
+          <t>Purely Plant laboratory — iCoA covering Ident A + B; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
       <c r="S18" s="7" t="inlineStr"/>
@@ -23515,10 +23515,10 @@
         </is>
       </c>
       <c r="L19" s="9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M19" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N19" s="9" t="n">
         <v>3</v>
@@ -23536,7 +23536,7 @@
       </c>
       <c r="R19" s="12" t="inlineStr">
         <is>
-          <t>Purely Plant laboratory — iCoA covering Ident A + B; outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest); Purely Plant laboratory — iCoA covering Foreign matter</t>
+          <t>Purely Plant laboratory — iCoA covering Ident A + B; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
       <c r="S19" s="12" t="inlineStr"/>
@@ -23598,10 +23598,10 @@
         </is>
       </c>
       <c r="L20" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N20" s="5" t="n">
         <v>3</v>
@@ -23619,7 +23619,7 @@
       </c>
       <c r="R20" s="7" t="inlineStr">
         <is>
-          <t>Purely Plant laboratory — iCoA covering Ident A + B; outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest); Purely Plant laboratory — iCoA covering Foreign matter</t>
+          <t>Purely Plant laboratory — iCoA covering Ident A + B; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
       <c r="S20" s="17" t="inlineStr">
@@ -23685,10 +23685,10 @@
         </is>
       </c>
       <c r="L21" s="9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M21" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N21" s="9" t="n">
         <v>3</v>
@@ -23706,7 +23706,7 @@
       </c>
       <c r="R21" s="12" t="inlineStr">
         <is>
-          <t>Purely Plant laboratory — iCoA covering Ident A + B; outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest); Purely Plant laboratory — iCoA covering Foreign matter</t>
+          <t>Purely Plant laboratory — iCoA covering Ident A + B; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
       <c r="S21" s="17" t="inlineStr">
@@ -23772,10 +23772,10 @@
         </is>
       </c>
       <c r="L22" s="5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N22" s="5" t="n">
         <v>2</v>
@@ -23793,7 +23793,7 @@
       </c>
       <c r="R22" s="7" t="inlineStr">
         <is>
-          <t>Purely Plant laboratory — iCoA covering Ident A + B; outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest); Purely Plant laboratory — iCoA covering Foreign matter</t>
+          <t>Purely Plant laboratory — iCoA covering Ident A + B; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
       <c r="S22" s="7" t="inlineStr"/>
@@ -23855,10 +23855,10 @@
         </is>
       </c>
       <c r="L23" s="9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M23" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N23" s="9" t="n">
         <v>3</v>
@@ -23876,7 +23876,7 @@
       </c>
       <c r="R23" s="12" t="inlineStr">
         <is>
-          <t>Purely Plant laboratory — iCoA covering Ident A + B; outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest); Purely Plant laboratory — iCoA covering Foreign matter</t>
+          <t>Purely Plant laboratory — iCoA covering Ident A + B; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
       <c r="S23" s="17" t="inlineStr">
@@ -23942,10 +23942,10 @@
         </is>
       </c>
       <c r="L24" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N24" s="5" t="n">
         <v>3</v>
@@ -23963,7 +23963,7 @@
       </c>
       <c r="R24" s="7" t="inlineStr">
         <is>
-          <t>Purely Plant laboratory — iCoA covering Ident A + B; outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest); Purely Plant laboratory — iCoA covering Foreign matter</t>
+          <t>Purely Plant laboratory — iCoA covering Ident A + B; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
       <c r="S24" s="7" t="inlineStr"/>
@@ -24025,10 +24025,10 @@
         </is>
       </c>
       <c r="L25" s="9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M25" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N25" s="9" t="n">
         <v>3</v>
@@ -24046,7 +24046,7 @@
       </c>
       <c r="R25" s="12" t="inlineStr">
         <is>
-          <t>Purely Plant laboratory — iCoA covering Ident A + B; outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest); Purely Plant laboratory — iCoA covering Foreign matter</t>
+          <t>Purely Plant laboratory — iCoA covering Ident A + B; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
       <c r="S25" s="17" t="inlineStr">
@@ -24112,10 +24112,10 @@
         </is>
       </c>
       <c r="L26" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N26" s="5" t="n">
         <v>3</v>
@@ -24133,7 +24133,7 @@
       </c>
       <c r="R26" s="7" t="inlineStr">
         <is>
-          <t>Purely Plant laboratory — iCoA covering Ident A + B; outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest); Purely Plant laboratory — iCoA covering Foreign matter</t>
+          <t>Purely Plant laboratory — iCoA covering Ident A + B; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
       <c r="S26" s="17" t="inlineStr">
@@ -24199,10 +24199,10 @@
         </is>
       </c>
       <c r="L27" s="9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M27" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N27" s="9" t="n">
         <v>3</v>
@@ -24220,7 +24220,7 @@
       </c>
       <c r="R27" s="12" t="inlineStr">
         <is>
-          <t>Purely Plant laboratory — iCoA covering Ident A + B; outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest); Purely Plant laboratory — iCoA covering Foreign matter</t>
+          <t>Purely Plant laboratory — iCoA covering Ident A + B; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
       <c r="S27" s="12" t="inlineStr"/>
@@ -24282,10 +24282,10 @@
         </is>
       </c>
       <c r="L28" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M28" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N28" s="5" t="n">
         <v>3</v>
@@ -24303,7 +24303,7 @@
       </c>
       <c r="R28" s="7" t="inlineStr">
         <is>
-          <t>Purely Plant laboratory — iCoA covering Ident A + B; outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest); Purely Plant laboratory — iCoA covering Foreign matter</t>
+          <t>Purely Plant laboratory — iCoA covering Ident A + B; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
       <c r="S28" s="17" t="inlineStr">
@@ -24369,10 +24369,10 @@
         </is>
       </c>
       <c r="L29" s="9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M29" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N29" s="9" t="n">
         <v>3</v>
@@ -24390,7 +24390,7 @@
       </c>
       <c r="R29" s="12" t="inlineStr">
         <is>
-          <t>Purely Plant laboratory — iCoA covering Ident A + B; outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest); Purely Plant laboratory — iCoA covering Foreign matter</t>
+          <t>Purely Plant laboratory — iCoA covering Ident A + B; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
       <c r="S29" s="17" t="inlineStr">
@@ -24456,10 +24456,10 @@
         </is>
       </c>
       <c r="L30" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M30" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N30" s="5" t="n">
         <v>3</v>
@@ -24477,7 +24477,7 @@
       </c>
       <c r="R30" s="7" t="inlineStr">
         <is>
-          <t>Purely Plant laboratory — iCoA covering Ident A + B; outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest); Purely Plant laboratory — iCoA covering Foreign matter</t>
+          <t>Purely Plant laboratory — iCoA covering Ident A + B; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
       <c r="S30" s="7" t="inlineStr"/>
@@ -24539,10 +24539,10 @@
         </is>
       </c>
       <c r="L31" s="9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M31" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N31" s="9" t="n">
         <v>3</v>
@@ -24560,7 +24560,7 @@
       </c>
       <c r="R31" s="12" t="inlineStr">
         <is>
-          <t>Purely Plant laboratory — iCoA covering Ident A + B; outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest); Purely Plant laboratory — iCoA covering Foreign matter</t>
+          <t>Purely Plant laboratory — iCoA covering Ident A + B; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
       <c r="S31" s="12" t="inlineStr"/>
@@ -24622,10 +24622,10 @@
         </is>
       </c>
       <c r="L32" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M32" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N32" s="5" t="n">
         <v>3</v>
@@ -24643,7 +24643,7 @@
       </c>
       <c r="R32" s="7" t="inlineStr">
         <is>
-          <t>Purely Plant laboratory — iCoA covering Ident A + B; outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest); Purely Plant laboratory — iCoA covering Foreign matter</t>
+          <t>Purely Plant laboratory — iCoA covering Ident A + B; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
       <c r="S32" s="17" t="inlineStr">
@@ -24709,10 +24709,10 @@
         </is>
       </c>
       <c r="L33" s="9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M33" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N33" s="9" t="n">
         <v>3</v>
@@ -24730,7 +24730,7 @@
       </c>
       <c r="R33" s="12" t="inlineStr">
         <is>
-          <t>Purely Plant laboratory — iCoA covering Ident A + B; outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest); Purely Plant laboratory — iCoA covering Foreign matter</t>
+          <t>Purely Plant laboratory — iCoA covering Ident A + B; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
       <c r="S33" s="17" t="inlineStr">
@@ -24796,10 +24796,10 @@
         </is>
       </c>
       <c r="L34" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M34" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N34" s="5" t="n">
         <v>3</v>
@@ -24817,7 +24817,7 @@
       </c>
       <c r="R34" s="7" t="inlineStr">
         <is>
-          <t>Purely Plant laboratory — iCoA covering Ident A + B; outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest); Purely Plant laboratory — iCoA covering Foreign matter</t>
+          <t>Purely Plant laboratory — iCoA covering Ident A + B; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
       <c r="S34" s="7" t="inlineStr"/>
@@ -24879,10 +24879,10 @@
         </is>
       </c>
       <c r="L35" s="9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M35" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N35" s="9" t="n">
         <v>3</v>
@@ -24900,7 +24900,7 @@
       </c>
       <c r="R35" s="12" t="inlineStr">
         <is>
-          <t>Purely Plant laboratory — iCoA covering Ident A + B; outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest); Purely Plant laboratory — iCoA covering Foreign matter</t>
+          <t>Purely Plant laboratory — iCoA covering Ident A + B; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
       <c r="S35" s="17" t="inlineStr">
@@ -24983,7 +24983,7 @@
       <c r="Q36" s="7" t="inlineStr"/>
       <c r="R36" s="7" t="inlineStr">
         <is>
-          <t>Purely Plant laboratory — iCoA covering Ident A + B; outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest); Purely Plant laboratory — iCoA covering Foreign matter</t>
+          <t>Purely Plant laboratory — iCoA covering Ident A + B; outside laboratory — the HPLC cannabinoid certificate discharges Ident C (Farmahem -K- or CNP); in-house iCoA P03 only where none exists; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
       <c r="S36" s="18" t="inlineStr">
@@ -25066,7 +25066,7 @@
       <c r="Q37" s="12" t="inlineStr"/>
       <c r="R37" s="12" t="inlineStr">
         <is>
-          <t>Purely Plant laboratory — iCoA covering Ident A + B; outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest); Purely Plant laboratory — iCoA covering Foreign matter</t>
+          <t>Purely Plant laboratory — iCoA covering Ident A + B; outside laboratory — the HPLC cannabinoid certificate discharges Ident C (Farmahem -K- or CNP); in-house iCoA P03 only where none exists; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
       <c r="S37" s="18" t="inlineStr">
@@ -25149,7 +25149,7 @@
       <c r="Q38" s="7" t="inlineStr"/>
       <c r="R38" s="7" t="inlineStr">
         <is>
-          <t>Purely Plant laboratory — iCoA covering Ident A + B; outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest); Purely Plant laboratory — iCoA covering Foreign matter</t>
+          <t>Purely Plant laboratory — iCoA covering Ident A + B; outside laboratory — the HPLC cannabinoid certificate discharges Ident C (Farmahem -K- or CNP); in-house iCoA P03 only where none exists; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
       <c r="S38" s="18" t="inlineStr">
@@ -25215,10 +25215,10 @@
         </is>
       </c>
       <c r="L39" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M39" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N39" s="9" t="n">
         <v>13</v>
@@ -25236,7 +25236,7 @@
       </c>
       <c r="R39" s="12" t="inlineStr">
         <is>
-          <t>Purely Plant laboratory — iCoA covering Ident A + B; outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest); Purely Plant laboratory — iCoA covering Foreign matter</t>
+          <t>Purely Plant laboratory — iCoA covering Ident A + B; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
       <c r="S39" s="12" t="inlineStr"/>
@@ -25298,10 +25298,10 @@
         </is>
       </c>
       <c r="L40" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M40" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N40" s="5" t="n">
         <v>13</v>
@@ -25319,7 +25319,7 @@
       </c>
       <c r="R40" s="7" t="inlineStr">
         <is>
-          <t>Purely Plant laboratory — iCoA covering Ident A + B; outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest); Purely Plant laboratory — iCoA covering Foreign matter</t>
+          <t>Purely Plant laboratory — iCoA covering Ident A + B; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
       <c r="S40" s="17" t="inlineStr">
@@ -25385,10 +25385,10 @@
         </is>
       </c>
       <c r="L41" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M41" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N41" s="9" t="n">
         <v>13</v>
@@ -25406,7 +25406,7 @@
       </c>
       <c r="R41" s="12" t="inlineStr">
         <is>
-          <t>Purely Plant laboratory — iCoA covering Ident A + B; outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest); Purely Plant laboratory — iCoA covering Foreign matter</t>
+          <t>Purely Plant laboratory — iCoA covering Ident A + B; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
       <c r="S41" s="17" t="inlineStr">
@@ -25472,10 +25472,10 @@
         </is>
       </c>
       <c r="L42" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="M42" s="5" t="n">
         <v>3</v>
-      </c>
-      <c r="M42" s="5" t="n">
-        <v>4</v>
       </c>
       <c r="N42" s="5" t="n">
         <v>14</v>
@@ -25493,7 +25493,7 @@
       </c>
       <c r="R42" s="7" t="inlineStr">
         <is>
-          <t>Purely Plant laboratory — iCoA covering Ident A + B; outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest); Purely Plant laboratory — iCoA covering Foreign matter</t>
+          <t>Purely Plant laboratory — iCoA covering Ident A + B; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
       <c r="S42" s="7" t="inlineStr"/>
@@ -25555,10 +25555,10 @@
         </is>
       </c>
       <c r="L43" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="M43" s="9" t="n">
         <v>3</v>
-      </c>
-      <c r="M43" s="9" t="n">
-        <v>4</v>
       </c>
       <c r="N43" s="9" t="n">
         <v>14</v>
@@ -25576,7 +25576,7 @@
       </c>
       <c r="R43" s="12" t="inlineStr">
         <is>
-          <t>Purely Plant laboratory — iCoA covering Ident A + B; outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest); Purely Plant laboratory — iCoA covering Foreign matter</t>
+          <t>Purely Plant laboratory — iCoA covering Ident A + B; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
       <c r="S43" s="12" t="inlineStr"/>
@@ -25638,10 +25638,10 @@
         </is>
       </c>
       <c r="L44" s="5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M44" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N44" s="5" t="n">
         <v>2</v>
@@ -25659,7 +25659,7 @@
       </c>
       <c r="R44" s="7" t="inlineStr">
         <is>
-          <t>Purely Plant laboratory — iCoA covering Ident A + B; outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest); Purely Plant laboratory — iCoA covering Foreign matter</t>
+          <t>Purely Plant laboratory — iCoA covering Ident A + B; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
       <c r="S44" s="7" t="inlineStr"/>
@@ -25721,10 +25721,10 @@
         </is>
       </c>
       <c r="L45" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="M45" s="9" t="n">
         <v>3</v>
-      </c>
-      <c r="M45" s="9" t="n">
-        <v>4</v>
       </c>
       <c r="N45" s="9" t="n">
         <v>14</v>
@@ -25742,7 +25742,7 @@
       </c>
       <c r="R45" s="12" t="inlineStr">
         <is>
-          <t>Purely Plant laboratory — iCoA covering Ident A + B; outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest); Purely Plant laboratory — iCoA covering Foreign matter</t>
+          <t>Purely Plant laboratory — iCoA covering Ident A + B; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
       <c r="S45" s="17" t="inlineStr">
@@ -25808,10 +25808,10 @@
         </is>
       </c>
       <c r="L46" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="M46" s="5" t="n">
         <v>3</v>
-      </c>
-      <c r="M46" s="5" t="n">
-        <v>4</v>
       </c>
       <c r="N46" s="5" t="n">
         <v>14</v>
@@ -25829,7 +25829,7 @@
       </c>
       <c r="R46" s="7" t="inlineStr">
         <is>
-          <t>Purely Plant laboratory — iCoA covering Ident A + B; outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest); Purely Plant laboratory — iCoA covering Foreign matter</t>
+          <t>Purely Plant laboratory — iCoA covering Ident A + B; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
       <c r="S46" s="17" t="inlineStr">
@@ -25912,7 +25912,7 @@
       <c r="Q47" s="12" t="inlineStr"/>
       <c r="R47" s="12" t="inlineStr">
         <is>
-          <t>Purely Plant laboratory — iCoA covering Ident A + B; outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest); Purely Plant laboratory — iCoA covering Foreign matter</t>
+          <t>Purely Plant laboratory — iCoA covering Ident A + B; outside laboratory — the HPLC cannabinoid certificate discharges Ident C (Farmahem -K- or CNP); in-house iCoA P03 only where none exists; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
       <c r="S47" s="18" t="inlineStr">
@@ -25995,7 +25995,7 @@
       <c r="Q48" s="7" t="inlineStr"/>
       <c r="R48" s="7" t="inlineStr">
         <is>
-          <t>Purely Plant laboratory — iCoA covering Ident A + B; outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest); Purely Plant laboratory — iCoA covering Foreign matter</t>
+          <t>Purely Plant laboratory — iCoA covering Ident A + B; outside laboratory — the HPLC cannabinoid certificate discharges Ident C (Farmahem -K- or CNP); in-house iCoA P03 only where none exists; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
       <c r="S48" s="17" t="inlineStr">
@@ -26061,10 +26061,10 @@
         </is>
       </c>
       <c r="L49" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M49" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N49" s="9" t="n">
         <v>13</v>
@@ -26082,7 +26082,7 @@
       </c>
       <c r="R49" s="12" t="inlineStr">
         <is>
-          <t>outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="S49" s="17" t="inlineStr">
@@ -26148,10 +26148,10 @@
         </is>
       </c>
       <c r="L50" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M50" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N50" s="5" t="n">
         <v>13</v>
@@ -26169,7 +26169,7 @@
       </c>
       <c r="R50" s="7" t="inlineStr">
         <is>
-          <t>outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="S50" s="17" t="inlineStr">
@@ -26252,7 +26252,7 @@
       <c r="Q51" s="12" t="inlineStr"/>
       <c r="R51" s="12" t="inlineStr">
         <is>
-          <t>Purely Plant laboratory — iCoA covering Ident A + B; outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest); Purely Plant laboratory — iCoA covering Foreign matter</t>
+          <t>Purely Plant laboratory — iCoA covering Ident A + B; outside laboratory — the HPLC cannabinoid certificate discharges Ident C (Farmahem -K- or CNP); in-house iCoA P03 only where none exists; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
       <c r="S51" s="18" t="inlineStr">
@@ -26318,10 +26318,10 @@
         </is>
       </c>
       <c r="L52" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M52" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N52" s="5" t="n">
         <v>13</v>
@@ -26339,7 +26339,7 @@
       </c>
       <c r="R52" s="7" t="inlineStr">
         <is>
-          <t>outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="S52" s="17" t="inlineStr">
@@ -26422,7 +26422,7 @@
       <c r="Q53" s="12" t="inlineStr"/>
       <c r="R53" s="12" t="inlineStr">
         <is>
-          <t>Purely Plant laboratory — iCoA covering Ident A + B; outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest); Purely Plant laboratory — iCoA covering Foreign matter</t>
+          <t>Purely Plant laboratory — iCoA covering Ident A + B; outside laboratory — the HPLC cannabinoid certificate discharges Ident C (Farmahem -K- or CNP); in-house iCoA P03 only where none exists; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
       <c r="S53" s="12" t="inlineStr"/>
@@ -26472,10 +26472,10 @@
         </is>
       </c>
       <c r="L54" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M54" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N54" s="5" t="n">
         <v>3</v>
@@ -26493,7 +26493,7 @@
       </c>
       <c r="R54" s="7" t="inlineStr">
         <is>
-          <t>Purely Plant laboratory — iCoA covering Ident A + B; outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest); Purely Plant laboratory — iCoA covering Foreign matter</t>
+          <t>Purely Plant laboratory — iCoA covering Ident A + B; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
       <c r="S54" s="7" t="inlineStr"/>
@@ -26543,10 +26543,10 @@
         </is>
       </c>
       <c r="L55" s="9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M55" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N55" s="9" t="n">
         <v>3</v>
@@ -26564,7 +26564,7 @@
       </c>
       <c r="R55" s="12" t="inlineStr">
         <is>
-          <t>Purely Plant laboratory — iCoA covering Ident A + B; outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest); Purely Plant laboratory — iCoA covering Foreign matter</t>
+          <t>Purely Plant laboratory — iCoA covering Ident A + B; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
       <c r="S55" s="12" t="inlineStr"/>
@@ -26614,10 +26614,10 @@
         </is>
       </c>
       <c r="L56" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M56" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N56" s="5" t="n">
         <v>3</v>
@@ -26635,7 +26635,7 @@
       </c>
       <c r="R56" s="7" t="inlineStr">
         <is>
-          <t>Purely Plant laboratory — iCoA covering Ident A + B; outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest); Purely Plant laboratory — iCoA covering Foreign matter</t>
+          <t>Purely Plant laboratory — iCoA covering Ident A + B; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
       <c r="S56" s="7" t="inlineStr"/>
@@ -26685,10 +26685,10 @@
         </is>
       </c>
       <c r="L57" s="9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M57" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N57" s="9" t="n">
         <v>3</v>
@@ -26706,7 +26706,7 @@
       </c>
       <c r="R57" s="12" t="inlineStr">
         <is>
-          <t>Purely Plant laboratory — iCoA covering Ident A + B; outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest); Purely Plant laboratory — iCoA covering Foreign matter</t>
+          <t>Purely Plant laboratory — iCoA covering Ident A + B; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
       <c r="S57" s="12" t="inlineStr"/>
@@ -26756,10 +26756,10 @@
         </is>
       </c>
       <c r="L58" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M58" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N58" s="5" t="n">
         <v>3</v>
@@ -26777,7 +26777,7 @@
       </c>
       <c r="R58" s="7" t="inlineStr">
         <is>
-          <t>Purely Plant laboratory — iCoA covering Ident A + B; outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest); Purely Plant laboratory — iCoA covering Foreign matter</t>
+          <t>Purely Plant laboratory — iCoA covering Ident A + B; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
       <c r="S58" s="7" t="inlineStr"/>
@@ -26827,10 +26827,10 @@
         </is>
       </c>
       <c r="L59" s="9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M59" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N59" s="9" t="n">
         <v>3</v>
@@ -26848,7 +26848,7 @@
       </c>
       <c r="R59" s="12" t="inlineStr">
         <is>
-          <t>Purely Plant laboratory — iCoA covering Ident A + B; outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest); Purely Plant laboratory — iCoA covering Foreign matter</t>
+          <t>Purely Plant laboratory — iCoA covering Ident A + B; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
       <c r="S59" s="12" t="inlineStr"/>
@@ -26898,10 +26898,10 @@
         </is>
       </c>
       <c r="L60" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M60" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N60" s="5" t="n">
         <v>3</v>
@@ -26919,7 +26919,7 @@
       </c>
       <c r="R60" s="7" t="inlineStr">
         <is>
-          <t>Purely Plant laboratory — iCoA covering Ident A + B; outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest); Purely Plant laboratory — iCoA covering Foreign matter</t>
+          <t>Purely Plant laboratory — iCoA covering Ident A + B; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
       <c r="S60" s="7" t="inlineStr"/>
@@ -26969,10 +26969,10 @@
         </is>
       </c>
       <c r="L61" s="9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M61" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N61" s="9" t="n">
         <v>3</v>
@@ -26990,7 +26990,7 @@
       </c>
       <c r="R61" s="12" t="inlineStr">
         <is>
-          <t>Purely Plant laboratory — iCoA covering Ident A + B; outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest); Purely Plant laboratory — iCoA covering Foreign matter</t>
+          <t>Purely Plant laboratory — iCoA covering Ident A + B; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
       <c r="S61" s="12" t="inlineStr"/>
@@ -27040,10 +27040,10 @@
         </is>
       </c>
       <c r="L62" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M62" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N62" s="5" t="n">
         <v>3</v>
@@ -27061,7 +27061,7 @@
       </c>
       <c r="R62" s="7" t="inlineStr">
         <is>
-          <t>Purely Plant laboratory — iCoA covering Ident A + B; outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest); Purely Plant laboratory — iCoA covering Foreign matter</t>
+          <t>Purely Plant laboratory — iCoA covering Ident A + B; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
       <c r="S62" s="7" t="inlineStr"/>
@@ -27111,10 +27111,10 @@
         </is>
       </c>
       <c r="L63" s="9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M63" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N63" s="9" t="n">
         <v>3</v>
@@ -27132,7 +27132,7 @@
       </c>
       <c r="R63" s="12" t="inlineStr">
         <is>
-          <t>Purely Plant laboratory — iCoA covering Ident A + B; outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest); Purely Plant laboratory — iCoA covering Foreign matter</t>
+          <t>Purely Plant laboratory — iCoA covering Ident A + B; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
       <c r="S63" s="12" t="inlineStr"/>
@@ -27182,10 +27182,10 @@
         </is>
       </c>
       <c r="L64" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M64" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N64" s="5" t="n">
         <v>3</v>
@@ -27203,7 +27203,7 @@
       </c>
       <c r="R64" s="7" t="inlineStr">
         <is>
-          <t>Purely Plant laboratory — iCoA covering Ident A + B; outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest); Purely Plant laboratory — iCoA covering Foreign matter</t>
+          <t>Purely Plant laboratory — iCoA covering Ident A + B; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
       <c r="S64" s="7" t="inlineStr"/>
@@ -27253,10 +27253,10 @@
         </is>
       </c>
       <c r="L65" s="9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M65" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N65" s="9" t="n">
         <v>3</v>
@@ -27274,7 +27274,7 @@
       </c>
       <c r="R65" s="12" t="inlineStr">
         <is>
-          <t>Purely Plant laboratory — iCoA covering Ident A + B; outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest); Purely Plant laboratory — iCoA covering Foreign matter</t>
+          <t>Purely Plant laboratory — iCoA covering Ident A + B; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
       <c r="S65" s="12" t="inlineStr"/>
@@ -27324,10 +27324,10 @@
         </is>
       </c>
       <c r="L66" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M66" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N66" s="5" t="n">
         <v>3</v>
@@ -27345,7 +27345,7 @@
       </c>
       <c r="R66" s="7" t="inlineStr">
         <is>
-          <t>Purely Plant laboratory — iCoA covering Ident A + B; outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest); Purely Plant laboratory — iCoA covering Foreign matter</t>
+          <t>Purely Plant laboratory — iCoA covering Ident A + B; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
       <c r="S66" s="7" t="inlineStr"/>
@@ -27395,10 +27395,10 @@
         </is>
       </c>
       <c r="L67" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M67" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N67" s="9" t="n">
         <v>13</v>
@@ -27416,7 +27416,7 @@
       </c>
       <c r="R67" s="12" t="inlineStr">
         <is>
-          <t>Purely Plant laboratory — iCoA covering Ident A + B; outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest); Purely Plant laboratory — iCoA covering Foreign matter</t>
+          <t>Purely Plant laboratory — iCoA covering Ident A + B; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
       <c r="S67" s="12" t="inlineStr"/>
@@ -27466,10 +27466,10 @@
         </is>
       </c>
       <c r="L68" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M68" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N68" s="5" t="n">
         <v>13</v>
@@ -27487,7 +27487,7 @@
       </c>
       <c r="R68" s="7" t="inlineStr">
         <is>
-          <t>Purely Plant laboratory — iCoA covering Ident A + B; outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest); Purely Plant laboratory — iCoA covering Foreign matter</t>
+          <t>Purely Plant laboratory — iCoA covering Ident A + B; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
       <c r="S68" s="7" t="inlineStr"/>
@@ -27537,10 +27537,10 @@
         </is>
       </c>
       <c r="L69" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="M69" s="9" t="n">
         <v>3</v>
-      </c>
-      <c r="M69" s="9" t="n">
-        <v>4</v>
       </c>
       <c r="N69" s="9" t="n">
         <v>14</v>
@@ -27558,7 +27558,7 @@
       </c>
       <c r="R69" s="12" t="inlineStr">
         <is>
-          <t>Purely Plant laboratory — iCoA covering Ident A + B; outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest); Purely Plant laboratory — iCoA covering Foreign matter</t>
+          <t>Purely Plant laboratory — iCoA covering Ident A + B; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
       <c r="S69" s="12" t="inlineStr"/>
@@ -27608,10 +27608,10 @@
         </is>
       </c>
       <c r="L70" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M70" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N70" s="5" t="n">
         <v>13</v>
@@ -27629,7 +27629,7 @@
       </c>
       <c r="R70" s="7" t="inlineStr">
         <is>
-          <t>Purely Plant laboratory — iCoA covering Ident A + B; outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest); Purely Plant laboratory — iCoA covering Foreign matter</t>
+          <t>Purely Plant laboratory — iCoA covering Ident A + B; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
       <c r="S70" s="7" t="inlineStr"/>
@@ -27679,10 +27679,10 @@
         </is>
       </c>
       <c r="L71" s="9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M71" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N71" s="9" t="n">
         <v>2</v>
@@ -27700,7 +27700,7 @@
       </c>
       <c r="R71" s="12" t="inlineStr">
         <is>
-          <t>Purely Plant laboratory — iCoA covering Ident A + B; outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest); Purely Plant laboratory — iCoA covering Foreign matter</t>
+          <t>Purely Plant laboratory — iCoA covering Ident A + B; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
       <c r="S71" s="12" t="inlineStr"/>
@@ -27750,10 +27750,10 @@
         </is>
       </c>
       <c r="L72" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M72" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N72" s="5" t="n">
         <v>3</v>
@@ -27771,7 +27771,7 @@
       </c>
       <c r="R72" s="7" t="inlineStr">
         <is>
-          <t>Purely Plant laboratory — iCoA covering Ident A + B; outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest); Purely Plant laboratory — iCoA covering Foreign matter</t>
+          <t>Purely Plant laboratory — iCoA covering Ident A + B; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
       <c r="S72" s="7" t="inlineStr"/>
@@ -27821,10 +27821,10 @@
         </is>
       </c>
       <c r="L73" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="M73" s="9" t="n">
         <v>3</v>
-      </c>
-      <c r="M73" s="9" t="n">
-        <v>4</v>
       </c>
       <c r="N73" s="9" t="n">
         <v>14</v>
@@ -27842,7 +27842,7 @@
       </c>
       <c r="R73" s="12" t="inlineStr">
         <is>
-          <t>Purely Plant laboratory — iCoA covering Ident A + B; outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest); Purely Plant laboratory — iCoA covering Foreign matter</t>
+          <t>Purely Plant laboratory — iCoA covering Ident A + B; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
       <c r="S73" s="12" t="inlineStr"/>
@@ -27892,10 +27892,10 @@
         </is>
       </c>
       <c r="L74" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="M74" s="5" t="n">
         <v>3</v>
-      </c>
-      <c r="M74" s="5" t="n">
-        <v>4</v>
       </c>
       <c r="N74" s="5" t="n">
         <v>14</v>
@@ -27913,7 +27913,7 @@
       </c>
       <c r="R74" s="7" t="inlineStr">
         <is>
-          <t>Purely Plant laboratory — iCoA covering Ident A + B; outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest); Purely Plant laboratory — iCoA covering Foreign matter</t>
+          <t>Purely Plant laboratory — iCoA covering Ident A + B; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
       <c r="S74" s="7" t="inlineStr"/>
@@ -27963,10 +27963,10 @@
         </is>
       </c>
       <c r="L75" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="M75" s="9" t="n">
         <v>3</v>
-      </c>
-      <c r="M75" s="9" t="n">
-        <v>4</v>
       </c>
       <c r="N75" s="9" t="n">
         <v>14</v>
@@ -27984,7 +27984,7 @@
       </c>
       <c r="R75" s="12" t="inlineStr">
         <is>
-          <t>Purely Plant laboratory — iCoA covering Ident A + B; outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest); Purely Plant laboratory — iCoA covering Foreign matter</t>
+          <t>Purely Plant laboratory — iCoA covering Ident A + B; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
       <c r="S75" s="12" t="inlineStr"/>
@@ -28034,10 +28034,10 @@
         </is>
       </c>
       <c r="L76" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="M76" s="5" t="n">
         <v>3</v>
-      </c>
-      <c r="M76" s="5" t="n">
-        <v>4</v>
       </c>
       <c r="N76" s="5" t="n">
         <v>14</v>
@@ -28055,7 +28055,7 @@
       </c>
       <c r="R76" s="7" t="inlineStr">
         <is>
-          <t>Purely Plant laboratory — iCoA covering Ident A + B; outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest); Purely Plant laboratory — iCoA covering Foreign matter</t>
+          <t>Purely Plant laboratory — iCoA covering Ident A + B; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
       <c r="S76" s="7" t="inlineStr"/>
@@ -28105,10 +28105,10 @@
         </is>
       </c>
       <c r="L77" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="M77" s="9" t="n">
         <v>3</v>
-      </c>
-      <c r="M77" s="9" t="n">
-        <v>4</v>
       </c>
       <c r="N77" s="9" t="n">
         <v>14</v>
@@ -28126,7 +28126,7 @@
       </c>
       <c r="R77" s="12" t="inlineStr">
         <is>
-          <t>Purely Plant laboratory — iCoA covering Ident A + B; outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest); Purely Plant laboratory — iCoA covering Foreign matter</t>
+          <t>Purely Plant laboratory — iCoA covering Ident A + B; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
       <c r="S77" s="12" t="inlineStr"/>
@@ -28176,10 +28176,10 @@
         </is>
       </c>
       <c r="L78" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M78" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N78" s="5" t="n">
         <v>13</v>
@@ -28197,7 +28197,7 @@
       </c>
       <c r="R78" s="7" t="inlineStr">
         <is>
-          <t>outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="S78" s="7" t="inlineStr"/>
@@ -28247,10 +28247,10 @@
         </is>
       </c>
       <c r="L79" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M79" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N79" s="9" t="n">
         <v>13</v>
@@ -28268,7 +28268,7 @@
       </c>
       <c r="R79" s="12" t="inlineStr">
         <is>
-          <t>outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="S79" s="12" t="inlineStr"/>
@@ -28318,10 +28318,10 @@
         </is>
       </c>
       <c r="L80" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M80" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N80" s="5" t="n">
         <v>13</v>
@@ -28339,7 +28339,7 @@
       </c>
       <c r="R80" s="7" t="inlineStr">
         <is>
-          <t>outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="S80" s="7" t="inlineStr"/>
@@ -28389,10 +28389,10 @@
         </is>
       </c>
       <c r="L81" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M81" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N81" s="9" t="n">
         <v>13</v>
@@ -28410,7 +28410,7 @@
       </c>
       <c r="R81" s="12" t="inlineStr">
         <is>
-          <t>outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="S81" s="12" t="inlineStr"/>
@@ -28460,10 +28460,10 @@
         </is>
       </c>
       <c r="L82" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M82" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N82" s="5" t="n">
         <v>13</v>
@@ -28481,7 +28481,7 @@
       </c>
       <c r="R82" s="7" t="inlineStr">
         <is>
-          <t>outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="S82" s="7" t="inlineStr"/>
@@ -28531,10 +28531,10 @@
         </is>
       </c>
       <c r="L83" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M83" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N83" s="9" t="n">
         <v>13</v>
@@ -28552,7 +28552,7 @@
       </c>
       <c r="R83" s="12" t="inlineStr">
         <is>
-          <t>outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="S83" s="12" t="inlineStr"/>
@@ -28602,10 +28602,10 @@
         </is>
       </c>
       <c r="L84" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M84" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N84" s="5" t="n">
         <v>13</v>
@@ -28623,7 +28623,7 @@
       </c>
       <c r="R84" s="7" t="inlineStr">
         <is>
-          <t>outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="S84" s="7" t="inlineStr"/>
@@ -28673,10 +28673,10 @@
         </is>
       </c>
       <c r="L85" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M85" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N85" s="9" t="n">
         <v>13</v>
@@ -28694,7 +28694,7 @@
       </c>
       <c r="R85" s="12" t="inlineStr">
         <is>
-          <t>outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="S85" s="12" t="inlineStr"/>
@@ -28744,10 +28744,10 @@
         </is>
       </c>
       <c r="L86" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M86" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N86" s="5" t="n">
         <v>13</v>
@@ -28765,7 +28765,7 @@
       </c>
       <c r="R86" s="7" t="inlineStr">
         <is>
-          <t>outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="S86" s="7" t="inlineStr"/>
@@ -28832,7 +28832,7 @@
       <c r="Q87" s="12" t="inlineStr"/>
       <c r="R87" s="12" t="inlineStr">
         <is>
-          <t>Purely Plant laboratory — iCoA covering Ident A + B; outside laboratory — Ident C (CNP Ident C only, or Farmahem with the retest); Purely Plant laboratory — iCoA covering Foreign matter</t>
+          <t>Purely Plant laboratory — iCoA covering Ident A + B; Purely Plant laboratory — iCoA covering Foreign matter</t>
         </is>
       </c>
       <c r="S87" s="12" t="inlineStr"/>
@@ -28894,10 +28894,10 @@
         </is>
       </c>
       <c r="L88" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M88" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N88" s="5" t="n">
         <v>0</v>
@@ -28981,10 +28981,10 @@
         </is>
       </c>
       <c r="L89" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M89" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N89" s="9" t="n">
         <v>0</v>
@@ -29147,10 +29147,10 @@
         </is>
       </c>
       <c r="L91" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M91" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N91" s="9" t="n">
         <v>0</v>
@@ -29234,10 +29234,10 @@
         </is>
       </c>
       <c r="L92" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M92" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N92" s="5" t="n">
         <v>0</v>
@@ -29317,10 +29317,10 @@
         </is>
       </c>
       <c r="L93" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M93" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N93" s="9" t="n">
         <v>0</v>
@@ -29483,10 +29483,10 @@
         </is>
       </c>
       <c r="L95" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M95" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N95" s="9" t="n">
         <v>0</v>
@@ -29570,10 +29570,10 @@
         </is>
       </c>
       <c r="L96" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M96" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N96" s="5" t="n">
         <v>0</v>
@@ -29819,10 +29819,10 @@
         </is>
       </c>
       <c r="L99" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M99" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N99" s="9" t="n">
         <v>0</v>
@@ -29985,10 +29985,10 @@
         </is>
       </c>
       <c r="L101" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M101" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N101" s="9" t="n">
         <v>0</v>
@@ -30068,10 +30068,10 @@
         </is>
       </c>
       <c r="L102" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M102" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N102" s="5" t="n">
         <v>0</v>
@@ -30645,10 +30645,10 @@
         </is>
       </c>
       <c r="L109" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M109" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N109" s="9" t="n">
         <v>0</v>
@@ -30894,10 +30894,10 @@
         </is>
       </c>
       <c r="L112" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M112" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N112" s="5" t="n">
         <v>0</v>
@@ -31056,10 +31056,10 @@
         </is>
       </c>
       <c r="L114" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M114" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N114" s="5" t="n">
         <v>0</v>
@@ -31637,10 +31637,10 @@
         </is>
       </c>
       <c r="L121" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M121" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N121" s="9" t="n">
         <v>0</v>
@@ -31886,10 +31886,10 @@
         </is>
       </c>
       <c r="L124" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M124" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N124" s="5" t="n">
         <v>0</v>
@@ -32048,10 +32048,10 @@
         </is>
       </c>
       <c r="L126" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M126" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N126" s="5" t="n">
         <v>0</v>
@@ -32380,10 +32380,10 @@
         </is>
       </c>
       <c r="L130" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M130" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N130" s="5" t="n">
         <v>0</v>
@@ -32550,10 +32550,10 @@
         </is>
       </c>
       <c r="L132" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M132" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N132" s="5" t="n">
         <v>0</v>
@@ -32803,10 +32803,10 @@
         </is>
       </c>
       <c r="L135" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M135" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N135" s="9" t="n">
         <v>0</v>
@@ -33611,10 +33611,10 @@
         </is>
       </c>
       <c r="L147" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M147" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N147" s="9" t="n">
         <v>0</v>
@@ -35089,10 +35089,10 @@
         </is>
       </c>
       <c r="L169" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M169" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N169" s="9" t="n">
         <v>0</v>
@@ -35213,7 +35213,7 @@
     <row r="9">
       <c r="A9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">  full panel — Ident A + B + C + foreign matter</t>
+          <t xml:space="preserve">  Ident A + B + foreign matter — Ident C discharged by the HPLC certificate</t>
         </is>
       </c>
       <c r="B9" s="20" t="n">
@@ -35224,7 +35224,7 @@
     <row r="10">
       <c r="A10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Ident C only — CNP Ph. Eur. 11.5 form covers the rest</t>
+          <t xml:space="preserve">  none owed — the CNP Ph. Eur. 11.5 form covers identity and foreign matter</t>
         </is>
       </c>
       <c r="B10" s="20" t="n">
@@ -35420,7 +35420,7 @@
         </is>
       </c>
       <c r="B26" s="20" t="n">
-        <v>896</v>
+        <v>990</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
@@ -35435,7 +35435,7 @@
         </is>
       </c>
       <c r="B27" s="20" t="n">
-        <v>617</v>
+        <v>523</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
@@ -35558,7 +35558,7 @@
         </is>
       </c>
       <c r="B36" s="20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C36" s="2" t="inlineStr"/>
     </row>
@@ -35639,7 +35639,7 @@
         </is>
       </c>
       <c r="B43" s="20" t="n">
-        <v>163</v>
+        <v>69</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>

--- a/deliverables/qc_gap_analysis/PP_QC_Document_Registers_2026-08-31.xlsx
+++ b/deliverables/qc_gap_analysis/PP_QC_Document_Registers_2026-08-31.xlsx
@@ -22661,7 +22661,7 @@
         </is>
       </c>
       <c r="L9" s="9" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="M9" s="9" t="n">
         <v>3</v>
@@ -22748,7 +22748,7 @@
         </is>
       </c>
       <c r="L10" s="5" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="M10" s="5" t="n">
         <v>3</v>
@@ -23772,7 +23772,7 @@
         </is>
       </c>
       <c r="L22" s="5" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="M22" s="5" t="n">
         <v>3</v>
@@ -27750,7 +27750,7 @@
         </is>
       </c>
       <c r="L72" s="5" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="M72" s="5" t="n">
         <v>3</v>
@@ -35420,7 +35420,7 @@
         </is>
       </c>
       <c r="B26" s="20" t="n">
-        <v>990</v>
+        <v>954</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
@@ -35558,7 +35558,7 @@
         </is>
       </c>
       <c r="B36" s="20" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C36" s="2" t="inlineStr"/>
     </row>
